--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <x:si>
     <x:t>EZMId</x:t>
   </x:si>
@@ -73,93 +73,78 @@
     <x:t>X-ray Grading</x:t>
   </x:si>
   <x:si>
-    <x:t>3169-CCB1</x:t>
+    <x:t>ACAF-C6JQ</x:t>
   </x:si>
   <x:si>
     <x:t>margalla hill</x:t>
   </x:si>
   <x:si>
-    <x:t>3535</x:t>
+    <x:t>Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/01/1900 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">                                                                                                    </x:t>
+  </x:si>
+  <x:si>
+    <x:t>83B6-ED47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>87DF-QPTY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>potential test test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz1@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nabeel Ahmed,Nabeel Ahmed,arsalan team member,Nabeel Ahmed,Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10/01/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/01/0001 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7900-P6ME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sufi cup</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/27/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/28/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8540-Q7DB</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>
   </x:si>
   <x:si>
-    <x:t>Owner nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03/05/2023 00:00:00 +00:00</x:t>
+    <x:t xml:space="preserve">tag 3 </x:t>
   </x:si>
   <x:si>
     <x:t>test</x:t>
   </x:si>
   <x:si>
-    <x:t>test occupation</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">                                                                                                    </x:t>
-  </x:si>
-  <x:si>
-    <x:t>543534</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03/04/2023 19:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83B6-ED47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/01/1900 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>87DF-QPTY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>potential test test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenz1@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nabeel Ahmed,Nabeel Ahmed,arsalan team member,Nabeel Ahmed,Nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tag 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10/01/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/01/0001 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7900-P6ME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sufi cup</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02/27/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02/28/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8540-Q7DB</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tag 3 </x:t>
-  </x:si>
-  <x:si>
     <x:t>F4B8-KXPP</x:t>
   </x:si>
   <x:si>
@@ -187,6 +172,9 @@
     <x:t>basic web</x:t>
   </x:si>
   <x:si>
+    <x:t>arsalan team member</x:t>
+  </x:si>
+  <x:si>
     <x:t>02/15/2023 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
@@ -200,9 +188,6 @@
   </x:si>
   <x:si>
     <x:t>Client nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member</x:t>
   </x:si>
   <x:si>
     <x:t>01/02/1996 00:00:00 +00:00</x:t>
@@ -308,8 +293,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S15" totalsRowShown="0">
-  <x:autoFilter ref="A1:S15"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S14" totalsRowShown="0">
+  <x:autoFilter ref="A1:S14"/>
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="EZMId"/>
     <x:tableColumn id="2" name="Name"/>
@@ -623,7 +608,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:S15"/>
+  <x:dimension ref="A1:S14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -692,90 +677,75 @@
       <x:c r="B2" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="F2" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
+      <x:c r="H2" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K2" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="P2" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
       <x:c r="A3" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
+      <x:c r="H3" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="P3" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S3" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:19">
       <x:c r="A4" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
+      <x:c r="G4" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E4" s="0" t="s">
+      <x:c r="H4" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="P4" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="S4" s="0" t="s">
-        <x:v>27</x:v>
+      <x:c r="J4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="O4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="Q4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="R4" s="0" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:19">
@@ -789,354 +759,325 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="G5" s="0" t="s">
+      <x:c r="J5" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="N5" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="N5" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="Q5" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="P5" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
       <x:c r="R5" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="S5" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:19">
       <x:c r="A6" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
+      <x:c r="H6" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="P6" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="Q6" s="0" t="s">
+        <x:v>33</x:v>
       </x:c>
       <x:c r="R6" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="S6" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:19">
       <x:c r="A7" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
+      <x:c r="H7" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="L7" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="N7" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="O7" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="Q7" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="R7" s="0" t="s">
-        <x:v>40</x:v>
+      <x:c r="P7" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S7" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:19">
       <x:c r="A8" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
+      <x:c r="J8" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="P8" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S8" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:19">
       <x:c r="A9" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>54</x:v>
+      <x:c r="O9" s="0" t="s">
+        <x:v>53</x:v>
       </x:c>
       <x:c r="P9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R9" s="0" t="s">
+        <x:v>53</x:v>
       </x:c>
       <x:c r="S9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:19">
       <x:c r="A10" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>53</x:v>
       </x:c>
       <x:c r="O10" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="P10" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="R10" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="S10" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:19">
       <x:c r="A11" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="O11" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P11" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="R11" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S11" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:19">
       <x:c r="A12" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B12" s="0" t="s">
+      <x:c r="I12" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>33</x:v>
+      <x:c r="J12" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="O12" s="0" t="s">
+        <x:v>64</x:v>
       </x:c>
       <x:c r="P12" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="Q12" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="R12" s="0" t="s">
+        <x:v>66</x:v>
       </x:c>
       <x:c r="S12" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:19">
       <x:c r="A13" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F13" s="0" t="s">
+      <x:c r="L13" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="H13" s="0" t="s">
+      <x:c r="N13" s="0" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="I13" s="0" t="s">
+      <x:c r="O13" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="J13" s="0" t="s">
+      <x:c r="P13" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="K13" s="0" t="s">
+      <x:c r="Q13" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="R13" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="L13" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="N13" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="O13" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="P13" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="Q13" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="R13" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="S13" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:19">
       <x:c r="A14" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="I14" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="K14" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="L14" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="N14" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="O14" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="P14" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="Q14" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="R14" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="S14" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:19">
-      <x:c r="A15" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E15" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F15" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G15" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H15" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="J15" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="N15" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="O15" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="Q15" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="R15" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <x:si>
     <x:t>EZMId</x:t>
   </x:si>
@@ -73,10 +73,13 @@
     <x:t>X-ray Grading</x:t>
   </x:si>
   <x:si>
-    <x:t>ACAF-C6JQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>margalla hill</x:t>
+    <x:t>83B6-ED47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123@gmail.com</x:t>
   </x:si>
   <x:si>
     <x:t>Owner nabeel</x:t>
@@ -86,15 +89,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">                                                                                                    </x:t>
-  </x:si>
-  <x:si>
-    <x:t>83B6-ED47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123@gmail.com</x:t>
   </x:si>
   <x:si>
     <x:t>87DF-QPTY</x:t>
@@ -293,8 +287,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S14" totalsRowShown="0">
-  <x:autoFilter ref="A1:S14"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S13" totalsRowShown="0">
+  <x:autoFilter ref="A1:S13"/>
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="EZMId"/>
     <x:tableColumn id="2" name="Name"/>
@@ -608,7 +602,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:S14"/>
+  <x:dimension ref="A1:S13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -677,252 +671,249 @@
       <x:c r="B2" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
       <x:c r="A3" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="P3" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="S3" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="O3" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="Q3" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="R3" s="0" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:19">
       <x:c r="A4" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="Q4" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="P4" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R4" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="S4" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:19">
       <x:c r="A5" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
+        <x:v>40</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="P5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="Q5" s="0" t="s">
+        <x:v>31</x:v>
       </x:c>
       <x:c r="R5" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="S5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:19">
       <x:c r="A6" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="L6" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="N6" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="O6" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="Q6" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="R6" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="P6" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S6" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:19">
       <x:c r="A7" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
+      <x:c r="F7" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="E7" s="0" t="s">
+      <x:c r="H7" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="F7" s="0" t="s">
+      <x:c r="I7" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="H7" s="0" t="s">
+      <x:c r="J7" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="P7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="S7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:19">
       <x:c r="A8" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="O8" s="0" t="s">
+        <x:v>51</x:v>
       </x:c>
       <x:c r="P8" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="R8" s="0" t="s">
+        <x:v>51</x:v>
       </x:c>
       <x:c r="S8" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:19">
       <x:c r="A9" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B9" s="0" t="s">
+      <x:c r="H9" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>53</x:v>
+      <x:c r="J9" s="0" t="s">
+        <x:v>51</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="P9" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R9" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="S9" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:19">
       <x:c r="A10" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="O10" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P10" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="R10" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="S10" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:19">
@@ -932,152 +923,135 @@
       <x:c r="B11" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L11" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="O11" s="0" t="s">
+        <x:v>62</x:v>
       </x:c>
       <x:c r="P11" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="Q11" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="R11" s="0" t="s">
+        <x:v>64</x:v>
       </x:c>
       <x:c r="S11" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:19">
       <x:c r="A12" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B12" s="0" t="s">
+      <x:c r="I12" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="I12" s="0" t="s">
+      <x:c r="J12" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="J12" s="0" t="s">
+      <x:c r="L12" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="K12" s="0" t="s">
+      <x:c r="N12" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="L12" s="0" t="s">
+      <x:c r="O12" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="N12" s="0" t="s">
+      <x:c r="P12" s="0" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="O12" s="0" t="s">
+      <x:c r="Q12" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="R12" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="P12" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="Q12" s="0" t="s">
+      <x:c r="S12" s="0" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="R12" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="S12" s="0" t="s">
-        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:19">
       <x:c r="A13" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="F13" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="I13" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="K13" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L13" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="N13" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="O13" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="P13" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="Q13" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="R13" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="S13" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:19">
-      <x:c r="A14" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="E14" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F14" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G14" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H14" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="J14" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="N14" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="O14" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="Q14" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="R14" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <x:si>
     <x:t>EZMId</x:t>
   </x:si>
@@ -112,6 +112,12 @@
     <x:t>01/01/0001 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
+    <x:t>A107-XTIX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>margalla hill</x:t>
+  </x:si>
+  <x:si>
     <x:t>7900-P6ME</x:t>
   </x:si>
   <x:si>
@@ -223,7 +229,7 @@
     <x:t>333333333</x:t>
   </x:si>
   <x:si>
-    <x:t>Nabeel Ahmed,Nabeel Ahmed,Nabeel Ahmed</x:t>
+    <x:t>Nabeel Ahmed,Nabeel Ahmed</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -287,8 +293,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S13" totalsRowShown="0">
-  <x:autoFilter ref="A1:S13"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S14" totalsRowShown="0">
+  <x:autoFilter ref="A1:S14"/>
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="EZMId"/>
     <x:tableColumn id="2" name="Name"/>
@@ -602,7 +608,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:S13"/>
+  <x:dimension ref="A1:S14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -729,29 +735,14 @@
       <x:c r="B4" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="O4" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P4" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="R4" s="0" t="s">
-        <x:v>35</x:v>
       </x:c>
       <x:c r="S4" s="0" t="s">
         <x:v>24</x:v>
@@ -759,82 +750,88 @@
     </x:row>
     <x:row r="5" spans="1:19">
       <x:c r="A5" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
+      <x:c r="J5" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="N5" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="N5" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="Q5" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="P5" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R5" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="S5" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:19">
       <x:c r="A6" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
+      <x:c r="H6" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="P6" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S6" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="N6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="O6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="Q6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="R6" s="0" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:19">
       <x:c r="A7" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="P7" s="0" t="s">
@@ -846,25 +843,28 @@
     </x:row>
     <x:row r="8" spans="1:19">
       <x:c r="A8" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
+      <x:c r="J8" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="O8" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="P8" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="R8" s="0" t="s">
-        <x:v>51</x:v>
       </x:c>
       <x:c r="S8" s="0" t="s">
         <x:v>24</x:v>
@@ -872,28 +872,25 @@
     </x:row>
     <x:row r="9" spans="1:19">
       <x:c r="A9" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="P9" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="R9" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="S9" s="0" t="s">
         <x:v>24</x:v>
@@ -901,16 +898,28 @@
     </x:row>
     <x:row r="10" spans="1:19">
       <x:c r="A10" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B10" s="0" t="s">
+      <x:c r="H10" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>23</x:v>
+      <x:c r="J10" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="O10" s="0" t="s">
+        <x:v>53</x:v>
       </x:c>
       <x:c r="P10" s="0" t="s">
         <x:v>24</x:v>
+      </x:c>
+      <x:c r="R10" s="0" t="s">
+        <x:v>53</x:v>
       </x:c>
       <x:c r="S10" s="0" t="s">
         <x:v>24</x:v>
@@ -923,134 +932,151 @@
       <x:c r="B11" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="I11" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="L11" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="N11" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="O11" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P11" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="Q11" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="R11" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="S11" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:19">
       <x:c r="A12" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="O12" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="P12" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="K12" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="L12" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="N12" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="O12" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="P12" s="0" t="s">
+      <x:c r="Q12" s="0" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="Q12" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="R12" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="S12" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:19">
       <x:c r="A13" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L13" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="N13" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="O13" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="P13" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="Q13" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="R13" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="S13" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:19">
+      <x:c r="A14" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="G13" s="0" t="s">
+      <x:c r="D14" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="H13" s="0" t="s">
+      <x:c r="H14" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="J13" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="N13" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="O13" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="Q13" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="R13" s="0" t="s">
+      <x:c r="J14" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="N14" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="O14" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="Q14" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="R14" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
     </x:row>

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -112,70 +112,70 @@
     <x:t>01/01/0001 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>A107-XTIX</x:t>
+    <x:t>7900-P6ME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sufi cup</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/27/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/28/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8540-Q7DB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>211267313</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tag 3 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F4B8-KXPP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nab ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rananabeelahmed772@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/03/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2323232332332</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/09/2023 06:52:56 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A5C1-YB22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>basic web</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/15/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>042C-IXD8</x:t>
   </x:si>
   <x:si>
     <x:t>margalla hill</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7900-P6ME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sufi cup</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02/27/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02/28/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8540-Q7DB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>211267313</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tag 3 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F4B8-KXPP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nab ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rananabeelahmed772@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/03/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2323232332332</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/09/2023 06:52:56 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A5C1-YB22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>basic web</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02/15/2023 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
     <x:t>1D77-ED7L</x:t>
@@ -735,14 +735,29 @@
       <x:c r="B4" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="N4" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="O4" s="0" t="s">
+        <x:v>35</x:v>
       </x:c>
       <x:c r="P4" s="0" t="s">
         <x:v>24</x:v>
+      </x:c>
+      <x:c r="R4" s="0" t="s">
+        <x:v>35</x:v>
       </x:c>
       <x:c r="S4" s="0" t="s">
         <x:v>24</x:v>
@@ -750,88 +765,82 @@
     </x:row>
     <x:row r="5" spans="1:19">
       <x:c r="A5" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
+        <x:v>40</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="P5" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="Q5" s="0" t="s">
+        <x:v>31</x:v>
       </x:c>
       <x:c r="R5" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="S5" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:19">
       <x:c r="A6" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="L6" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="N6" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="O6" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="Q6" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="R6" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="P6" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S6" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:19">
       <x:c r="A7" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
+      <x:c r="F7" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="E7" s="0" t="s">
+      <x:c r="H7" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="F7" s="0" t="s">
+      <x:c r="I7" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="H7" s="0" t="s">
+      <x:c r="J7" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="P7" s="0" t="s">
@@ -843,28 +852,25 @@
     </x:row>
     <x:row r="8" spans="1:19">
       <x:c r="A8" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="O8" s="0" t="s">
+        <x:v>51</x:v>
       </x:c>
       <x:c r="P8" s="0" t="s">
         <x:v>24</x:v>
+      </x:c>
+      <x:c r="R8" s="0" t="s">
+        <x:v>51</x:v>
       </x:c>
       <x:c r="S8" s="0" t="s">
         <x:v>24</x:v>
@@ -872,25 +878,28 @@
     </x:row>
     <x:row r="9" spans="1:19">
       <x:c r="A9" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B9" s="0" t="s">
+      <x:c r="H9" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>53</x:v>
+      <x:c r="J9" s="0" t="s">
+        <x:v>51</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="P9" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="R9" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="S9" s="0" t="s">
         <x:v>24</x:v>
@@ -898,28 +907,19 @@
     </x:row>
     <x:row r="10" spans="1:19">
       <x:c r="A10" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="O10" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P10" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="R10" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="S10" s="0" t="s">
         <x:v>24</x:v>
@@ -950,13 +950,13 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
         <x:v>58</x:v>
@@ -1000,13 +1000,13 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
         <x:v>58</x:v>

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
   <x:si>
     <x:t>EZMId</x:t>
   </x:si>
@@ -73,6 +73,48 @@
     <x:t>X-ray Grading</x:t>
   </x:si>
   <x:si>
+    <x:t>BC27-YS4F</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">test </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/01/1900 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/01/0001 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24D9-XVJK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tes test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03/29/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D0C9-M0CQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>testm il</x:t>
+  </x:si>
+  <x:si>
+    <x:t>63FD-0W6X</x:t>
+  </x:si>
+  <x:si>
+    <x:t>margalla hill</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">                                                                                                    </x:t>
+  </x:si>
+  <x:si>
     <x:t>83B6-ED47</x:t>
   </x:si>
   <x:si>
@@ -82,15 +124,6 @@
     <x:t>test123@gmail.com</x:t>
   </x:si>
   <x:si>
-    <x:t>Owner nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/01/1900 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">                                                                                                    </x:t>
-  </x:si>
-  <x:si>
     <x:t>87DF-QPTY</x:t>
   </x:si>
   <x:si>
@@ -109,7 +142,13 @@
     <x:t>10/01/2023 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>01/01/0001 00:00:00 +00:00</x:t>
+    <x:t>0924-9S1L</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,arsalan team member</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/19/2001 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
     <x:t>7900-P6ME</x:t>
@@ -121,12 +160,21 @@
     <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
   </x:si>
   <x:si>
+    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
     <x:t>02/27/2023 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
     <x:t>02/28/2023 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
+    <x:t>5D0A-RMPK</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tst </x:t>
+  </x:si>
+  <x:si>
     <x:t>8540-Q7DB</x:t>
   </x:si>
   <x:si>
@@ -160,36 +208,48 @@
     <x:t>01/09/2023 06:52:56 +00:00</x:t>
   </x:si>
   <x:si>
+    <x:t>AA8F-FH1K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>lets see</x:t>
+  </x:si>
+  <x:si>
     <x:t>A5C1-YB22</x:t>
   </x:si>
   <x:si>
     <x:t>basic web</x:t>
   </x:si>
   <x:si>
+    <x:t>arsalan team member,Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/15/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>043E-D109</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1D77-ED7L</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">testhshhd...1 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBB9-PGI5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>trd test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AE97-FNFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Client nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
     <x:t>arsalan team member</x:t>
   </x:si>
   <x:si>
-    <x:t>02/15/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>042C-IXD8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>margalla hill</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1D77-ED7L</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">testhshhd...1 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>AE97-FNFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Client nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
     <x:t>01/02/1996 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
@@ -230,6 +290,18 @@
   </x:si>
   <x:si>
     <x:t>Nabeel Ahmed,Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F12A-92SY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>first name last name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5657</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz2@gmail.com</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -293,8 +365,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S14" totalsRowShown="0">
-  <x:autoFilter ref="A1:S14"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S23" totalsRowShown="0">
+  <x:autoFilter ref="A1:S23"/>
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="EZMId"/>
     <x:tableColumn id="2" name="Name"/>
@@ -608,7 +680,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:S14"/>
+  <x:dimension ref="A1:S23"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -677,407 +749,662 @@
       <x:c r="B2" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="E2" s="0" t="s">
+      <x:c r="F2" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F2" s="0" t="s">
+      <x:c r="H2" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P2" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S2" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="J2" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N2" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="O2" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q2" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R2" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
       <x:c r="A3" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
+      <x:c r="E3" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
+      <x:c r="F3" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="Q3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="R3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:19">
       <x:c r="A4" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="P4" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q4" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
       <x:c r="R4" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="S4" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:19">
       <x:c r="A5" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="N5" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="O5" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="Q5" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="R5" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P5" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="S5" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:19">
       <x:c r="A6" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P6" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="S6" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:19">
       <x:c r="A7" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="P7" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S7" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N7" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="O7" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q7" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R7" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:19">
       <x:c r="A8" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="P8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q8" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
       <x:c r="R8" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="S8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:19">
       <x:c r="A9" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B9" s="0" t="s">
+      <x:c r="H9" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="F9" s="0" t="s">
+      <x:c r="J9" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="N9" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="O9" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="P9" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="R9" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S9" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:19">
       <x:c r="A10" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="F10" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P10" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S10" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="J10" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N10" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="O10" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q10" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R10" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:19">
       <x:c r="A11" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B11" s="0" t="s">
+      <x:c r="G11" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P11" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S11" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L11" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="O11" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q11" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R11" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:19">
       <x:c r="A12" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="I12" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="J12" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="K12" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="L12" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="N12" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="O12" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
       <x:c r="P12" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="Q12" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="R12" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="S12" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:19">
       <x:c r="A13" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="K13" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L13" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="N13" s="0" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="O13" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
       <x:c r="P13" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="Q13" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="R13" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="S13" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:19">
       <x:c r="A14" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P14" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="S14" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:19">
+      <x:c r="A15" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="B14" s="0" t="s">
+      <x:c r="H15" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="D14" s="0" t="s">
+      <x:c r="O15" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="P15" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="R15" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="S15" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:19">
+      <x:c r="A16" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H16" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="J16" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="O16" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="P16" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="R16" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="S16" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:19">
+      <x:c r="A17" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="E14" s="0" t="s">
+      <x:c r="B17" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H17" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J17" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N17" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="O17" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q17" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R17" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:19">
+      <x:c r="A18" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H18" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P18" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="S18" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:19">
+      <x:c r="A19" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H19" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="F14" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G14" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H14" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="J14" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="N14" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="O14" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="Q14" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="R14" s="0" t="s">
-        <x:v>31</x:v>
+      <x:c r="J19" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N19" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="O19" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q19" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R19" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:19">
+      <x:c r="A20" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F20" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H20" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="I20" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="J20" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K20" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="L20" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="N20" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="O20" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="P20" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="Q20" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="R20" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="S20" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:19">
+      <x:c r="A21" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F21" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H21" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="I21" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="J21" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="K21" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="L21" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="N21" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="O21" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="P21" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="Q21" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="R21" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="S21" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:19">
+      <x:c r="A22" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F22" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G22" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H22" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="J22" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N22" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="O22" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q22" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R22" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:19">
+      <x:c r="A23" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="E23" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F23" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H23" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J23" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N23" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="O23" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q23" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R23" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <x:si>
     <x:t>EZMId</x:t>
   </x:si>
@@ -88,6 +88,21 @@
     <x:t>01/01/0001 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
+    <x:t>A3BE-VZNV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>margalla hill</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">                                                                                                    </x:t>
+  </x:si>
+  <x:si>
+    <x:t>E260-TX8K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>check now</x:t>
+  </x:si>
+  <x:si>
     <x:t>24D9-XVJK</x:t>
   </x:si>
   <x:si>
@@ -106,15 +121,6 @@
     <x:t>testm il</x:t>
   </x:si>
   <x:si>
-    <x:t>63FD-0W6X</x:t>
-  </x:si>
-  <x:si>
-    <x:t>margalla hill</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">                                                                                                    </x:t>
-  </x:si>
-  <x:si>
     <x:t>83B6-ED47</x:t>
   </x:si>
   <x:si>
@@ -151,6 +157,12 @@
     <x:t>01/19/2001 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
+    <x:t>FE65-MJIB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test nabeel</x:t>
+  </x:si>
+  <x:si>
     <x:t>7900-P6ME</x:t>
   </x:si>
   <x:si>
@@ -208,6 +220,12 @@
     <x:t>01/09/2023 06:52:56 +00:00</x:t>
   </x:si>
   <x:si>
+    <x:t>9713-YA5L</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nimal test</x:t>
+  </x:si>
+  <x:si>
     <x:t>AA8F-FH1K</x:t>
   </x:si>
   <x:si>
@@ -302,6 +320,12 @@
   </x:si>
   <x:si>
     <x:t>nabeeloutsourcenz2@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2B7C-80QZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>client nme</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -365,8 +389,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S23" totalsRowShown="0">
-  <x:autoFilter ref="A1:S23"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S27" totalsRowShown="0">
+  <x:autoFilter ref="A1:S27"/>
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="EZMId"/>
     <x:tableColumn id="2" name="Name"/>
@@ -680,7 +704,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:S23"/>
+  <x:dimension ref="A1:S27"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -778,75 +802,66 @@
       <x:c r="B3" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N3" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="O3" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="Q3" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="R3" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P3" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:19">
       <x:c r="A4" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
         <x:v>28</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="O4" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="Q4" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="R4" s="0" t="s">
-        <x:v>23</x:v>
+      <x:c r="P4" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="S4" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:19">
       <x:c r="A5" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
+      <x:c r="E5" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="P5" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="S5" s="0" t="s">
-        <x:v>32</x:v>
+      <x:c r="J5" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N5" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="O5" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q5" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R5" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:19">
@@ -856,69 +871,66 @@
       <x:c r="B6" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="P6" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="S6" s="0" t="s">
-        <x:v>32</x:v>
+      <x:c r="J6" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="O6" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q6" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R6" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:19">
       <x:c r="A7" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
+      <x:c r="E7" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N7" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="O7" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="Q7" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="R7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P7" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="S7" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:19">
       <x:c r="A8" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
+      <x:c r="H8" s="0" t="s">
         <x:v>43</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>44</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
         <x:v>23</x:v>
@@ -938,48 +950,39 @@
     </x:row>
     <x:row r="9" spans="1:19">
       <x:c r="A9" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="B9" s="0" t="s">
+      <x:c r="H9" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="P9" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q9" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
       <x:c r="R9" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="S9" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:19">
       <x:c r="A10" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>22</x:v>
@@ -1002,60 +1005,66 @@
     </x:row>
     <x:row r="11" spans="1:19">
       <x:c r="A11" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
+      <x:c r="J11" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="L11" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="N11" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="O11" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="Q11" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="P11" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="R11" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="S11" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:19">
       <x:c r="A12" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="P12" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="S12" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="O12" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q12" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R12" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:19">
@@ -1063,100 +1072,103 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="E13" s="0" t="s">
+      <x:c r="G13" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="F13" s="0" t="s">
+      <x:c r="H13" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L13" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="H13" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="I13" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="J13" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="P13" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="S13" s="0" t="s">
-        <x:v>32</x:v>
+      <x:c r="N13" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="O13" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q13" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R13" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:19">
       <x:c r="A14" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B14" s="0" t="s">
+      <x:c r="H14" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="H14" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="P14" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="S14" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:19">
       <x:c r="A15" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B15" s="0" t="s">
+      <x:c r="J15" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="F15" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H15" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="O15" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
       <x:c r="P15" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="R15" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="S15" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:19">
       <x:c r="A16" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F16" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="J16" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="O16" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P16" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="R16" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="S16" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:19">
@@ -1164,197 +1176,131 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F17" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J17" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N17" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="O17" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="Q17" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="R17" s="0" t="s">
-        <x:v>23</x:v>
+      <x:c r="P17" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="S17" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:19">
       <x:c r="A18" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="O18" s="0" t="s">
+        <x:v>75</x:v>
       </x:c>
       <x:c r="P18" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="R18" s="0" t="s">
+        <x:v>75</x:v>
       </x:c>
       <x:c r="S18" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:19">
       <x:c r="A19" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="B19" s="0" t="s">
+      <x:c r="F19" s="0" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="F19" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="J19" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N19" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="O19" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="Q19" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="P19" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="R19" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="S19" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:19">
       <x:c r="A20" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D20" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E20" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="I20" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="K20" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="L20" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N20" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="O20" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="P20" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="Q20" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="R20" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="S20" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:19">
       <x:c r="A21" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D21" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E21" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F21" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="I21" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="J21" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="K21" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="L21" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="N21" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="O21" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P21" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="Q21" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="R21" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="S21" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:19">
       <x:c r="A22" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D22" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E22" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="G22" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
         <x:v>23</x:v>
@@ -1374,37 +1320,192 @@
     </x:row>
     <x:row r="23" spans="1:19">
       <x:c r="A23" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E23" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F23" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H23" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="I23" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="J23" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="K23" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="L23" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="N23" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="O23" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="P23" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="Q23" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="R23" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="B23" s="0" t="s">
+      <x:c r="S23" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:19">
+      <x:c r="A24" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F24" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H24" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="I24" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="J24" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="D23" s="0" t="s">
+      <x:c r="K24" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="L24" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="N24" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="O24" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="P24" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="Q24" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="R24" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="S24" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:19">
+      <x:c r="A25" s="0" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="E23" s="0" t="s">
+      <x:c r="B25" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="F23" s="0" t="s">
+      <x:c r="D25" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G25" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H25" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="J25" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N25" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="O25" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q25" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R25" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:19">
+      <x:c r="A26" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="H23" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="J23" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N23" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="O23" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="Q23" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="R23" s="0" t="s">
-        <x:v>23</x:v>
+      <x:c r="H26" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="J26" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N26" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="O26" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q26" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R26" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:19">
+      <x:c r="A27" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H27" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P27" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="S27" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -88,31 +88,31 @@
     <x:t>01/01/0001 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>A3BE-VZNV</x:t>
+    <x:t>E260-TX8K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>check now</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">                                                                                                    </x:t>
+  </x:si>
+  <x:si>
+    <x:t>24D9-XVJK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tes test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03/29/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8D33-8344</x:t>
   </x:si>
   <x:si>
     <x:t>margalla hill</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">                                                                                                    </x:t>
-  </x:si>
-  <x:si>
-    <x:t>E260-TX8K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>check now</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24D9-XVJK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tes test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenz@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03/29/2023 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
     <x:t>D0C9-M0CQ</x:t>
@@ -802,9 +802,6 @@
       <x:c r="B3" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -822,46 +819,49 @@
       <x:c r="B4" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="P4" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="S4" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N4" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="O4" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q4" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R4" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:19">
       <x:c r="A5" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N5" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="O5" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="Q5" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="R5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P5" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="S5" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:19">
@@ -1300,7 +1300,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
         <x:v>23</x:v>
@@ -1473,7 +1473,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
         <x:v>23</x:v>

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
   <x:si>
     <x:t>EZMId</x:t>
   </x:si>
@@ -88,15 +88,21 @@
     <x:t>01/01/0001 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
+    <x:t>00F6-VGS6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>margalla hill</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">                                                                                                    </x:t>
+  </x:si>
+  <x:si>
     <x:t>E260-TX8K</x:t>
   </x:si>
   <x:si>
     <x:t>check now</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">                                                                                                    </x:t>
-  </x:si>
-  <x:si>
     <x:t>24D9-XVJK</x:t>
   </x:si>
   <x:si>
@@ -109,27 +115,42 @@
     <x:t>03/29/2023 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>8D33-8344</x:t>
-  </x:si>
-  <x:si>
-    <x:t>margalla hill</x:t>
-  </x:si>
-  <x:si>
     <x:t>D0C9-M0CQ</x:t>
   </x:si>
   <x:si>
     <x:t>testm il</x:t>
   </x:si>
   <x:si>
+    <x:t>70A6-XDYQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TETSTTTWT TT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>999999</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,add agent</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tag 3 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>10/05/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test sqaq</x:t>
+  </x:si>
+  <x:si>
     <x:t>83B6-ED47</x:t>
   </x:si>
   <x:si>
     <x:t>test test</x:t>
   </x:si>
   <x:si>
-    <x:t>test123@gmail.com</x:t>
-  </x:si>
-  <x:si>
     <x:t>87DF-QPTY</x:t>
   </x:si>
   <x:si>
@@ -163,6 +184,30 @@
     <x:t>test nabeel</x:t>
   </x:si>
   <x:si>
+    <x:t>B349-82KH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>finame shuja</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3535</x:t>
+  </x:si>
+  <x:si>
+    <x:t>211267313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05/25/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test occupation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5435345</x:t>
+  </x:si>
+  <x:si>
     <x:t>7900-P6ME</x:t>
   </x:si>
   <x:si>
@@ -172,9 +217,6 @@
     <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
   </x:si>
   <x:si>
-    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
     <x:t>02/27/2023 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
@@ -188,15 +230,6 @@
   </x:si>
   <x:si>
     <x:t>8540-Q7DB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>211267313</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tag 3 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>test</x:t>
   </x:si>
   <x:si>
     <x:t>F4B8-KXPP</x:t>
@@ -389,8 +422,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S27" totalsRowShown="0">
-  <x:autoFilter ref="A1:S27"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S30" totalsRowShown="0">
+  <x:autoFilter ref="A1:S30"/>
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="EZMId"/>
     <x:tableColumn id="2" name="Name"/>
@@ -704,7 +737,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:S27"/>
+  <x:dimension ref="A1:S30"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -802,6 +835,9 @@
       <x:c r="B3" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -819,49 +855,46 @@
       <x:c r="B4" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="O4" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="Q4" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="R4" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P4" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="S4" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:19">
       <x:c r="A5" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
         <x:v>31</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>32</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="P5" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="S5" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N5" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="O5" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q5" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R5" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:19">
@@ -897,69 +930,81 @@
       <x:c r="B7" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="P7" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="S7" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L7" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="N7" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="O7" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q7" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R7" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:19">
       <x:c r="A8" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N8" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="O8" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="Q8" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="R8" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P8" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="S8" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:19">
       <x:c r="A9" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
         <x:v>23</x:v>
@@ -979,13 +1024,16 @@
     </x:row>
     <x:row r="10" spans="1:19">
       <x:c r="A10" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
         <x:v>23</x:v>
@@ -1005,121 +1053,154 @@
     </x:row>
     <x:row r="11" spans="1:19">
       <x:c r="A11" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N11" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="O11" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="P11" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q11" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
       <x:c r="R11" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="S11" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:19">
       <x:c r="A12" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J12" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>62</x:v>
       </x:c>
       <x:c r="N12" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="O12" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="Q12" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="P12" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="R12" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="S12" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:19">
       <x:c r="A13" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>36</x:v>
+      <x:c r="C13" s="0" t="s">
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G13" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
+        <x:v>61</x:v>
       </x:c>
       <x:c r="L13" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="N13" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="N13" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="O13" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="Q13" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="P13" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="R13" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="S13" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:19">
       <x:c r="A14" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="J14" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="N14" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="O14" s="0" t="s">
+        <x:v>67</x:v>
       </x:c>
       <x:c r="P14" s="0" t="s">
         <x:v>26</x:v>
+      </x:c>
+      <x:c r="R14" s="0" t="s">
+        <x:v>67</x:v>
       </x:c>
       <x:c r="S14" s="0" t="s">
         <x:v>26</x:v>
@@ -1127,59 +1208,83 @@
     </x:row>
     <x:row r="15" spans="1:19">
       <x:c r="A15" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="E15" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="I15" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="P15" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="S15" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N15" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="O15" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q15" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R15" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:19">
       <x:c r="A16" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="P16" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="S16" s="0" t="s">
-        <x:v>26</x:v>
+      <x:c r="J16" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L16" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="N16" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="O16" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q16" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R16" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:19">
       <x:c r="A17" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="P17" s="0" t="s">
         <x:v>26</x:v>
@@ -1195,20 +1300,23 @@
       <x:c r="B18" s="0" t="s">
         <x:v>73</x:v>
       </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="O18" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="I18" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="J18" s="0" t="s">
+        <x:v>78</x:v>
       </x:c>
       <x:c r="P18" s="0" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="R18" s="0" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="S18" s="0" t="s">
         <x:v>26</x:v>
@@ -1216,28 +1324,16 @@
     </x:row>
     <x:row r="19" spans="1:19">
       <x:c r="A19" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="F19" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="J19" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="O19" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P19" s="0" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="R19" s="0" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="S19" s="0" t="s">
         <x:v>26</x:v>
@@ -1245,45 +1341,42 @@
     </x:row>
     <x:row r="20" spans="1:19">
       <x:c r="A20" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F20" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J20" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N20" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="O20" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="Q20" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="R20" s="0" t="s">
-        <x:v>23</x:v>
+      <x:c r="P20" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="S20" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:19">
       <x:c r="A21" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="F21" s="0" t="s">
+        <x:v>85</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="O21" s="0" t="s">
+        <x:v>86</x:v>
       </x:c>
       <x:c r="P21" s="0" t="s">
         <x:v>26</x:v>
+      </x:c>
+      <x:c r="R21" s="0" t="s">
+        <x:v>86</x:v>
       </x:c>
       <x:c r="S21" s="0" t="s">
         <x:v>26</x:v>
@@ -1291,154 +1384,91 @@
     </x:row>
     <x:row r="22" spans="1:19">
       <x:c r="A22" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N22" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="O22" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="Q22" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="P22" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="R22" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="S22" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:19">
       <x:c r="A23" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D23" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="E23" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="I23" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="K23" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="L23" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N23" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="O23" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="P23" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="Q23" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="R23" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="S23" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:19">
       <x:c r="A24" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D24" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="E24" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F24" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="I24" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="J24" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="K24" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="L24" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="N24" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="O24" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P24" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="Q24" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="R24" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="S24" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:19">
       <x:c r="A25" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D25" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="E25" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="G25" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
         <x:v>23</x:v>
@@ -1458,53 +1488,191 @@
     </x:row>
     <x:row r="26" spans="1:19">
       <x:c r="A26" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="H26" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="I26" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="J26" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="K26" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="B26" s="0" t="s">
+      <x:c r="L26" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="D26" s="0" t="s">
+      <x:c r="N26" s="0" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="E26" s="0" t="s">
+      <x:c r="O26" s="0" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="F26" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="H26" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="J26" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N26" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="O26" s="0" t="s">
-        <x:v>23</x:v>
+      <x:c r="P26" s="0" t="s">
+        <x:v>102</x:v>
       </x:c>
       <x:c r="Q26" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="R26" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="S26" s="0" t="s">
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:19">
       <x:c r="A27" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F27" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="H27" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="I27" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="J27" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="K27" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="L27" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="N27" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="O27" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="P27" s="0" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="B27" s="0" t="s">
+      <x:c r="Q27" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="R27" s="0" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="H27" s="0" t="s">
+      <x:c r="S27" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:19">
+      <x:c r="A28" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F28" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G28" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H28" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="J28" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N28" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="O28" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q28" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R28" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:19">
+      <x:c r="A29" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="F29" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H29" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="J29" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N29" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="O29" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q29" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R29" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:19">
+      <x:c r="A30" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H30" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="P27" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="S27" s="0" t="s">
+      <x:c r="P30" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="S30" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
     </x:row>

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="139">
   <x:si>
     <x:t>EZMId</x:t>
   </x:si>
@@ -73,30 +73,48 @@
     <x:t>X-ray Grading</x:t>
   </x:si>
   <x:si>
+    <x:t>F2E4-KJPR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>margalla hill</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/01/1900 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">                                                                                                    </x:t>
+  </x:si>
+  <x:si>
+    <x:t>601F-EQSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test gamux</x:t>
+  </x:si>
+  <x:si>
+    <x:t>a@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>331F-46PG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>st test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test@gmail.com</x:t>
+  </x:si>
+  <x:si>
     <x:t>BC27-YS4F</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">test </x:t>
   </x:si>
   <x:si>
-    <x:t>Owner nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/01/1900 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
     <x:t>01/01/0001 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>00F6-VGS6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>margalla hill</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">                                                                                                    </x:t>
-  </x:si>
-  <x:si>
     <x:t>E260-TX8K</x:t>
   </x:si>
   <x:si>
@@ -115,6 +133,39 @@
     <x:t>03/29/2023 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
+    <x:t>1414-W44K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3540479390287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3233232</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05/24/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05/25/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3323232323</x:t>
+  </x:si>
+  <x:si>
+    <x:t>252F-ASJE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tett test</x:t>
+  </x:si>
+  <x:si>
     <x:t>D0C9-M0CQ</x:t>
   </x:si>
   <x:si>
@@ -151,15 +202,24 @@
     <x:t>test test</x:t>
   </x:si>
   <x:si>
+    <x:t>2289-PRD0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dilbar rukha</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz1@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed,exteme team</x:t>
+  </x:si>
+  <x:si>
     <x:t>87DF-QPTY</x:t>
   </x:si>
   <x:si>
     <x:t>potential test test</x:t>
   </x:si>
   <x:si>
-    <x:t>nabeeloutsourcenz1@gmail.com</x:t>
-  </x:si>
-  <x:si>
     <x:t>Nabeel Ahmed,Nabeel Ahmed,arsalan team member,Nabeel Ahmed,Nabeel Ahmed</x:t>
   </x:si>
   <x:si>
@@ -184,54 +244,39 @@
     <x:t>test nabeel</x:t>
   </x:si>
   <x:si>
-    <x:t>B349-82KH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>finame shuja</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3535</x:t>
+    <x:t>7900-P6ME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sufi cup</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/27/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/28/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5D0A-RMPK</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tst </x:t>
+  </x:si>
+  <x:si>
+    <x:t>8540-Q7DB</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>
   </x:si>
   <x:si>
-    <x:t>05/25/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
     <x:t>test</x:t>
   </x:si>
   <x:si>
-    <x:t>test occupation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5435345</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7900-P6ME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sufi cup</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02/27/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02/28/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5D0A-RMPK</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tst </x:t>
-  </x:si>
-  <x:si>
-    <x:t>8540-Q7DB</x:t>
-  </x:si>
-  <x:si>
     <x:t>F4B8-KXPP</x:t>
   </x:si>
   <x:si>
@@ -265,6 +310,21 @@
     <x:t>lets see</x:t>
   </x:si>
   <x:si>
+    <x:t>1AA1-TIH9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>carmi gandazia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3232323</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4343435435</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5544545</x:t>
+  </x:si>
+  <x:si>
     <x:t>A5C1-YB22</x:t>
   </x:si>
   <x:si>
@@ -277,6 +337,15 @@
     <x:t>02/15/2023 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
+    <x:t>D1DD-IRVU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>khush hona</x:t>
+  </x:si>
+  <x:si>
+    <x:t>khush1@gmail.con</x:t>
+  </x:si>
+  <x:si>
     <x:t>043E-D109</x:t>
   </x:si>
   <x:si>
@@ -286,6 +355,12 @@
     <x:t xml:space="preserve">testhshhd...1 </x:t>
   </x:si>
   <x:si>
+    <x:t>AFA9-V8G1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test missinh</x:t>
+  </x:si>
+  <x:si>
     <x:t>EBB9-PGI5</x:t>
   </x:si>
   <x:si>
@@ -296,9 +371,6 @@
   </x:si>
   <x:si>
     <x:t>Client nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member</x:t>
   </x:si>
   <x:si>
     <x:t>01/02/1996 00:00:00 +00:00</x:t>
@@ -422,8 +494,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S30" totalsRowShown="0">
-  <x:autoFilter ref="A1:S30"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S38" totalsRowShown="0">
+  <x:autoFilter ref="A1:S38"/>
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="EZMId"/>
     <x:tableColumn id="2" name="Name"/>
@@ -737,7 +809,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:S30"/>
+  <x:dimension ref="A1:S38"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -812,19 +884,10 @@
       <x:c r="H2" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J2" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N2" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="O2" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="Q2" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="R2" s="0" t="s">
+      <x:c r="P2" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S2" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
@@ -835,6 +898,9 @@
       <x:c r="B3" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
@@ -842,10 +908,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="P3" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S3" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:19">
@@ -855,46 +921,49 @@
       <x:c r="B4" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="P4" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S4" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:19">
       <x:c r="A5" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="Q5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="R5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:19">
@@ -907,19 +976,10 @@
       <x:c r="H6" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N6" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="O6" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="Q6" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="R6" s="0" t="s">
+      <x:c r="P6" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S6" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
@@ -930,309 +990,273 @@
       <x:c r="B7" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D7" s="0" t="s">
+      <x:c r="E7" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="E7" s="0" t="s">
+      <x:c r="F7" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="L7" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="N7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="O7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="Q7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="R7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:19">
       <x:c r="A8" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
+      <x:c r="F8" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O8" s="0" t="s">
+        <x:v>46</x:v>
       </x:c>
       <x:c r="P8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R8" s="0" t="s">
+        <x:v>46</x:v>
       </x:c>
       <x:c r="S8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:19">
       <x:c r="A9" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="B9" s="0" t="s">
+      <x:c r="I9" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N9" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="O9" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="Q9" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="P9" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="R9" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="S9" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:19">
       <x:c r="A10" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N10" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="O10" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="Q10" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="R10" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P10" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S10" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:19">
       <x:c r="A11" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="N11" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="O11" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="Q11" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="R11" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:19">
       <x:c r="A12" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B12" s="0" t="s">
+      <x:c r="G12" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="C12" s="0" t="s">
+      <x:c r="H12" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="D12" s="0" t="s">
+      <x:c r="J12" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="K12" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L12" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="N12" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="O12" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="P12" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="Q12" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
       <x:c r="R12" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="S12" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:19">
       <x:c r="A13" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I13" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="J13" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="K13" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L13" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="N13" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="O13" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P13" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="R13" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S13" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:19">
       <x:c r="A14" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B14" s="0" t="s">
+      <x:c r="F14" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="E14" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F14" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="J14" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="N14" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="O14" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P14" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="R14" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S14" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:19">
       <x:c r="A15" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="B15" s="0" t="s">
+      <x:c r="H15" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="F15" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="H15" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="J15" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="N15" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="O15" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="Q15" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="R15" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:19">
@@ -1240,440 +1264,672 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D16" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="G16" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="L16" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="N16" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="O16" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="Q16" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="R16" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:19">
       <x:c r="A17" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F17" s="0" t="s">
         <x:v>75</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="P17" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="S17" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J17" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="N17" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="O17" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="Q17" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="R17" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:19">
       <x:c r="A18" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="I18" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="N18" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="O18" s="0" t="s">
+        <x:v>80</x:v>
       </x:c>
       <x:c r="P18" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R18" s="0" t="s">
+        <x:v>80</x:v>
       </x:c>
       <x:c r="S18" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:19">
       <x:c r="A19" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="P19" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="S19" s="0" t="s">
-        <x:v>26</x:v>
+      <x:c r="J19" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="N19" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="O19" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="Q19" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="R19" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:19">
       <x:c r="A20" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="P20" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="S20" s="0" t="s">
-        <x:v>26</x:v>
+      <x:c r="J20" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="L20" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="N20" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="O20" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="Q20" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="R20" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:19">
       <x:c r="A21" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="O21" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="P21" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="R21" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S21" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:19">
       <x:c r="A22" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="I22" s="0" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="O22" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="P22" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="R22" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S22" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:19">
       <x:c r="A23" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F23" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J23" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N23" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="O23" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="Q23" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="R23" s="0" t="s">
+      <x:c r="P23" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S23" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:19">
       <x:c r="A24" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="P24" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S24" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:19">
       <x:c r="A25" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="J25" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="I25" s="0" t="s">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="N25" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="O25" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="Q25" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="R25" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:19">
       <x:c r="A26" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E26" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="J26" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="K26" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="L26" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="N26" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="O26" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="P26" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="Q26" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="R26" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="S26" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:19">
       <x:c r="A27" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D27" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E27" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="I27" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="J27" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="K27" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="L27" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="N27" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="O27" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="P27" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="Q27" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="R27" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="S27" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:19">
       <x:c r="A28" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="F28" s="0" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="B28" s="0" t="s">
+      <x:c r="H28" s="0" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="D28" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="E28" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F28" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="G28" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H28" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="J28" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N28" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="O28" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="Q28" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="P28" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="R28" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="S28" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:19">
       <x:c r="A29" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="D29" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E29" s="0" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="F29" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="N29" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="O29" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="Q29" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="R29" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:19">
       <x:c r="A30" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F30" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H30" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J30" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="N30" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="O30" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="Q30" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="R30" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:19">
+      <x:c r="A31" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="H31" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P31" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S31" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:19">
+      <x:c r="A32" s="0" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="B30" s="0" t="s">
+      <x:c r="B32" s="0" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="H30" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="P30" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="S30" s="0" t="s">
-        <x:v>26</x:v>
+      <x:c r="F32" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H32" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P32" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S32" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:19">
+      <x:c r="A33" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="F33" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H33" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J33" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="N33" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="O33" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="Q33" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="R33" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:19">
+      <x:c r="A34" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="E34" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F34" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H34" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="I34" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="J34" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="K34" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="L34" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="N34" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="O34" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="P34" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="Q34" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="R34" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="S34" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:19">
+      <x:c r="A35" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F35" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H35" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="I35" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="J35" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="K35" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="L35" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="N35" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="O35" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="P35" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="Q35" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="R35" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="S35" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:19">
+      <x:c r="A36" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F36" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="G36" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H36" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="J36" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="N36" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="O36" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="Q36" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="R36" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:19">
+      <x:c r="A37" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F37" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H37" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J37" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="N37" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="O37" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="Q37" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="R37" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:19">
+      <x:c r="A38" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H38" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P38" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S38" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="121">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
   <x:si>
     <x:t>EZMId</x:t>
   </x:si>
@@ -109,6 +109,21 @@
     <x:t>01/01/0001 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
+    <x:t>AE20-18YO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tst client log</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz1@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E1E7-CYE8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>margalla hill</x:t>
+  </x:si>
+  <x:si>
     <x:t>E260-TX8K</x:t>
   </x:si>
   <x:si>
@@ -154,9 +169,6 @@
     <x:t>3323232323</x:t>
   </x:si>
   <x:si>
-    <x:t>1661-L13A</x:t>
-  </x:si>
-  <x:si>
     <x:t>252F-ASJE</x:t>
   </x:si>
   <x:si>
@@ -205,12 +217,15 @@
     <x:t>dilbar rukha</x:t>
   </x:si>
   <x:si>
-    <x:t>nabeeloutsourcenz1@gmail.com</x:t>
-  </x:si>
-  <x:si>
     <x:t>arsalan team member,Nabeel Ahmed,exteme team,Owner nabeel</x:t>
   </x:si>
   <x:si>
+    <x:t>D4C5-ZQQB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tets tet</x:t>
+  </x:si>
+  <x:si>
     <x:t>0924-9S1L</x:t>
   </x:si>
   <x:si>
@@ -292,12 +307,21 @@
     <x:t>lets see</x:t>
   </x:si>
   <x:si>
+    <x:t>2E65-SXT6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>first test</x:t>
+  </x:si>
+  <x:si>
     <x:t>3A8B-SII4</x:t>
   </x:si>
   <x:si>
     <x:t>new last</x:t>
   </x:si>
   <x:si>
+    <x:t>tag 1</x:t>
+  </x:si>
+  <x:si>
     <x:t>1AA1-TIH9</x:t>
   </x:si>
   <x:si>
@@ -328,19 +352,34 @@
     <x:t>D1DD-IRVU</x:t>
   </x:si>
   <x:si>
-    <x:t>khush hona</x:t>
+    <x:t>khush hona1</x:t>
   </x:si>
   <x:si>
     <x:t>khush1@gmail.con</x:t>
   </x:si>
   <x:si>
+    <x:t>4356-V95A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>main husband</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/10/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/02/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/17/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>msin husbanfd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/08/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
     <x:t>043E-D109</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FB3D-2TV8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>margalla hill</x:t>
   </x:si>
   <x:si>
     <x:t>1D77-ED7L</x:t>
@@ -440,8 +479,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S36" totalsRowShown="0">
-  <x:autoFilter ref="A1:S36"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S40" totalsRowShown="0">
+  <x:autoFilter ref="A1:S40"/>
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="EZMId"/>
     <x:tableColumn id="2" name="Name"/>
@@ -755,7 +794,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:S36"/>
+  <x:dimension ref="A1:S40"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -899,6 +938,12 @@
       <x:c r="B5" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -911,69 +956,36 @@
     </x:row>
     <x:row r="6" spans="1:19">
       <x:c r="A6" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N6" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O6" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q6" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R6" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P6" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S6" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:19">
       <x:c r="A7" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O7" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P7" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="R7" s="0" t="s">
-        <x:v>44</x:v>
       </x:c>
       <x:c r="S7" s="0" t="s">
         <x:v>24</x:v>
@@ -981,57 +993,69 @@
     </x:row>
     <x:row r="8" spans="1:19">
       <x:c r="A8" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D8" s="0" t="s">
+      <x:c r="E8" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E8" s="0" t="s">
+      <x:c r="F8" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="P8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q8" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R8" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="S8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:19">
       <x:c r="A9" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>29</x:v>
+      <x:c r="F9" s="0" t="s">
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="O9" s="0" t="s">
+        <x:v>49</x:v>
       </x:c>
       <x:c r="P9" s="0" t="s">
         <x:v>24</x:v>
+      </x:c>
+      <x:c r="R9" s="0" t="s">
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S9" s="0" t="s">
         <x:v>24</x:v>
@@ -1039,16 +1063,40 @@
     </x:row>
     <x:row r="10" spans="1:19">
       <x:c r="A10" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B10" s="0" t="s">
+      <x:c r="H10" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>23</x:v>
+      <x:c r="I10" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="O10" s="0" t="s">
+        <x:v>49</x:v>
       </x:c>
       <x:c r="P10" s="0" t="s">
         <x:v>24</x:v>
+      </x:c>
+      <x:c r="R10" s="0" t="s">
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S10" s="0" t="s">
         <x:v>24</x:v>
@@ -1056,57 +1104,33 @@
     </x:row>
     <x:row r="11" spans="1:19">
       <x:c r="A11" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N11" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O11" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q11" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R11" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="P11" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S11" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:19">
       <x:c r="A12" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="L12" s="0" t="s">
-        <x:v>58</x:v>
       </x:c>
       <x:c r="N12" s="0" t="s">
         <x:v>30</x:v>
@@ -1123,39 +1147,57 @@
     </x:row>
     <x:row r="13" spans="1:19">
       <x:c r="A13" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B13" s="0" t="s">
+      <x:c r="G13" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F13" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P13" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S13" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L13" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="N13" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O13" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q13" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R13" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:19">
       <x:c r="A14" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
         <x:v>23</x:v>
@@ -1172,28 +1214,22 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="J15" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N15" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O15" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q15" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R15" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P15" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S15" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:19">
@@ -1203,23 +1239,17 @@
       <x:c r="B16" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="H16" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="J16" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N16" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O16" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q16" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R16" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="P16" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S16" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:19">
@@ -1227,45 +1257,36 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="E17" s="0" t="s">
+      <x:c r="H17" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="F17" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H17" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
       <x:c r="J17" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N17" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O17" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="P17" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q17" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R17" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="S17" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:19">
       <x:c r="A18" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="F18" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
         <x:v>23</x:v>
@@ -1288,37 +1309,37 @@
     </x:row>
     <x:row r="19" spans="1:19">
       <x:c r="A19" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D19" s="0" t="s">
+      <x:c r="H19" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="G19" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H19" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="J19" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="L19" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="N19" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="N19" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="O19" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q19" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="P19" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R19" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="S19" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:19">
@@ -1328,60 +1349,78 @@
       <x:c r="B20" s="0" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="E20" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="P20" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S20" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J20" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N20" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O20" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q20" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R20" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:19">
       <x:c r="A21" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="E21" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="F21" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
+      <x:c r="G21" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
       <x:c r="H21" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J21" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L21" s="0" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="I21" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="J21" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="P21" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S21" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="N21" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O21" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q21" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R21" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:19">
       <x:c r="A22" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B22" s="0" t="s">
+      <x:c r="F22" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="P22" s="0" t="s">
         <x:v>24</x:v>
@@ -1392,13 +1431,25 @@
     </x:row>
     <x:row r="23" spans="1:19">
       <x:c r="A23" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E23" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F23" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="H23" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="B23" s="0" t="s">
+      <x:c r="I23" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="H23" s="0" t="s">
-        <x:v>23</x:v>
+      <x:c r="J23" s="0" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="P23" s="0" t="s">
         <x:v>24</x:v>
@@ -1409,16 +1460,10 @@
     </x:row>
     <x:row r="24" spans="1:19">
       <x:c r="A24" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="E24" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="F24" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
         <x:v>23</x:v>
@@ -1432,45 +1477,27 @@
     </x:row>
     <x:row r="25" spans="1:19">
       <x:c r="A25" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D25" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="F25" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H25" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="I25" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="N25" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O25" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q25" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R25" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="P25" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S25" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:19">
       <x:c r="A26" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D26" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
         <x:v>22</x:v>
@@ -1478,20 +1505,11 @@
       <x:c r="H26" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="I26" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="N26" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O26" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q26" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R26" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="P26" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S26" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:19">
@@ -1501,20 +1519,23 @@
       <x:c r="B27" s="0" t="s">
         <x:v>100</x:v>
       </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
       <x:c r="F27" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G27" s="0" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="O27" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P27" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="R27" s="0" t="s">
-        <x:v>102</x:v>
       </x:c>
       <x:c r="S27" s="0" t="s">
         <x:v>24</x:v>
@@ -1522,48 +1543,54 @@
     </x:row>
     <x:row r="28" spans="1:19">
       <x:c r="A28" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>104</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="J28" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="I28" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="N28" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O28" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="P28" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q28" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R28" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="S28" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:19">
       <x:c r="A29" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="B29" s="0" t="s">
+      <x:c r="D29" s="0" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="E29" s="0" t="s">
-        <x:v>105</x:v>
+      <x:c r="F29" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="J29" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="I29" s="0" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="N29" s="0" t="s">
         <x:v>30</x:v>
@@ -1580,31 +1607,28 @@
     </x:row>
     <x:row r="30" spans="1:19">
       <x:c r="A30" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="J30" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N30" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="O30" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q30" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="P30" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R30" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="S30" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:19">
@@ -1615,13 +1639,22 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="J31" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="O31" s="0" t="s">
+        <x:v>110</x:v>
       </x:c>
       <x:c r="P31" s="0" t="s">
         <x:v>24</x:v>
+      </x:c>
+      <x:c r="R31" s="0" t="s">
+        <x:v>110</x:v>
       </x:c>
       <x:c r="S31" s="0" t="s">
         <x:v>24</x:v>
@@ -1629,33 +1662,60 @@
     </x:row>
     <x:row r="32" spans="1:19">
       <x:c r="A32" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="E32" s="0" t="s">
+        <x:v>113</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="P32" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S32" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="J32" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N32" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O32" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q32" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R32" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:19">
       <x:c r="A33" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
+      <x:c r="G33" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="I33" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="N33" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="O33" s="0" t="s">
+        <x:v>118</x:v>
       </x:c>
       <x:c r="P33" s="0" t="s">
         <x:v>24</x:v>
@@ -1666,51 +1726,54 @@
     </x:row>
     <x:row r="34" spans="1:19">
       <x:c r="A34" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
+      <x:c r="G34" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="I34" s="0" t="s">
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J34" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="N34" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="O34" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q34" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R34" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="P34" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S34" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:19">
       <x:c r="A35" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="E35" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J35" s="0" t="s">
         <x:v>30</x:v>
@@ -1730,10 +1793,10 @@
     </x:row>
     <x:row r="36" spans="1:19">
       <x:c r="A36" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H36" s="0" t="s">
         <x:v>23</x:v>
@@ -1742,6 +1805,107 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="S36" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:19">
+      <x:c r="A37" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="F37" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H37" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P37" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S37" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:19">
+      <x:c r="A38" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="F38" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H38" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="J38" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N38" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O38" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q38" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R38" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:19">
+      <x:c r="A39" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="E39" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="F39" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H39" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="J39" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N39" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O39" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q39" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R39" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:19">
+      <x:c r="A40" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="H40" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P40" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S40" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
   <x:si>
     <x:t>EZMId</x:t>
   </x:si>
@@ -118,162 +118,222 @@
     <x:t>nabeeloutsourcenz1@gmail.com</x:t>
   </x:si>
   <x:si>
-    <x:t>E1E7-CYE8</x:t>
+    <x:t>D980-Q0AX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel secutriy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>434434434</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/03/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/01/2023 11:20:30 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6F95-P7I6</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">TST </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tag 3 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>2B13-9R2K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nbaaa Efgh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0300000000000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rana44@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11/07/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teacher</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E260-TX8K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>check now</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24D9-XVJK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tes test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03/29/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1414-W44K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3540479390287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3233232</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05/24/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05/25/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3323232323</x:t>
+  </x:si>
+  <x:si>
+    <x:t>252F-ASJE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tett test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D0C9-M0CQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>testm il</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70A6-XDYQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TETSTTTWT TT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>999999</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,add agent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10/05/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test sqaq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83B6-ED47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2289-PRD0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dilbar rukha</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member,Nabeel Ahmed,exteme team,Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D4C5-ZQQB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tets tet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0924-9S1L</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,arsalan team member</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/19/2001 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0F2D-MM6C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">testt </x:t>
+  </x:si>
+  <x:si>
+    <x:t>BE8D-A2NZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>reign test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09/19/1982 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FE65-MJIB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7900-P6ME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sufi cup</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/27/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/28/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5D0A-RMPK</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tst </x:t>
+  </x:si>
+  <x:si>
+    <x:t>E7BC-GDFQ</x:t>
   </x:si>
   <x:si>
     <x:t>margalla hill</x:t>
   </x:si>
   <x:si>
-    <x:t>E260-TX8K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>check now</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24D9-XVJK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tes test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenz@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03/29/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1414-W44K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3540479390287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3233232</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05/24/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05/25/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3323232323</x:t>
-  </x:si>
-  <x:si>
-    <x:t>252F-ASJE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tett test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D0C9-M0CQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>testm il</x:t>
-  </x:si>
-  <x:si>
-    <x:t>70A6-XDYQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TETSTTTWT TT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>999999</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,add agent</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tag 3 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>10/05/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test sqaq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83B6-ED47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2289-PRD0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dilbar rukha</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member,Nabeel Ahmed,exteme team,Owner nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D4C5-ZQQB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tets tet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0924-9S1L</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,arsalan team member</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/19/2001 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FE65-MJIB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7900-P6ME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sufi cup</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02/27/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02/28/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5D0A-RMPK</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tst </x:t>
-  </x:si>
-  <x:si>
     <x:t>8540-Q7DB</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>
   </x:si>
   <x:si>
-    <x:t>test</x:t>
-  </x:si>
-  <x:si>
     <x:t>F4B8-KXPP</x:t>
   </x:si>
   <x:si>
@@ -313,6 +373,30 @@
     <x:t>first test</x:t>
   </x:si>
   <x:si>
+    <x:t>7851-Q2TO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mawaz Ejaz</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawazejaz@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>840E-CILQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel muhammad changes</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33333333</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test3333@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/02/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
     <x:t>3A8B-SII4</x:t>
   </x:si>
   <x:si>
@@ -358,6 +442,12 @@
     <x:t>khush1@gmail.con</x:t>
   </x:si>
   <x:si>
+    <x:t>exteme team</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/11/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
     <x:t>4356-V95A</x:t>
   </x:si>
   <x:si>
@@ -410,6 +500,18 @@
   </x:si>
   <x:si>
     <x:t>nabeeloutsourcenz2@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6EB4-PR75</x:t>
+  </x:si>
+  <x:si>
+    <x:t>toyota  7hecf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3535</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12/25/2023 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
     <x:t>2B7C-80QZ</x:t>
@@ -479,8 +581,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S40" totalsRowShown="0">
-  <x:autoFilter ref="A1:S40"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S49" totalsRowShown="0">
+  <x:autoFilter ref="A1:S49"/>
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="EZMId"/>
     <x:tableColumn id="2" name="Name"/>
@@ -794,7 +896,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:S40"/>
+  <x:dimension ref="A1:S49"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -961,11 +1063,17 @@
       <x:c r="B6" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="P6" s="0" t="s">
         <x:v>24</x:v>
@@ -976,13 +1084,28 @@
     </x:row>
     <x:row r="7" spans="1:19">
       <x:c r="A7" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
+      <x:c r="E7" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>23</x:v>
+      <x:c r="I7" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>39</x:v>
       </x:c>
       <x:c r="P7" s="0" t="s">
         <x:v>24</x:v>
@@ -993,44 +1116,29 @@
     </x:row>
     <x:row r="8" spans="1:19">
       <x:c r="A8" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N8" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O8" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q8" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R8" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P8" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S8" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:19">
       <x:c r="A9" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
@@ -1040,63 +1148,45 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
+      <x:c r="N9" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
       <x:c r="O9" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="P9" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q9" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R9" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="S9" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:19">
       <x:c r="A10" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="I10" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="O10" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P10" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="R10" s="0" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="S10" s="0" t="s">
         <x:v>24</x:v>
@@ -1104,100 +1194,121 @@
     </x:row>
     <x:row r="11" spans="1:19">
       <x:c r="A11" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P11" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S11" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O11" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q11" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R11" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:19">
       <x:c r="A12" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N12" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="O12" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q12" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="P12" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R12" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="S12" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:19">
       <x:c r="A13" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="G13" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="L13" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="N13" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="O13" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q13" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="P13" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R13" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="S13" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:19">
       <x:c r="A14" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="E14" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F14" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
         <x:v>23</x:v>
@@ -1211,132 +1322,135 @@
     </x:row>
     <x:row r="15" spans="1:19">
       <x:c r="A15" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E15" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F15" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="P15" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S15" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="J15" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N15" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O15" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q15" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R15" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:19">
       <x:c r="A16" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P16" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S16" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="J16" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L16" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="N16" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O16" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q16" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R16" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:19">
       <x:c r="A17" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="J17" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N17" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O17" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q17" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R17" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P17" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S17" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:19">
       <x:c r="A18" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="J18" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N18" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O18" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q18" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R18" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="P18" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S18" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:19">
       <x:c r="A19" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="J19" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="N19" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="O19" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P19" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="R19" s="0" t="s">
-        <x:v>79</x:v>
       </x:c>
       <x:c r="S19" s="0" t="s">
         <x:v>24</x:v>
@@ -1344,16 +1458,16 @@
     </x:row>
     <x:row r="20" spans="1:19">
       <x:c r="A20" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
         <x:v>30</x:v>
@@ -1373,103 +1487,115 @@
     </x:row>
     <x:row r="21" spans="1:19">
       <x:c r="A21" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D21" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="J21" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="L21" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="N21" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O21" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q21" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R21" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="P21" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S21" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:19">
       <x:c r="A22" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="P22" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S22" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="J22" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N22" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O22" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q22" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R22" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:19">
       <x:c r="A23" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="E23" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="F23" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="I23" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="P23" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S23" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N23" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O23" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q23" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R23" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:19">
       <x:c r="A24" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="F24" s="0" t="s">
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="J24" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="K24" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="N24" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="O24" s="0" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="P24" s="0" t="s">
         <x:v>24</x:v>
+      </x:c>
+      <x:c r="R24" s="0" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="S24" s="0" t="s">
         <x:v>24</x:v>
@@ -1477,27 +1603,39 @@
     </x:row>
     <x:row r="25" spans="1:19">
       <x:c r="A25" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="P25" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S25" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="J25" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N25" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O25" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q25" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R25" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:19">
       <x:c r="A26" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
         <x:v>22</x:v>
@@ -1514,118 +1652,103 @@
     </x:row>
     <x:row r="27" spans="1:19">
       <x:c r="A27" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="E27" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="F27" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="P27" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S27" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="J27" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L27" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="N27" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O27" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q27" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R27" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:19">
       <x:c r="A28" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D28" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I28" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="N28" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O28" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q28" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R28" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="P28" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S28" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:19">
       <x:c r="A29" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D29" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="N29" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O29" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q29" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R29" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="J29" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="P29" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S29" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:19">
       <x:c r="A30" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="F30" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="O30" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P30" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="R30" s="0" t="s">
-        <x:v>110</x:v>
       </x:c>
       <x:c r="S30" s="0" t="s">
         <x:v>24</x:v>
@@ -1633,28 +1756,16 @@
     </x:row>
     <x:row r="31" spans="1:19">
       <x:c r="A31" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="F31" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="J31" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="O31" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P31" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="R31" s="0" t="s">
-        <x:v>110</x:v>
       </x:c>
       <x:c r="S31" s="0" t="s">
         <x:v>24</x:v>
@@ -1662,60 +1773,42 @@
     </x:row>
     <x:row r="32" spans="1:19">
       <x:c r="A32" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="E32" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="F32" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="J32" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N32" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O32" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q32" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R32" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="P32" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S32" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:19">
       <x:c r="A33" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="D33" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E33" s="0" t="s">
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="I33" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="N33" s="0" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="O33" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P33" s="0" t="s">
         <x:v>24</x:v>
@@ -1726,34 +1819,22 @@
     </x:row>
     <x:row r="34" spans="1:19">
       <x:c r="A34" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="E34" s="0" t="s">
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G34" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="I34" s="0" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="J34" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="N34" s="0" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="O34" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="P34" s="0" t="s">
         <x:v>24</x:v>
@@ -1764,56 +1845,74 @@
     </x:row>
     <x:row r="35" spans="1:19">
       <x:c r="A35" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
+      <x:c r="G35" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
       <x:c r="H35" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="J35" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N35" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O35" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q35" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R35" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="P35" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S35" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:19">
       <x:c r="A36" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="F36" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H36" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="P36" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S36" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="I36" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="N36" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O36" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q36" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R36" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:19">
       <x:c r="A37" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
         <x:v>22</x:v>
@@ -1821,91 +1920,352 @@
       <x:c r="H37" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="P37" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S37" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="I37" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="N37" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O37" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q37" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R37" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:19">
       <x:c r="A38" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="H38" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="J38" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N38" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="O38" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q38" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="P38" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R38" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="S38" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:19">
       <x:c r="A39" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="E39" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J39" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N39" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="O39" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q39" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="P39" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R39" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="S39" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:19">
       <x:c r="A40" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="E40" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="F40" s="0" t="s">
+        <x:v>142</x:v>
       </x:c>
       <x:c r="H40" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P40" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S40" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="J40" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N40" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O40" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q40" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R40" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:19">
+      <x:c r="A41" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="F41" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G41" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H41" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="I41" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="N41" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="O41" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="P41" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S41" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:19">
+      <x:c r="A42" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="F42" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G42" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H42" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="I42" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="J42" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="N42" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="O42" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="P42" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S42" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:19">
+      <x:c r="A43" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F43" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H43" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J43" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N43" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O43" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q43" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R43" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:19">
+      <x:c r="A44" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="H44" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P44" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S44" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:19">
+      <x:c r="A45" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="F45" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H45" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P45" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S45" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:19">
+      <x:c r="A46" s="0" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="F46" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H46" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="J46" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N46" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O46" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q46" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R46" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:19">
+      <x:c r="A47" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="E47" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="F47" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H47" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="J47" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N47" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O47" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q47" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R47" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:19">
+      <x:c r="A48" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="F48" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H48" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="P48" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S48" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:19">
+      <x:c r="A49" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="H49" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P49" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S49" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="164">
   <x:si>
     <x:t>EZMId</x:t>
   </x:si>
@@ -322,196 +322,184 @@
     <x:t xml:space="preserve">tst </x:t>
   </x:si>
   <x:si>
-    <x:t>E7BC-GDFQ</x:t>
+    <x:t>8540-Q7DB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>211267313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F4B8-KXPP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nab ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rananabeelahmed772@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/03/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2323232332332</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/09/2023 06:52:56 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9713-YA5L</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nimal test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AA8F-FH1K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>lets see</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2E65-SXT6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>first test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7851-Q2TO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mawaz Ejaz</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawazejaz@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>840E-CILQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel muhammad changes</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33333333</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test3333@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/02/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3A8B-SII4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>new last</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1AA1-TIH9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>carmi gandazia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3232323</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4343435435</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5544545</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A5C1-YB22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>basic web</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member,Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/15/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D1DD-IRVU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>khush hona1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>khush1@gmail.con</x:t>
+  </x:si>
+  <x:si>
+    <x:t>exteme team</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/11/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4356-V95A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>main husband</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/10/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/02/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/17/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>msin husbanfd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/08/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>043E-D109</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1D77-ED7L</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">testhshhd...1 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFA9-V8G1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test missinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBB9-PGI5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>trd test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F12A-92SY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>first name last name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5657</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz2@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEEA-YQ1Z</x:t>
   </x:si>
   <x:si>
     <x:t>margalla hill</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8540-Q7DB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>211267313</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F4B8-KXPP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nab ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rananabeelahmed772@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/03/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2323232332332</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/09/2023 06:52:56 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9713-YA5L</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nimal test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AA8F-FH1K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>lets see</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2E65-SXT6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>first test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7851-Q2TO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mawaz Ejaz</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawazejaz@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>840E-CILQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel muhammad changes</x:t>
-  </x:si>
-  <x:si>
-    <x:t>33333333</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test3333@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/02/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3A8B-SII4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>new last</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tag 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1AA1-TIH9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>carmi gandazia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3232323</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4343435435</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5544545</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A5C1-YB22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>basic web</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member,Owner nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02/15/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D1DD-IRVU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>khush hona1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>khush1@gmail.con</x:t>
-  </x:si>
-  <x:si>
-    <x:t>exteme team</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/11/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4356-V95A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>main husband</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/10/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/02/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/17/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>msin husbanfd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/08/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>043E-D109</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1D77-ED7L</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">testhshhd...1 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFA9-V8G1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test missinh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBB9-PGI5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>trd test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F12A-92SY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>first name last name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5657</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenz2@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6EB4-PR75</x:t>
-  </x:si>
-  <x:si>
-    <x:t>toyota  7hecf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3535</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12/25/2023 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
     <x:t>2B7C-80QZ</x:t>
@@ -581,8 +569,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S49" totalsRowShown="0">
-  <x:autoFilter ref="A1:S49"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S48" totalsRowShown="0">
+  <x:autoFilter ref="A1:S48"/>
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="EZMId"/>
     <x:tableColumn id="2" name="Name"/>
@@ -896,7 +884,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:S49"/>
+  <x:dimension ref="A1:S48"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -1635,19 +1623,34 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="F26" s="0" t="s">
-        <x:v>22</x:v>
+      <x:c r="G26" s="0" t="s">
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="P26" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S26" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="J26" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L26" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="N26" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O26" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q26" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R26" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:19">
@@ -1655,50 +1658,44 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D27" s="0" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="G27" s="0" t="s">
-        <x:v>42</x:v>
+      <x:c r="E27" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="F27" s="0" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="J27" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="L27" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="N27" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O27" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q27" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R27" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="P27" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S27" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:19">
       <x:c r="A28" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="B28" s="0" t="s">
+      <x:c r="F28" s="0" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="E28" s="0" t="s">
+      <x:c r="H28" s="0" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="F28" s="0" t="s">
+      <x:c r="I28" s="0" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="H28" s="0" t="s">
+      <x:c r="J28" s="0" t="s">
         <x:v>110</x:v>
       </x:c>
       <x:c r="P28" s="0" t="s">
@@ -1710,25 +1707,13 @@
     </x:row>
     <x:row r="29" spans="1:19">
       <x:c r="A29" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="E29" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="F29" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="I29" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="J29" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P29" s="0" t="s">
         <x:v>24</x:v>
@@ -1761,6 +1746,9 @@
       <x:c r="B31" s="0" t="s">
         <x:v>116</x:v>
       </x:c>
+      <x:c r="F31" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="H31" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -1778,8 +1766,14 @@
       <x:c r="B32" s="0" t="s">
         <x:v>118</x:v>
       </x:c>
+      <x:c r="E32" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
       <x:c r="F32" s="0" t="s">
         <x:v>22</x:v>
+      </x:c>
+      <x:c r="G32" s="0" t="s">
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
         <x:v>23</x:v>
@@ -1793,22 +1787,22 @@
     </x:row>
     <x:row r="33" spans="1:19">
       <x:c r="A33" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G33" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="P33" s="0" t="s">
         <x:v>24</x:v>
@@ -1819,22 +1813,25 @@
     </x:row>
     <x:row r="34" spans="1:19">
       <x:c r="A34" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
+      <x:c r="G34" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P34" s="0" t="s">
         <x:v>24</x:v>
@@ -1845,51 +1842,54 @@
     </x:row>
     <x:row r="35" spans="1:19">
       <x:c r="A35" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="E35" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G35" s="0" t="s">
-        <x:v>129</x:v>
-      </x:c>
       <x:c r="H35" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="P35" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S35" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="I35" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="N35" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O35" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q35" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R35" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:19">
       <x:c r="A36" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="D36" s="0" t="s">
+      <x:c r="F36" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H36" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="I36" s="0" t="s">
         <x:v>132</x:v>
-      </x:c>
-      <x:c r="F36" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H36" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I36" s="0" t="s">
-        <x:v>133</x:v>
       </x:c>
       <x:c r="N36" s="0" t="s">
         <x:v>30</x:v>
@@ -1906,57 +1906,54 @@
     </x:row>
     <x:row r="37" spans="1:19">
       <x:c r="A37" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="D37" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H37" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I37" s="0" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="N37" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="O37" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q37" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="P37" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R37" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="S37" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:19">
       <x:c r="A38" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="F38" s="0" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="B38" s="0" t="s">
+      <x:c r="H38" s="0" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="F38" s="0" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="H38" s="0" t="s">
-        <x:v>138</x:v>
+      <x:c r="J38" s="0" t="s">
+        <x:v>136</x:v>
       </x:c>
       <x:c r="O38" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P38" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="R38" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="S38" s="0" t="s">
         <x:v>24</x:v>
@@ -1964,74 +1961,80 @@
     </x:row>
     <x:row r="39" spans="1:19">
       <x:c r="A39" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="E39" s="0" t="s">
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="J39" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N39" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O39" s="0" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="P39" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q39" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R39" s="0" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="S39" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:19">
       <x:c r="A40" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="E40" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
+        <x:v>103</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G40" s="0" t="s">
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H40" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="I40" s="0" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="J40" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="N40" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="O40" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q40" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R40" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="P40" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S40" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:19">
       <x:c r="A41" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
         <x:v>22</x:v>
@@ -2040,16 +2043,19 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H41" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="I41" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="J41" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="N41" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="O41" s="0" t="s">
         <x:v>146</x:v>
-      </x:c>
-      <x:c r="I41" s="0" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="N41" s="0" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="O41" s="0" t="s">
-        <x:v>148</x:v>
       </x:c>
       <x:c r="P41" s="0" t="s">
         <x:v>24</x:v>
@@ -2060,69 +2066,48 @@
     </x:row>
     <x:row r="42" spans="1:19">
       <x:c r="A42" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="D42" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G42" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="H42" s="0" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="I42" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J42" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N42" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O42" s="0" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="P42" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S42" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q42" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R42" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:19">
       <x:c r="A43" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F43" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H43" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="J43" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N43" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O43" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q43" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R43" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="P43" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S43" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:19">
@@ -2132,6 +2117,9 @@
       <x:c r="B44" s="0" t="s">
         <x:v>153</x:v>
       </x:c>
+      <x:c r="F44" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="H44" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -2153,13 +2141,22 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H45" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P45" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S45" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="J45" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N45" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O45" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q45" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R45" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:19">
@@ -2169,6 +2166,12 @@
       <x:c r="B46" s="0" t="s">
         <x:v>157</x:v>
       </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="E46" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
       <x:c r="F46" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -2193,37 +2196,22 @@
     </x:row>
     <x:row r="47" spans="1:19">
       <x:c r="A47" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="D47" s="0" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="E47" s="0" t="s">
         <x:v>161</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H47" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="J47" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N47" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O47" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q47" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R47" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P47" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S47" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:19">
@@ -2233,39 +2221,13 @@
       <x:c r="B48" s="0" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="C48" s="0" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="D48" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="F48" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H48" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P48" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="S48" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:19">
-      <x:c r="A49" s="0" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="H49" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P49" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S49" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -145,6 +145,12 @@
     <x:t xml:space="preserve">tag 3 </x:t>
   </x:si>
   <x:si>
+    <x:t>6417-W0BG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>margalla hill</x:t>
+  </x:si>
+  <x:si>
     <x:t>2B13-9R2K</x:t>
   </x:si>
   <x:si>
@@ -494,12 +500,6 @@
   </x:si>
   <x:si>
     <x:t>nabeeloutsourcenz2@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEEA-YQ1Z</x:t>
-  </x:si>
-  <x:si>
-    <x:t>margalla hill</x:t>
   </x:si>
   <x:si>
     <x:t>2B7C-80QZ</x:t>
@@ -1129,55 +1129,58 @@
       <x:c r="B9" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="N9" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O9" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q9" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R9" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P9" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S9" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:19">
       <x:c r="A10" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B10" s="0" t="s">
+      <x:c r="J10" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P10" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S10" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="N10" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O10" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q10" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R10" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:19">
@@ -1187,105 +1190,81 @@
       <x:c r="B11" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N11" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O11" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q11" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P11" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S11" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:19">
       <x:c r="A12" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B12" s="0" t="s">
+      <x:c r="F12" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O12" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="P12" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q12" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R12" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="S12" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:19">
       <x:c r="A13" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="I13" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="O13" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="P13" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="R13" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="S13" s="0" t="s">
         <x:v>24</x:v>
@@ -1293,16 +1272,40 @@
     </x:row>
     <x:row r="14" spans="1:19">
       <x:c r="A14" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="J14" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H14" s="0" t="s">
-        <x:v>23</x:v>
+      <x:c r="O14" s="0" t="s">
+        <x:v>65</x:v>
       </x:c>
       <x:c r="P14" s="0" t="s">
         <x:v>24</x:v>
+      </x:c>
+      <x:c r="R14" s="0" t="s">
+        <x:v>65</x:v>
       </x:c>
       <x:c r="S14" s="0" t="s">
         <x:v>24</x:v>
@@ -1318,20 +1321,11 @@
       <x:c r="H15" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="J15" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N15" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O15" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q15" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R15" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="P15" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S15" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:19">
@@ -1341,26 +1335,11 @@
       <x:c r="B16" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="D16" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="E16" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="F16" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="G16" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="L16" s="0" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="N16" s="0" t="s">
         <x:v>30</x:v>
@@ -1377,25 +1356,43 @@
     </x:row>
     <x:row r="17" spans="1:19">
       <x:c r="A17" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H17" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="B17" s="0" t="s">
+      <x:c r="J17" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L17" s="0" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="F17" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H17" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P17" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S17" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="N17" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O17" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q17" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R17" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:19">
@@ -1406,10 +1403,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
         <x:v>23</x:v>
@@ -1423,16 +1420,16 @@
     </x:row>
     <x:row r="19" spans="1:19">
       <x:c r="A19" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="B19" s="0" t="s">
+      <x:c r="E19" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
         <x:v>82</x:v>
-      </x:c>
-      <x:c r="E19" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="F19" s="0" t="s">
-        <x:v>22</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
         <x:v>23</x:v>
@@ -1446,51 +1443,54 @@
     </x:row>
     <x:row r="20" spans="1:19">
       <x:c r="A20" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="B20" s="0" t="s">
-        <x:v>77</x:v>
+      <x:c r="E20" s="0" t="s">
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="J20" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N20" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O20" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q20" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R20" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P20" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S20" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:19">
       <x:c r="A21" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F21" s="0" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="B21" s="0" t="s">
+      <x:c r="H21" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="G21" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H21" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P21" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S21" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="J21" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N21" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O21" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q21" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R21" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:19">
@@ -1500,40 +1500,34 @@
       <x:c r="B22" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="E22" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F22" s="0" t="s">
-        <x:v>22</x:v>
+      <x:c r="G22" s="0" t="s">
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="J22" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N22" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O22" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q22" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R22" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P22" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S22" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:19">
       <x:c r="A23" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="B23" s="0" t="s">
+      <x:c r="E23" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F23" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H23" s="0" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="H23" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
         <x:v>30</x:v>
@@ -1558,64 +1552,61 @@
       <x:c r="B24" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="E24" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="F24" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="K24" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N24" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O24" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="P24" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q24" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R24" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="S24" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:19">
       <x:c r="A25" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="H25" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="J25" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="K25" s="0" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="B25" s="0" t="s">
+      <x:c r="N25" s="0" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="F25" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H25" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="J25" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N25" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="O25" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q25" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="P25" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R25" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="S25" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:19">
@@ -1623,22 +1614,16 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D26" s="0" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="G26" s="0" t="s">
-        <x:v>42</x:v>
+      <x:c r="F26" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="L26" s="0" t="s">
-        <x:v>38</x:v>
       </x:c>
       <x:c r="N26" s="0" t="s">
         <x:v>30</x:v>
@@ -1658,44 +1643,50 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="E27" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="F27" s="0" t="s">
-        <x:v>107</x:v>
+      <x:c r="G27" s="0" t="s">
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="P27" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S27" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J27" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L27" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="N27" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O27" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q27" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R27" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:19">
       <x:c r="A28" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="I28" s="0" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="J28" s="0" t="s">
         <x:v>110</x:v>
       </x:c>
       <x:c r="P28" s="0" t="s">
@@ -1707,13 +1698,25 @@
     </x:row>
     <x:row r="29" spans="1:19">
       <x:c r="A29" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="F29" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="H29" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="I29" s="0" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="B29" s="0" t="s">
+      <x:c r="J29" s="0" t="s">
         <x:v>112</x:v>
-      </x:c>
-      <x:c r="H29" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
       <x:c r="P29" s="0" t="s">
         <x:v>24</x:v>
@@ -1746,9 +1749,6 @@
       <x:c r="B31" s="0" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="F31" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H31" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -1766,14 +1766,8 @@
       <x:c r="B32" s="0" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="E32" s="0" t="s">
-        <x:v>119</x:v>
-      </x:c>
       <x:c r="F32" s="0" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="G32" s="0" t="s">
-        <x:v>47</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
         <x:v>23</x:v>
@@ -1787,22 +1781,22 @@
     </x:row>
     <x:row r="33" spans="1:19">
       <x:c r="A33" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="B33" s="0" t="s">
+      <x:c r="E33" s="0" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="D33" s="0" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="E33" s="0" t="s">
-        <x:v>123</x:v>
-      </x:c>
       <x:c r="F33" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
+      <x:c r="G33" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P33" s="0" t="s">
         <x:v>24</x:v>
@@ -1813,25 +1807,22 @@
     </x:row>
     <x:row r="34" spans="1:19">
       <x:c r="A34" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="E34" s="0" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="B34" s="0" t="s">
+      <x:c r="F34" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H34" s="0" t="s">
         <x:v>126</x:v>
-      </x:c>
-      <x:c r="D34" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="E34" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="F34" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G34" s="0" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="H34" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
       <x:c r="P34" s="0" t="s">
         <x:v>24</x:v>
@@ -1842,45 +1833,42 @@
     </x:row>
     <x:row r="35" spans="1:19">
       <x:c r="A35" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="B35" s="0" t="s">
+      <x:c r="D35" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="F35" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G35" s="0" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="F35" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H35" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="I35" s="0" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="N35" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O35" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q35" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R35" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="P35" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S35" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:19">
       <x:c r="A36" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
         <x:v>22</x:v>
@@ -1889,7 +1877,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="I36" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="N36" s="0" t="s">
         <x:v>30</x:v>
@@ -1906,54 +1894,57 @@
     </x:row>
     <x:row r="37" spans="1:19">
       <x:c r="A37" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="F37" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H37" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="I37" s="0" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="F37" s="0" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="H37" s="0" t="s">
-        <x:v>136</x:v>
+      <x:c r="N37" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O37" s="0" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="P37" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q37" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R37" s="0" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="S37" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:19">
       <x:c r="A38" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="H38" s="0" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="J38" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="O38" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="P38" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="R38" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="S38" s="0" t="s">
         <x:v>24</x:v>
@@ -1961,80 +1952,74 @@
     </x:row>
     <x:row r="39" spans="1:19">
       <x:c r="A39" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F39" s="0" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="B39" s="0" t="s">
+      <x:c r="H39" s="0" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="E39" s="0" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="F39" s="0" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="H39" s="0" t="s">
-        <x:v>141</x:v>
-      </x:c>
       <x:c r="J39" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N39" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="O39" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q39" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="P39" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R39" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="S39" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:19">
       <x:c r="A40" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="E40" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="F40" s="0" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="B40" s="0" t="s">
+      <x:c r="H40" s="0" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="D40" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="F40" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G40" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H40" s="0" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="I40" s="0" t="s">
-        <x:v>143</x:v>
+      <x:c r="J40" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N40" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O40" s="0" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="P40" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S40" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q40" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R40" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:19">
       <x:c r="A41" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
         <x:v>22</x:v>
@@ -2043,19 +2028,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H41" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="I41" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="N41" s="0" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="J41" s="0" t="s">
+      <x:c r="O41" s="0" t="s">
         <x:v>148</x:v>
-      </x:c>
-      <x:c r="N41" s="0" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="O41" s="0" t="s">
-        <x:v>146</x:v>
       </x:c>
       <x:c r="P41" s="0" t="s">
         <x:v>24</x:v>
@@ -2066,48 +2048,69 @@
     </x:row>
     <x:row r="42" spans="1:19">
       <x:c r="A42" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="F42" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G42" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H42" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="I42" s="0" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F42" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H42" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="J42" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="N42" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="O42" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q42" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R42" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="P42" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S42" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:19">
       <x:c r="A43" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F43" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H43" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="P43" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S43" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="J43" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N43" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O43" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q43" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R43" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:19">
@@ -2117,9 +2120,6 @@
       <x:c r="B44" s="0" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="F44" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H44" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -2141,22 +2141,13 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H45" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="J45" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N45" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O45" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q45" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R45" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P45" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S45" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:19">
@@ -2166,17 +2157,11 @@
       <x:c r="B46" s="0" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="D46" s="0" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="E46" s="0" t="s">
-        <x:v>159</x:v>
-      </x:c>
       <x:c r="F46" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H46" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J46" s="0" t="s">
         <x:v>30</x:v>
@@ -2196,22 +2181,37 @@
     </x:row>
     <x:row r="47" spans="1:19">
       <x:c r="A47" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="B47" s="0" t="s">
+      <x:c r="E47" s="0" t="s">
         <x:v>161</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H47" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P47" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S47" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="J47" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N47" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O47" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q47" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R47" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:19">

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="164">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
   <x:si>
     <x:t>EZMId</x:t>
   </x:si>
@@ -145,307 +145,313 @@
     <x:t xml:space="preserve">tag 3 </x:t>
   </x:si>
   <x:si>
-    <x:t>6417-W0BG</x:t>
+    <x:t>2B13-9R2K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nbaaa Efgh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0300000000000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rana44@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11/07/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teacher</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E260-TX8K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>check now</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24D9-XVJK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tes test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03/29/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1414-W44K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3540479390287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3233232</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05/24/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05/25/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3323232323</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2AE0-BA0G</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test school</x:t>
+  </x:si>
+  <x:si>
+    <x:t>252F-ASJE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tett test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D0C9-M0CQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>testm il</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70A6-XDYQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TETSTTTWT TT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>999999</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,add agent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10/05/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test sqaq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83B6-ED47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2289-PRD0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dilbar rukha</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member,Nabeel Ahmed,exteme team,Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D4C5-ZQQB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tets tet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0924-9S1L</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,arsalan team member</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/19/2001 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0F2D-MM6C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">testt </x:t>
+  </x:si>
+  <x:si>
+    <x:t>BE8D-A2NZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>reign test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09/19/1982 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FE65-MJIB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7900-P6ME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sufi cup</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/27/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/28/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5D0A-RMPK</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tst </x:t>
+  </x:si>
+  <x:si>
+    <x:t>8540-Q7DB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>211267313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F4B8-KXPP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nab ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rananabeelahmed772@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/03/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2323232332332</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/09/2023 06:52:56 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9713-YA5L</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nimal test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AA8F-FH1K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>lets see</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2E65-SXT6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>first test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7851-Q2TO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mawaz Ejaz</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawazejaz@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>840E-CILQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel muhammad changes</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33333333</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test3333@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/02/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3A8B-SII4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>new last</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1AA1-TIH9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>carmi gandazia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3232323</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4343435435</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5544545</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A5C1-YB22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>basic web</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member,Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/15/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D1DD-IRVU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>khush hona1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>khush1@gmail.con</x:t>
+  </x:si>
+  <x:si>
+    <x:t>exteme team</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/11/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1D31-N0NX</x:t>
   </x:si>
   <x:si>
     <x:t>margalla hill</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2B13-9R2K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nbaaa Efgh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0300000000000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rana44@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tag 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11/07/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Teacher</x:t>
-  </x:si>
-  <x:si>
-    <x:t>E260-TX8K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>check now</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24D9-XVJK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tes test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenz@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03/29/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1414-W44K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3540479390287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3233232</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05/24/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05/25/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3323232323</x:t>
-  </x:si>
-  <x:si>
-    <x:t>252F-ASJE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tett test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D0C9-M0CQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>testm il</x:t>
-  </x:si>
-  <x:si>
-    <x:t>70A6-XDYQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TETSTTTWT TT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>999999</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,add agent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10/05/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test sqaq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83B6-ED47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2289-PRD0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dilbar rukha</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member,Nabeel Ahmed,exteme team,Owner nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D4C5-ZQQB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tets tet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0924-9S1L</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,arsalan team member</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/19/2001 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0F2D-MM6C</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">testt </x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE8D-A2NZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>reign test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09/19/1982 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FE65-MJIB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7900-P6ME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sufi cup</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02/27/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02/28/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5D0A-RMPK</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tst </x:t>
-  </x:si>
-  <x:si>
-    <x:t>8540-Q7DB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>211267313</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F4B8-KXPP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nab ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rananabeelahmed772@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/03/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2323232332332</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/09/2023 06:52:56 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9713-YA5L</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nimal test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AA8F-FH1K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>lets see</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2E65-SXT6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>first test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7851-Q2TO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mawaz Ejaz</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawazejaz@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>840E-CILQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel muhammad changes</x:t>
-  </x:si>
-  <x:si>
-    <x:t>33333333</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test3333@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/02/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3A8B-SII4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>new last</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tag 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1AA1-TIH9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>carmi gandazia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3232323</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4343435435</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5544545</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A5C1-YB22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>basic web</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member,Owner nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02/15/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D1DD-IRVU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>khush hona1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>khush1@gmail.con</x:t>
-  </x:si>
-  <x:si>
-    <x:t>exteme team</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/11/2023 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
     <x:t>4356-V95A</x:t>
@@ -569,8 +575,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S48" totalsRowShown="0">
-  <x:autoFilter ref="A1:S48"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S49" totalsRowShown="0">
+  <x:autoFilter ref="A1:S49"/>
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="EZMId"/>
     <x:tableColumn id="2" name="Name"/>
@@ -884,7 +890,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:S48"/>
+  <x:dimension ref="A1:S49"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -1129,58 +1135,55 @@
       <x:c r="B9" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P9" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S9" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="N9" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O9" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q9" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R9" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:19">
       <x:c r="A10" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="N10" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O10" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q10" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R10" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P10" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S10" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:19">
@@ -1190,81 +1193,105 @@
       <x:c r="B11" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P11" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S11" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O11" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q11" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R11" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:19">
       <x:c r="A12" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N12" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="O12" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q12" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="P12" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R12" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="S12" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:19">
       <x:c r="A13" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B13" s="0" t="s">
+      <x:c r="D13" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="C13" s="0" t="s">
+      <x:c r="E13" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D13" s="0" t="s">
+      <x:c r="F13" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="E13" s="0" t="s">
+      <x:c r="H13" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="F13" s="0" t="s">
+      <x:c r="I13" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="H13" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="J13" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="O13" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="P13" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="R13" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="S13" s="0" t="s">
         <x:v>24</x:v>
@@ -1272,40 +1299,19 @@
     </x:row>
     <x:row r="14" spans="1:19">
       <x:c r="A14" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="E14" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F14" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="I14" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="J14" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="O14" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P14" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="R14" s="0" t="s">
-        <x:v>65</x:v>
       </x:c>
       <x:c r="S14" s="0" t="s">
         <x:v>24</x:v>
@@ -1793,7 +1799,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
         <x:v>23</x:v>
@@ -2018,26 +2024,11 @@
       <x:c r="B41" s="0" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="D41" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
       <x:c r="F41" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G41" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="H41" s="0" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="I41" s="0" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="N41" s="0" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="O41" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P41" s="0" t="s">
         <x:v>24</x:v>
@@ -2048,10 +2039,10 @@
     </x:row>
     <x:row r="42" spans="1:19">
       <x:c r="A42" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
         <x:v>105</x:v>
@@ -2063,19 +2054,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H42" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="I42" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="N42" s="0" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="J42" s="0" t="s">
+      <x:c r="O42" s="0" t="s">
         <x:v>150</x:v>
-      </x:c>
-      <x:c r="N42" s="0" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="O42" s="0" t="s">
-        <x:v>148</x:v>
       </x:c>
       <x:c r="P42" s="0" t="s">
         <x:v>24</x:v>
@@ -2086,48 +2074,69 @@
     </x:row>
     <x:row r="43" spans="1:19">
       <x:c r="A43" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="F43" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G43" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H43" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="I43" s="0" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F43" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H43" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="J43" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="N43" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="O43" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q43" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R43" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="P43" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S43" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:19">
       <x:c r="A44" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F44" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H44" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="P44" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S44" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="J44" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N44" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O44" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q44" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R44" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:19">
@@ -2137,9 +2146,6 @@
       <x:c r="B45" s="0" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="F45" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H45" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -2161,22 +2167,13 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H46" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="J46" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N46" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O46" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q46" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R46" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P46" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S46" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:19">
@@ -2186,17 +2183,11 @@
       <x:c r="B47" s="0" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="D47" s="0" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="E47" s="0" t="s">
-        <x:v>161</x:v>
-      </x:c>
       <x:c r="F47" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H47" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J47" s="0" t="s">
         <x:v>30</x:v>
@@ -2216,18 +2207,53 @@
     </x:row>
     <x:row r="48" spans="1:19">
       <x:c r="A48" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="B48" s="0" t="s">
+      <x:c r="E48" s="0" t="s">
         <x:v>163</x:v>
       </x:c>
+      <x:c r="F48" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="H48" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P48" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S48" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="J48" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N48" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O48" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q48" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R48" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:19">
+      <x:c r="A49" s="0" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="H49" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P49" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S49" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
   <x:si>
     <x:t>EZMId</x:t>
   </x:si>
@@ -217,6 +217,12 @@
     <x:t>test school</x:t>
   </x:si>
   <x:si>
+    <x:t>AC22-Z9CM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test Streich</x:t>
+  </x:si>
+  <x:si>
     <x:t>252F-ASJE</x:t>
   </x:si>
   <x:si>
@@ -448,34 +454,34 @@
     <x:t>08/11/2023 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>1D31-N0NX</x:t>
+    <x:t>4356-V95A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>main husband</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/10/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/02/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/17/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>msin husbanfd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/08/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>043E-D109</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BC40-QLMQ</x:t>
   </x:si>
   <x:si>
     <x:t>margalla hill</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4356-V95A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>main husband</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/10/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/02/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/17/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>msin husbanfd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/08/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>043E-D109</x:t>
   </x:si>
   <x:si>
     <x:t>1D77-ED7L</x:t>
@@ -575,8 +581,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S49" totalsRowShown="0">
-  <x:autoFilter ref="A1:S49"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S50" totalsRowShown="0">
+  <x:autoFilter ref="A1:S50"/>
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="EZMId"/>
     <x:tableColumn id="2" name="Name"/>
@@ -890,7 +896,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:S49"/>
+  <x:dimension ref="A1:S50"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -1344,20 +1350,11 @@
       <x:c r="H16" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="J16" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N16" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O16" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q16" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R16" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="P16" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S16" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:19">
@@ -1367,26 +1364,11 @@
       <x:c r="B17" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="D17" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F17" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="G17" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J17" s="0" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="L17" s="0" t="s">
-        <x:v>77</x:v>
       </x:c>
       <x:c r="N17" s="0" t="s">
         <x:v>30</x:v>
@@ -1403,25 +1385,43 @@
     </x:row>
     <x:row r="18" spans="1:19">
       <x:c r="A18" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H18" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B18" s="0" t="s">
+      <x:c r="J18" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L18" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="E18" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F18" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H18" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P18" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S18" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="N18" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O18" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q18" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R18" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:19">
@@ -1432,10 +1432,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
         <x:v>23</x:v>
@@ -1449,16 +1449,16 @@
     </x:row>
     <x:row r="20" spans="1:19">
       <x:c r="A20" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="B20" s="0" t="s">
+      <x:c r="E20" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F20" s="0" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="E20" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="F20" s="0" t="s">
-        <x:v>22</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
         <x:v>23</x:v>
@@ -1472,51 +1472,54 @@
     </x:row>
     <x:row r="21" spans="1:19">
       <x:c r="A21" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>79</x:v>
+      <x:c r="E21" s="0" t="s">
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="J21" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N21" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O21" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q21" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R21" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P21" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S21" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:19">
       <x:c r="A22" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F22" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="B22" s="0" t="s">
+      <x:c r="H22" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="G22" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H22" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P22" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S22" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="J22" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N22" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O22" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q22" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R22" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:19">
@@ -1526,40 +1529,34 @@
       <x:c r="B23" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="E23" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F23" s="0" t="s">
-        <x:v>22</x:v>
+      <x:c r="G23" s="0" t="s">
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="J23" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N23" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O23" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q23" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R23" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P23" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S23" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:19">
       <x:c r="A24" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="B24" s="0" t="s">
+      <x:c r="E24" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F24" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H24" s="0" t="s">
         <x:v>95</x:v>
-      </x:c>
-      <x:c r="H24" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
         <x:v>30</x:v>
@@ -1584,64 +1581,61 @@
       <x:c r="B25" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="E25" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="F25" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="K25" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N25" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O25" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="P25" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q25" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R25" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="S25" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:19">
       <x:c r="A26" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H26" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="J26" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="K26" s="0" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="B26" s="0" t="s">
+      <x:c r="N26" s="0" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="F26" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H26" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="J26" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N26" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="O26" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q26" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="P26" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R26" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="S26" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:19">
@@ -1649,22 +1643,16 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D27" s="0" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="G27" s="0" t="s">
-        <x:v>42</x:v>
+      <x:c r="F27" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="L27" s="0" t="s">
-        <x:v>38</x:v>
       </x:c>
       <x:c r="N27" s="0" t="s">
         <x:v>30</x:v>
@@ -1684,44 +1672,50 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="E28" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="F28" s="0" t="s">
-        <x:v>109</x:v>
+      <x:c r="G28" s="0" t="s">
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="P28" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S28" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J28" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L28" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="N28" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O28" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q28" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R28" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:19">
       <x:c r="A29" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="I29" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="J29" s="0" t="s">
         <x:v>112</x:v>
       </x:c>
       <x:c r="P29" s="0" t="s">
@@ -1733,13 +1727,25 @@
     </x:row>
     <x:row r="30" spans="1:19">
       <x:c r="A30" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="F30" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="H30" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="I30" s="0" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="B30" s="0" t="s">
+      <x:c r="J30" s="0" t="s">
         <x:v>114</x:v>
-      </x:c>
-      <x:c r="H30" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
       <x:c r="P30" s="0" t="s">
         <x:v>24</x:v>
@@ -1772,9 +1778,6 @@
       <x:c r="B32" s="0" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="F32" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H32" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -1792,14 +1795,8 @@
       <x:c r="B33" s="0" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="E33" s="0" t="s">
-        <x:v>121</x:v>
-      </x:c>
       <x:c r="F33" s="0" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="G33" s="0" t="s">
-        <x:v>47</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
         <x:v>23</x:v>
@@ -1813,22 +1810,22 @@
     </x:row>
     <x:row r="34" spans="1:19">
       <x:c r="A34" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="B34" s="0" t="s">
+      <x:c r="E34" s="0" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="D34" s="0" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="E34" s="0" t="s">
-        <x:v>125</x:v>
-      </x:c>
       <x:c r="F34" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
+      <x:c r="G34" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P34" s="0" t="s">
         <x:v>24</x:v>
@@ -1839,25 +1836,22 @@
     </x:row>
     <x:row r="35" spans="1:19">
       <x:c r="A35" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="B35" s="0" t="s">
+      <x:c r="F35" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H35" s="0" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="E35" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="F35" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G35" s="0" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="H35" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
       <x:c r="P35" s="0" t="s">
         <x:v>24</x:v>
@@ -1868,45 +1862,42 @@
     </x:row>
     <x:row r="36" spans="1:19">
       <x:c r="A36" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="B36" s="0" t="s">
+      <x:c r="D36" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="F36" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G36" s="0" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="D36" s="0" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="F36" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H36" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="I36" s="0" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="N36" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O36" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q36" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R36" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="P36" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S36" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:19">
       <x:c r="A37" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
         <x:v>22</x:v>
@@ -1915,7 +1906,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="I37" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="N37" s="0" t="s">
         <x:v>30</x:v>
@@ -1932,54 +1923,57 @@
     </x:row>
     <x:row r="38" spans="1:19">
       <x:c r="A38" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="F38" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H38" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="I38" s="0" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="F38" s="0" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="H38" s="0" t="s">
-        <x:v>138</x:v>
+      <x:c r="N38" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O38" s="0" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="P38" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q38" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R38" s="0" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="S38" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:19">
       <x:c r="A39" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="J39" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="O39" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="P39" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="R39" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="S39" s="0" t="s">
         <x:v>24</x:v>
@@ -1987,54 +1981,63 @@
     </x:row>
     <x:row r="40" spans="1:19">
       <x:c r="A40" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="F40" s="0" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="B40" s="0" t="s">
+      <x:c r="H40" s="0" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="E40" s="0" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="F40" s="0" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="H40" s="0" t="s">
-        <x:v>143</x:v>
-      </x:c>
       <x:c r="J40" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N40" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="O40" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q40" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="P40" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R40" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="S40" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:19">
       <x:c r="A41" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="E41" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="F41" s="0" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="B41" s="0" t="s">
+      <x:c r="H41" s="0" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="F41" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H41" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P41" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S41" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="J41" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N41" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O41" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q41" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R41" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:19">
@@ -2045,7 +2048,7 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
         <x:v>22</x:v>
@@ -2080,7 +2083,7 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
         <x:v>22</x:v>
@@ -2146,6 +2149,9 @@
       <x:c r="B45" s="0" t="s">
         <x:v>155</x:v>
       </x:c>
+      <x:c r="F45" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="H45" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -2163,9 +2169,6 @@
       <x:c r="B46" s="0" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="F46" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H46" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -2187,22 +2190,13 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H47" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="J47" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N47" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O47" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q47" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R47" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P47" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S47" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:19">
@@ -2212,12 +2206,6 @@
       <x:c r="B48" s="0" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="D48" s="0" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="E48" s="0" t="s">
-        <x:v>163</x:v>
-      </x:c>
       <x:c r="F48" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -2242,18 +2230,53 @@
     </x:row>
     <x:row r="49" spans="1:19">
       <x:c r="A49" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="B49" s="0" t="s">
+      <x:c r="E49" s="0" t="s">
         <x:v>165</x:v>
       </x:c>
+      <x:c r="F49" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="H49" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P49" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S49" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="J49" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N49" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O49" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q49" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R49" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:19">
+      <x:c r="A50" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="H50" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P50" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S50" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -118,6 +118,12 @@
     <x:t>nabeeloutsourcenz1@gmail.com</x:t>
   </x:si>
   <x:si>
+    <x:t>0246-SJS4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>margalla hill</x:t>
+  </x:si>
+  <x:si>
     <x:t>D980-Q0AX</x:t>
   </x:si>
   <x:si>
@@ -476,12 +482,6 @@
   </x:si>
   <x:si>
     <x:t>043E-D109</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BC40-QLMQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>margalla hill</x:t>
   </x:si>
   <x:si>
     <x:t>1D77-ED7L</x:t>
@@ -1063,17 +1063,11 @@
       <x:c r="B6" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P6" s="0" t="s">
         <x:v>24</x:v>
@@ -1084,13 +1078,13 @@
     </x:row>
     <x:row r="7" spans="1:19">
       <x:c r="A7" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
         <x:v>27</x:v>
@@ -1099,12 +1093,6 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="P7" s="0" t="s">
@@ -1116,16 +1104,28 @@
     </x:row>
     <x:row r="8" spans="1:19">
       <x:c r="A8" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
+      <x:c r="J8" s="0" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
       <x:c r="P8" s="0" t="s">
         <x:v>24</x:v>
@@ -1136,60 +1136,63 @@
     </x:row>
     <x:row r="9" spans="1:19">
       <x:c r="A9" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B9" s="0" t="s">
+      <x:c r="G9" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="N9" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O9" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q9" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R9" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P9" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S9" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:19">
       <x:c r="A10" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B10" s="0" t="s">
+      <x:c r="J10" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P10" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S10" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="N10" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O10" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q10" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R10" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:19">
@@ -1199,105 +1202,81 @@
       <x:c r="B11" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N11" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O11" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q11" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P11" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S11" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:19">
       <x:c r="A12" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B12" s="0" t="s">
+      <x:c r="F12" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O12" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="P12" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q12" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R12" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="S12" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:19">
       <x:c r="A13" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="I13" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="O13" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="P13" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="R13" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="S13" s="0" t="s">
         <x:v>24</x:v>
@@ -1305,19 +1284,40 @@
     </x:row>
     <x:row r="14" spans="1:19">
       <x:c r="A14" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="J14" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="G14" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H14" s="0" t="s">
-        <x:v>23</x:v>
+      <x:c r="O14" s="0" t="s">
+        <x:v>65</x:v>
       </x:c>
       <x:c r="P14" s="0" t="s">
         <x:v>24</x:v>
+      </x:c>
+      <x:c r="R14" s="0" t="s">
+        <x:v>65</x:v>
       </x:c>
       <x:c r="S14" s="0" t="s">
         <x:v>24</x:v>
@@ -1330,6 +1330,9 @@
       <x:c r="B15" s="0" t="s">
         <x:v>68</x:v>
       </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
       <x:c r="H15" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -1367,20 +1370,11 @@
       <x:c r="H17" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="J17" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N17" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O17" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q17" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R17" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="P17" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S17" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:19">
@@ -1390,26 +1384,11 @@
       <x:c r="B18" s="0" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E18" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F18" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="G18" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="L18" s="0" t="s">
-        <x:v>79</x:v>
       </x:c>
       <x:c r="N18" s="0" t="s">
         <x:v>30</x:v>
@@ -1426,25 +1405,43 @@
     </x:row>
     <x:row r="19" spans="1:19">
       <x:c r="A19" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H19" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B19" s="0" t="s">
+      <x:c r="J19" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L19" s="0" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="E19" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F19" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H19" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P19" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S19" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="N19" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O19" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q19" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R19" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:19">
@@ -1455,10 +1452,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
         <x:v>23</x:v>
@@ -1472,16 +1469,16 @@
     </x:row>
     <x:row r="21" spans="1:19">
       <x:c r="A21" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="B21" s="0" t="s">
+      <x:c r="E21" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F21" s="0" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="E21" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F21" s="0" t="s">
-        <x:v>22</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
         <x:v>23</x:v>
@@ -1495,51 +1492,54 @@
     </x:row>
     <x:row r="22" spans="1:19">
       <x:c r="A22" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>81</x:v>
+      <x:c r="E22" s="0" t="s">
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="J22" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N22" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O22" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q22" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R22" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P22" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S22" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:19">
       <x:c r="A23" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="F23" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="B23" s="0" t="s">
+      <x:c r="H23" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="G23" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H23" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P23" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S23" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="J23" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N23" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O23" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q23" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R23" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:19">
@@ -1549,40 +1549,34 @@
       <x:c r="B24" s="0" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="E24" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F24" s="0" t="s">
-        <x:v>22</x:v>
+      <x:c r="G24" s="0" t="s">
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="J24" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N24" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O24" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q24" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R24" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P24" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S24" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:19">
       <x:c r="A25" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="B25" s="0" t="s">
+      <x:c r="E25" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H25" s="0" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="H25" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
         <x:v>30</x:v>
@@ -1607,64 +1601,61 @@
       <x:c r="B26" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="E26" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F26" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="K26" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N26" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O26" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="P26" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q26" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R26" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="S26" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:19">
       <x:c r="A27" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F27" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="H27" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="J27" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="K27" s="0" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="B27" s="0" t="s">
+      <x:c r="N27" s="0" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="F27" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H27" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="J27" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N27" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="O27" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q27" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="P27" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R27" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="S27" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:19">
@@ -1672,22 +1663,16 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D28" s="0" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="G28" s="0" t="s">
-        <x:v>42</x:v>
+      <x:c r="F28" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="J28" s="0" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="L28" s="0" t="s">
-        <x:v>38</x:v>
       </x:c>
       <x:c r="N28" s="0" t="s">
         <x:v>30</x:v>
@@ -1707,44 +1692,50 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="E29" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="F29" s="0" t="s">
-        <x:v>111</x:v>
+      <x:c r="G29" s="0" t="s">
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="P29" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S29" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J29" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L29" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="N29" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O29" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q29" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R29" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:19">
       <x:c r="A30" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="I30" s="0" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="J30" s="0" t="s">
         <x:v>114</x:v>
       </x:c>
       <x:c r="P30" s="0" t="s">
@@ -1756,13 +1747,25 @@
     </x:row>
     <x:row r="31" spans="1:19">
       <x:c r="A31" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E31" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="F31" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="H31" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="I31" s="0" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="B31" s="0" t="s">
+      <x:c r="J31" s="0" t="s">
         <x:v>116</x:v>
-      </x:c>
-      <x:c r="H31" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
       <x:c r="P31" s="0" t="s">
         <x:v>24</x:v>
@@ -1795,9 +1798,6 @@
       <x:c r="B33" s="0" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="F33" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H33" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -1815,14 +1815,8 @@
       <x:c r="B34" s="0" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="E34" s="0" t="s">
-        <x:v>123</x:v>
-      </x:c>
       <x:c r="F34" s="0" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="G34" s="0" t="s">
-        <x:v>47</x:v>
       </x:c>
       <x:c r="H34" s="0" t="s">
         <x:v>23</x:v>
@@ -1836,22 +1830,22 @@
     </x:row>
     <x:row r="35" spans="1:19">
       <x:c r="A35" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="B35" s="0" t="s">
+      <x:c r="E35" s="0" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="E35" s="0" t="s">
-        <x:v>127</x:v>
-      </x:c>
       <x:c r="F35" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
+      <x:c r="G35" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P35" s="0" t="s">
         <x:v>24</x:v>
@@ -1862,25 +1856,22 @@
     </x:row>
     <x:row r="36" spans="1:19">
       <x:c r="A36" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="B36" s="0" t="s">
+      <x:c r="F36" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H36" s="0" t="s">
         <x:v>130</x:v>
-      </x:c>
-      <x:c r="D36" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="E36" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F36" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G36" s="0" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="H36" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
       <x:c r="P36" s="0" t="s">
         <x:v>24</x:v>
@@ -1891,45 +1882,42 @@
     </x:row>
     <x:row r="37" spans="1:19">
       <x:c r="A37" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="B37" s="0" t="s">
+      <x:c r="D37" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F37" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G37" s="0" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="D37" s="0" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="F37" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H37" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="I37" s="0" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="N37" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O37" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q37" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R37" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="P37" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S37" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:19">
       <x:c r="A38" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
         <x:v>22</x:v>
@@ -1938,7 +1926,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="I38" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="N38" s="0" t="s">
         <x:v>30</x:v>
@@ -1955,54 +1943,57 @@
     </x:row>
     <x:row r="39" spans="1:19">
       <x:c r="A39" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F39" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H39" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="I39" s="0" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="F39" s="0" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="H39" s="0" t="s">
-        <x:v>140</x:v>
+      <x:c r="N39" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O39" s="0" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="P39" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q39" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R39" s="0" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="S39" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:19">
       <x:c r="A40" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H40" s="0" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="J40" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="O40" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="P40" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="R40" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="S40" s="0" t="s">
         <x:v>24</x:v>
@@ -2010,101 +2001,92 @@
     </x:row>
     <x:row r="41" spans="1:19">
       <x:c r="A41" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="F41" s="0" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="B41" s="0" t="s">
+      <x:c r="H41" s="0" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="E41" s="0" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="F41" s="0" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="H41" s="0" t="s">
-        <x:v>145</x:v>
-      </x:c>
       <x:c r="J41" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N41" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="O41" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q41" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="P41" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R41" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="S41" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:19">
       <x:c r="A42" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="E42" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="F42" s="0" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="B42" s="0" t="s">
+      <x:c r="H42" s="0" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="D42" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="F42" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G42" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H42" s="0" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="I42" s="0" t="s">
-        <x:v>147</x:v>
+      <x:c r="J42" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N42" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O42" s="0" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="P42" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S42" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q42" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R42" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:19">
       <x:c r="A43" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="G43" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H43" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="I43" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="N43" s="0" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="J43" s="0" t="s">
+      <x:c r="O43" s="0" t="s">
         <x:v>152</x:v>
-      </x:c>
-      <x:c r="N43" s="0" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="O43" s="0" t="s">
-        <x:v>150</x:v>
       </x:c>
       <x:c r="P43" s="0" t="s">
         <x:v>24</x:v>
@@ -2115,39 +2097,48 @@
     </x:row>
     <x:row r="44" spans="1:19">
       <x:c r="A44" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F44" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G44" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H44" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="I44" s="0" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F44" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H44" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="J44" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="N44" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="O44" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q44" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R44" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="P44" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S44" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:19">
       <x:c r="A45" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
         <x:v>22</x:v>
@@ -2155,11 +2146,20 @@
       <x:c r="H45" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="P45" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S45" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="J45" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N45" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O45" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q45" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R45" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:19">
@@ -2210,7 +2210,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H48" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J48" s="0" t="s">
         <x:v>30</x:v>
@@ -2245,7 +2245,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H49" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J49" s="0" t="s">
         <x:v>30</x:v>

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="171">
   <x:si>
     <x:t>EZMId</x:t>
   </x:si>
@@ -118,34 +118,34 @@
     <x:t>nabeeloutsourcenz1@gmail.com</x:t>
   </x:si>
   <x:si>
-    <x:t>0246-SJS4</x:t>
+    <x:t>D980-Q0AX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel secutriy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>434434434</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/03/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/01/2023 11:20:30 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D025-AAOV</x:t>
   </x:si>
   <x:si>
     <x:t>margalla hill</x:t>
   </x:si>
   <x:si>
-    <x:t>D980-Q0AX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel secutriy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>434434434</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/03/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/01/2023 11:20:30 +00:00</x:t>
-  </x:si>
-  <x:si>
     <x:t>6F95-P7I6</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TST </x:t>
+    <x:t>TST again</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">tag 3 </x:t>
@@ -385,15 +385,6 @@
     <x:t>first test</x:t>
   </x:si>
   <x:si>
-    <x:t>7851-Q2TO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mawaz Ejaz</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawazejaz@gmail.com</x:t>
-  </x:si>
-  <x:si>
     <x:t>840E-CILQ</x:t>
   </x:si>
   <x:si>
@@ -458,6 +449,24 @@
   </x:si>
   <x:si>
     <x:t>08/11/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B5E5-C09G</x:t>
+  </x:si>
+  <x:si>
+    <x:t>finame shuja</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3535</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12/25/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test occupation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5435345</x:t>
   </x:si>
   <x:si>
     <x:t>4356-V95A</x:t>
@@ -581,8 +590,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S50" totalsRowShown="0">
-  <x:autoFilter ref="A1:S50"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S51" totalsRowShown="0">
+  <x:autoFilter ref="A1:S51"/>
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="EZMId"/>
     <x:tableColumn id="2" name="Name"/>
@@ -896,7 +905,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:S50"/>
+  <x:dimension ref="A1:S51"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -1063,11 +1072,17 @@
       <x:c r="B6" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="P6" s="0" t="s">
         <x:v>24</x:v>
@@ -1078,13 +1093,13 @@
     </x:row>
     <x:row r="7" spans="1:19">
       <x:c r="A7" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
         <x:v>36</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>38</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
         <x:v>27</x:v>
@@ -1093,6 +1108,12 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="P7" s="0" t="s">
@@ -1104,28 +1125,16 @@
     </x:row>
     <x:row r="8" spans="1:19">
       <x:c r="A8" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P8" s="0" t="s">
         <x:v>24</x:v>
@@ -1141,6 +1150,9 @@
       <x:c r="B9" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
       <x:c r="G9" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -1350,6 +1362,9 @@
       <x:c r="B16" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
       <x:c r="H16" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -1707,7 +1722,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L29" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="N29" s="0" t="s">
         <x:v>30</x:v>
@@ -1835,17 +1850,17 @@
       <x:c r="B35" s="0" t="s">
         <x:v>124</x:v>
       </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G35" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="P35" s="0" t="s">
         <x:v>24</x:v>
@@ -1856,22 +1871,25 @@
     </x:row>
     <x:row r="36" spans="1:19">
       <x:c r="A36" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
+      <x:c r="G36" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
       <x:c r="H36" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P36" s="0" t="s">
         <x:v>24</x:v>
@@ -1888,45 +1906,48 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="E37" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G37" s="0" t="s">
-        <x:v>133</x:v>
-      </x:c>
       <x:c r="H37" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="P37" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S37" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="I37" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="N37" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O37" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q37" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R37" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:19">
       <x:c r="A38" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="F38" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H38" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="I38" s="0" t="s">
         <x:v>135</x:v>
-      </x:c>
-      <x:c r="D38" s="0" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="F38" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H38" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I38" s="0" t="s">
-        <x:v>137</x:v>
       </x:c>
       <x:c r="N38" s="0" t="s">
         <x:v>30</x:v>
@@ -1943,57 +1964,54 @@
     </x:row>
     <x:row r="39" spans="1:19">
       <x:c r="A39" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I39" s="0" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="N39" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="O39" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q39" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="P39" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R39" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="S39" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:19">
       <x:c r="A40" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="F40" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H40" s="0" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="F40" s="0" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="H40" s="0" t="s">
-        <x:v>142</x:v>
+      <x:c r="J40" s="0" t="s">
+        <x:v>139</x:v>
       </x:c>
       <x:c r="O40" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="P40" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="R40" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="S40" s="0" t="s">
         <x:v>24</x:v>
@@ -2001,95 +2019,125 @@
     </x:row>
     <x:row r="41" spans="1:19">
       <x:c r="A41" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="E41" s="0" t="s">
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="H41" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="J41" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N41" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O41" s="0" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="P41" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q41" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R41" s="0" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="S41" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:19">
       <x:c r="A42" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H42" s="0" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="J42" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="K42" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="L42" s="0" t="s">
+        <x:v>149</x:v>
       </x:c>
       <x:c r="N42" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="O42" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q42" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="P42" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R42" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="S42" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:19">
       <x:c r="A43" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
         <x:v>109</x:v>
       </x:c>
+      <x:c r="E43" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
       <x:c r="F43" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G43" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="H43" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="I43" s="0" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="I43" s="0" t="s">
+      <x:c r="J43" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="K43" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="L43" s="0" t="s">
         <x:v>149</x:v>
       </x:c>
       <x:c r="N43" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="O43" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="P43" s="0" t="s">
         <x:v>24</x:v>
+      </x:c>
+      <x:c r="R43" s="0" t="s">
+        <x:v>148</x:v>
       </x:c>
       <x:c r="S43" s="0" t="s">
         <x:v>24</x:v>
@@ -2097,10 +2145,10 @@
     </x:row>
     <x:row r="44" spans="1:19">
       <x:c r="A44" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
         <x:v>109</x:v>
@@ -2112,19 +2160,16 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="H44" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I44" s="0" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="J44" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="N44" s="0" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="N44" s="0" t="s">
-        <x:v>151</x:v>
-      </x:c>
       <x:c r="O44" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="P44" s="0" t="s">
         <x:v>24</x:v>
@@ -2135,59 +2180,77 @@
     </x:row>
     <x:row r="45" spans="1:19">
       <x:c r="A45" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F45" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G45" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H45" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="I45" s="0" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="J45" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="N45" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="O45" s="0" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F45" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H45" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="J45" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N45" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O45" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q45" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R45" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="P45" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S45" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:19">
       <x:c r="A46" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F46" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H46" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="P46" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S46" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="J46" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N46" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O46" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q46" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R46" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:19">
       <x:c r="A47" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="F47" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="H47" s="0" t="s">
         <x:v>23</x:v>
@@ -2201,45 +2264,30 @@
     </x:row>
     <x:row r="48" spans="1:19">
       <x:c r="A48" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H48" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="J48" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N48" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O48" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q48" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R48" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P48" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S48" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:19">
       <x:c r="A49" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="D49" s="0" t="s">
         <x:v>164</x:v>
-      </x:c>
-      <x:c r="E49" s="0" t="s">
-        <x:v>165</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
         <x:v>22</x:v>
@@ -2265,18 +2313,53 @@
     </x:row>
     <x:row r="50" spans="1:19">
       <x:c r="A50" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="B50" s="0" t="s">
+      <x:c r="D50" s="0" t="s">
         <x:v>167</x:v>
       </x:c>
+      <x:c r="E50" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="F50" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="H50" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P50" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S50" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="J50" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N50" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O50" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q50" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R50" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:19">
+      <x:c r="A51" s="0" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="H51" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P51" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S51" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="171">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="165">
   <x:si>
     <x:t>EZMId</x:t>
   </x:si>
@@ -136,7 +136,7 @@
     <x:t>08/01/2023 11:20:30 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>D025-AAOV</x:t>
+    <x:t>CE98-EA61</x:t>
   </x:si>
   <x:si>
     <x:t>margalla hill</x:t>
@@ -449,24 +449,6 @@
   </x:si>
   <x:si>
     <x:t>08/11/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B5E5-C09G</x:t>
-  </x:si>
-  <x:si>
-    <x:t>finame shuja</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3535</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12/25/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test occupation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5435345</x:t>
   </x:si>
   <x:si>
     <x:t>4356-V95A</x:t>
@@ -590,8 +572,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S51" totalsRowShown="0">
-  <x:autoFilter ref="A1:S51"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S49" totalsRowShown="0">
+  <x:autoFilter ref="A1:S49"/>
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="EZMId"/>
     <x:tableColumn id="2" name="Name"/>
@@ -905,7 +887,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:S51"/>
+  <x:dimension ref="A1:S49"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -2056,9 +2038,6 @@
       <x:c r="B42" s="0" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="C42" s="0" t="s">
-        <x:v>147</x:v>
-      </x:c>
       <x:c r="D42" s="0" t="s">
         <x:v>109</x:v>
       </x:c>
@@ -2068,26 +2047,23 @@
       <x:c r="F42" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
+      <x:c r="G42" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
       <x:c r="H42" s="0" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="K42" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="L42" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="I42" s="0" t="s">
+        <x:v>146</x:v>
       </x:c>
       <x:c r="N42" s="0" t="s">
         <x:v>148</x:v>
       </x:c>
       <x:c r="O42" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="P42" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="R42" s="0" t="s">
-        <x:v>148</x:v>
       </x:c>
       <x:c r="S42" s="0" t="s">
         <x:v>24</x:v>
@@ -2100,9 +2076,6 @@
       <x:c r="B43" s="0" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>147</x:v>
-      </x:c>
       <x:c r="D43" s="0" t="s">
         <x:v>109</x:v>
       </x:c>
@@ -2112,32 +2085,26 @@
       <x:c r="F43" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
+      <x:c r="G43" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
       <x:c r="H43" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="I43" s="0" t="s">
         <x:v>150</x:v>
       </x:c>
       <x:c r="J43" s="0" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="K43" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="L43" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="N43" s="0" t="s">
         <x:v>148</x:v>
       </x:c>
       <x:c r="O43" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="P43" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="R43" s="0" t="s">
-        <x:v>148</x:v>
       </x:c>
       <x:c r="S43" s="0" t="s">
         <x:v>24</x:v>
@@ -2145,69 +2112,42 @@
     </x:row>
     <x:row r="44" spans="1:19">
       <x:c r="A44" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="D44" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G44" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="H44" s="0" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="I44" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J44" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N44" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O44" s="0" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="P44" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S44" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q44" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R44" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:19">
       <x:c r="A45" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="D45" s="0" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="F45" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G45" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="H45" s="0" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="I45" s="0" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="J45" s="0" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="N45" s="0" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="O45" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P45" s="0" t="s">
         <x:v>24</x:v>
@@ -2218,10 +2158,10 @@
     </x:row>
     <x:row r="46" spans="1:19">
       <x:c r="A46" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
         <x:v>22</x:v>
@@ -2229,57 +2169,75 @@
       <x:c r="H46" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="J46" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N46" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O46" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q46" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R46" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="P46" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S46" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:19">
       <x:c r="A47" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="F47" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H47" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P47" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S47" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="J47" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N47" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O47" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q47" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R47" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:19">
       <x:c r="A48" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="B48" s="0" t="s">
+      <x:c r="E48" s="0" t="s">
         <x:v>162</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H48" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P48" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S48" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="J48" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N48" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O48" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q48" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R48" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:19">
@@ -2289,77 +2247,13 @@
       <x:c r="B49" s="0" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="F49" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H49" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="J49" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N49" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O49" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q49" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R49" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:19">
-      <x:c r="A50" s="0" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="D50" s="0" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="E50" s="0" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="F50" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H50" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="J50" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N50" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O50" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q50" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R50" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:19">
-      <x:c r="A51" s="0" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="H51" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P51" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S51" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P49" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S49" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="165">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
   <x:si>
     <x:t>EZMId</x:t>
   </x:si>
@@ -136,340 +136,349 @@
     <x:t>08/01/2023 11:20:30 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>CE98-EA61</x:t>
+    <x:t>6F95-P7I6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TST again</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tag 3 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>2B13-9R2K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nbaaa Efgh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0300000000000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rana44@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11/07/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teacher</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E260-TX8K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>check now</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24D9-XVJK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tes test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03/29/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1414-W44K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3540479390287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3233232</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05/24/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05/25/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3323232323</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2AE0-BA0G</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test school</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AC22-Z9CM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test Streich</x:t>
+  </x:si>
+  <x:si>
+    <x:t>252F-ASJE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tett test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D0C9-M0CQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>testm il</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70A6-XDYQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TETSTTTWT TT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>999999</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,add agent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10/05/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test sqaq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83B6-ED47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2289-PRD0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dilbar rukha</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member,Nabeel Ahmed,exteme team,Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D4C5-ZQQB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tets tet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0924-9S1L</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,arsalan team member</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/19/2001 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0F2D-MM6C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">testt </x:t>
+  </x:si>
+  <x:si>
+    <x:t>BE8D-A2NZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>reign test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09/19/1982 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8627-1VBD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rar test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FE65-MJIB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7900-P6ME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sufi cup</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/27/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/28/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5D0A-RMPK</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tst </x:t>
+  </x:si>
+  <x:si>
+    <x:t>8540-Q7DB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>211267313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F4B8-KXPP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nab ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rananabeelahmed772@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/03/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2323232332332</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/09/2023 06:52:56 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9713-YA5L</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nimal test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AA8F-FH1K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>lets see</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2E65-SXT6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>first test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>840E-CILQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel muhammad changes</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33333333</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test3333@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/02/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3A8B-SII4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>new last</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,team member nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1AA1-TIH9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>carmi gandazia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3232323</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4343435435</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5544545</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A5C1-YB22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>basic web</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member,Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/15/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D1DD-IRVU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>khush hona1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>khush1@gmail.con</x:t>
+  </x:si>
+  <x:si>
+    <x:t>exteme team</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/11/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4356-V95A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>main husband</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/10/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/02/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/17/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>msin husbanfd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/08/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C3EC-NP7K</x:t>
   </x:si>
   <x:si>
     <x:t>margalla hill</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6F95-P7I6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TST again</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tag 3 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>2B13-9R2K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nbaaa Efgh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0300000000000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rana44@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tag 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11/07/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Teacher</x:t>
-  </x:si>
-  <x:si>
-    <x:t>E260-TX8K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>check now</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24D9-XVJK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tes test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenz@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03/29/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1414-W44K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3540479390287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3233232</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05/24/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05/25/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3323232323</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2AE0-BA0G</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test school</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AC22-Z9CM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test Streich</x:t>
-  </x:si>
-  <x:si>
-    <x:t>252F-ASJE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tett test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D0C9-M0CQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>testm il</x:t>
-  </x:si>
-  <x:si>
-    <x:t>70A6-XDYQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TETSTTTWT TT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>999999</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,add agent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10/05/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test sqaq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83B6-ED47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2289-PRD0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dilbar rukha</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member,Nabeel Ahmed,exteme team,Owner nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D4C5-ZQQB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tets tet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0924-9S1L</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,arsalan team member</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/19/2001 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0F2D-MM6C</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">testt </x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE8D-A2NZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>reign test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09/19/1982 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FE65-MJIB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7900-P6ME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sufi cup</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02/27/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02/28/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5D0A-RMPK</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tst </x:t>
-  </x:si>
-  <x:si>
-    <x:t>8540-Q7DB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>211267313</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F4B8-KXPP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nab ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rananabeelahmed772@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/03/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2323232332332</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/09/2023 06:52:56 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9713-YA5L</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nimal test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AA8F-FH1K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>lets see</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2E65-SXT6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>first test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>840E-CILQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel muhammad changes</x:t>
-  </x:si>
-  <x:si>
-    <x:t>33333333</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test3333@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/02/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3A8B-SII4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>new last</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tag 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1AA1-TIH9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>carmi gandazia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3232323</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4343435435</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5544545</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A5C1-YB22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>basic web</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member,Owner nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02/15/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D1DD-IRVU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>khush hona1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>khush1@gmail.con</x:t>
-  </x:si>
-  <x:si>
-    <x:t>exteme team</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/11/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4356-V95A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>main husband</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/10/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/02/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/17/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>msin husbanfd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/08/2023 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
     <x:t>043E-D109</x:t>
@@ -572,8 +581,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S49" totalsRowShown="0">
-  <x:autoFilter ref="A1:S49"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S50" totalsRowShown="0">
+  <x:autoFilter ref="A1:S50"/>
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="EZMId"/>
     <x:tableColumn id="2" name="Name"/>
@@ -887,7 +896,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:S49"/>
+  <x:dimension ref="A1:S50"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -1112,8 +1121,11 @@
       <x:c r="B8" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>22</x:v>
+      <x:c r="E8" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>23</x:v>
@@ -1127,66 +1139,60 @@
     </x:row>
     <x:row r="9" spans="1:19">
       <x:c r="A9" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P9" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S9" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="N9" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O9" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q9" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R9" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:19">
       <x:c r="A10" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="N10" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O10" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q10" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R10" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P10" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S10" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:19">
@@ -1196,81 +1202,105 @@
       <x:c r="B11" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P11" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S11" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O11" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q11" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R11" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:19">
       <x:c r="A12" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N12" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="O12" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q12" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="P12" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R12" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="S12" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:19">
       <x:c r="A13" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B13" s="0" t="s">
+      <x:c r="D13" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="C13" s="0" t="s">
+      <x:c r="E13" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D13" s="0" t="s">
+      <x:c r="F13" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="E13" s="0" t="s">
+      <x:c r="H13" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="F13" s="0" t="s">
+      <x:c r="I13" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="H13" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="J13" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="O13" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="P13" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="R13" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="S13" s="0" t="s">
         <x:v>24</x:v>
@@ -1278,40 +1308,19 @@
     </x:row>
     <x:row r="14" spans="1:19">
       <x:c r="A14" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="E14" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F14" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="I14" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="J14" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="O14" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P14" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="R14" s="0" t="s">
-        <x:v>65</x:v>
       </x:c>
       <x:c r="S14" s="0" t="s">
         <x:v>24</x:v>
@@ -1324,8 +1333,8 @@
       <x:c r="B15" s="0" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="G15" s="0" t="s">
-        <x:v>44</x:v>
+      <x:c r="E15" s="0" t="s">
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
         <x:v>23</x:v>
@@ -1344,9 +1353,6 @@
       <x:c r="B16" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="E16" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="H16" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -1367,11 +1373,20 @@
       <x:c r="H17" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="P17" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S17" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="J17" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N17" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O17" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q17" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R17" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:19">
@@ -1381,11 +1396,26 @@
       <x:c r="B18" s="0" t="s">
         <x:v>74</x:v>
       </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
         <x:v>30</x:v>
+      </x:c>
+      <x:c r="L18" s="0" t="s">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="N18" s="0" t="s">
         <x:v>30</x:v>
@@ -1402,43 +1432,25 @@
     </x:row>
     <x:row r="19" spans="1:19">
       <x:c r="A19" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="D19" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="E19" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="G19" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="J19" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="L19" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="N19" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O19" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q19" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R19" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P19" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S19" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:19">
@@ -1449,10 +1461,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
         <x:v>23</x:v>
@@ -1466,16 +1478,16 @@
     </x:row>
     <x:row r="21" spans="1:19">
       <x:c r="A21" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
         <x:v>23</x:v>
@@ -1489,54 +1501,51 @@
     </x:row>
     <x:row r="22" spans="1:19">
       <x:c r="A22" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="E22" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F22" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="F22" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P22" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S22" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="J22" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N22" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O22" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q22" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R22" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:19">
       <x:c r="A23" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="F23" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G23" s="0" t="s">
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="J23" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N23" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O23" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q23" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R23" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P23" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S23" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:19">
@@ -1546,49 +1555,52 @@
       <x:c r="B24" s="0" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="G24" s="0" t="s">
-        <x:v>44</x:v>
+      <x:c r="E24" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F24" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P24" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S24" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J24" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N24" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O24" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q24" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R24" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:19">
       <x:c r="A25" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="J25" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N25" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O25" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q25" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R25" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P25" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S25" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:19">
@@ -1625,7 +1637,7 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
         <x:v>102</x:v>
@@ -1689,13 +1701,13 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
         <x:v>109</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
         <x:v>23</x:v>
@@ -1862,13 +1874,13 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="H36" s="0" t="s">
         <x:v>23</x:v>
@@ -1882,13 +1894,13 @@
     </x:row>
     <x:row r="37" spans="1:19">
       <x:c r="A37" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
         <x:v>22</x:v>
@@ -1897,7 +1909,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="I37" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="N37" s="0" t="s">
         <x:v>30</x:v>
@@ -1914,13 +1926,13 @@
     </x:row>
     <x:row r="38" spans="1:19">
       <x:c r="A38" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
         <x:v>22</x:v>
@@ -1929,7 +1941,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="I38" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="N38" s="0" t="s">
         <x:v>30</x:v>
@@ -1946,25 +1958,25 @@
     </x:row>
     <x:row r="39" spans="1:19">
       <x:c r="A39" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="O39" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="P39" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="R39" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="S39" s="0" t="s">
         <x:v>24</x:v>
@@ -1972,28 +1984,28 @@
     </x:row>
     <x:row r="40" spans="1:19">
       <x:c r="A40" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="H40" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J40" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="O40" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="P40" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="R40" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="S40" s="0" t="s">
         <x:v>24</x:v>
@@ -2001,19 +2013,19 @@
     </x:row>
     <x:row r="41" spans="1:19">
       <x:c r="A41" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="H41" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="J41" s="0" t="s">
         <x:v>30</x:v>
@@ -2033,10 +2045,10 @@
     </x:row>
     <x:row r="42" spans="1:19">
       <x:c r="A42" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
         <x:v>109</x:v>
@@ -2048,19 +2060,19 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="G42" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H42" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="I42" s="0" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="I42" s="0" t="s">
-        <x:v>146</x:v>
-      </x:c>
       <x:c r="N42" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="O42" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="P42" s="0" t="s">
         <x:v>24</x:v>
@@ -2071,10 +2083,10 @@
     </x:row>
     <x:row r="43" spans="1:19">
       <x:c r="A43" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
         <x:v>109</x:v>
@@ -2086,22 +2098,22 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="G43" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H43" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="I43" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="J43" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="N43" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="O43" s="0" t="s">
         <x:v>150</x:v>
-      </x:c>
-      <x:c r="J43" s="0" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="N43" s="0" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="O43" s="0" t="s">
-        <x:v>149</x:v>
       </x:c>
       <x:c r="P43" s="0" t="s">
         <x:v>24</x:v>
@@ -2112,10 +2124,10 @@
     </x:row>
     <x:row r="44" spans="1:19">
       <x:c r="A44" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
         <x:v>22</x:v>
@@ -2123,48 +2135,48 @@
       <x:c r="H44" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="J44" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N44" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O44" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q44" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R44" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="P44" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S44" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:19">
       <x:c r="A45" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F45" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H45" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="P45" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S45" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="J45" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N45" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O45" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q45" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R45" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:19">
       <x:c r="A46" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="F46" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="H46" s="0" t="s">
         <x:v>23</x:v>
@@ -2178,51 +2190,36 @@
     </x:row>
     <x:row r="47" spans="1:19">
       <x:c r="A47" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H47" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="J47" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N47" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O47" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q47" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R47" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P47" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S47" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:19">
       <x:c r="A48" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="D48" s="0" t="s">
         <x:v>161</x:v>
-      </x:c>
-      <x:c r="E48" s="0" t="s">
-        <x:v>162</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H48" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J48" s="0" t="s">
         <x:v>30</x:v>
@@ -2242,18 +2239,53 @@
     </x:row>
     <x:row r="49" spans="1:19">
       <x:c r="A49" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="B49" s="0" t="s">
+      <x:c r="D49" s="0" t="s">
         <x:v>164</x:v>
       </x:c>
+      <x:c r="E49" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="F49" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="H49" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P49" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S49" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="J49" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N49" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O49" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q49" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R49" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:19">
+      <x:c r="A50" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="H50" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P50" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S50" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="176">
   <x:si>
     <x:t>EZMId</x:t>
   </x:si>
@@ -91,6 +91,12 @@
     <x:t xml:space="preserve">                                                                                                    </x:t>
   </x:si>
   <x:si>
+    <x:t>0A29-OCUQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>amjad ali</x:t>
+  </x:si>
+  <x:si>
     <x:t>331F-46PG</x:t>
   </x:si>
   <x:si>
@@ -145,6 +151,12 @@
     <x:t xml:space="preserve">tag 3 </x:t>
   </x:si>
   <x:si>
+    <x:t>4786-GNA5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>margalla hill</x:t>
+  </x:si>
+  <x:si>
     <x:t>2B13-9R2K</x:t>
   </x:si>
   <x:si>
@@ -475,12 +487,6 @@
     <x:t>08/08/2023 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>C3EC-NP7K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>margalla hill</x:t>
-  </x:si>
-  <x:si>
     <x:t>043E-D109</x:t>
   </x:si>
   <x:si>
@@ -488,6 +494,24 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">testhshhd...1 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>331E-Z1J3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>finame shuja</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3535</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12/25/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test occupation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5435345</x:t>
   </x:si>
   <x:si>
     <x:t>AFA9-V8G1</x:t>
@@ -581,8 +605,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S50" totalsRowShown="0">
-  <x:autoFilter ref="A1:S50"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S53" totalsRowShown="0">
+  <x:autoFilter ref="A1:S53"/>
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="EZMId"/>
     <x:tableColumn id="2" name="Name"/>
@@ -896,7 +920,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:S50"/>
+  <x:dimension ref="A1:S53"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -988,9 +1012,6 @@
       <x:c r="B3" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -1006,9 +1027,12 @@
     </x:row>
     <x:row r="4" spans="1:19">
       <x:c r="A4" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
+      <x:c r="E4" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
@@ -1017,63 +1041,57 @@
       <x:c r="H4" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O4" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q4" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R4" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="P4" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S4" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:19">
       <x:c r="A5" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="P5" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S5" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="J5" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="N5" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="O5" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="Q5" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="R5" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:19">
       <x:c r="A6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
+      <x:c r="E6" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P6" s="0" t="s">
         <x:v>24</x:v>
@@ -1084,27 +1102,21 @@
     </x:row>
     <x:row r="7" spans="1:19">
       <x:c r="A7" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="P7" s="0" t="s">
@@ -1116,19 +1128,28 @@
     </x:row>
     <x:row r="8" spans="1:19">
       <x:c r="A8" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
+      <x:c r="J8" s="0" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
       <x:c r="P8" s="0" t="s">
         <x:v>24</x:v>
@@ -1139,51 +1160,36 @@
     </x:row>
     <x:row r="9" spans="1:19">
       <x:c r="A9" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B9" s="0" t="s">
+      <x:c r="E9" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="N9" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O9" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q9" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R9" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P9" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S9" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:19">
       <x:c r="A10" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>23</x:v>
@@ -1197,69 +1203,57 @@
     </x:row>
     <x:row r="11" spans="1:19">
       <x:c r="A11" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B11" s="0" t="s">
+      <x:c r="J11" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="L11" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="N11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="O11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="Q11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="R11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:19">
       <x:c r="A12" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="J12" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="O12" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P12" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="R12" s="0" t="s">
-        <x:v>63</x:v>
       </x:c>
       <x:c r="S12" s="0" t="s">
         <x:v>24</x:v>
@@ -1272,55 +1266,64 @@
       <x:c r="B13" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="C13" s="0" t="s">
+      <x:c r="E13" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="D13" s="0" t="s">
+      <x:c r="F13" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F13" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="H13" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="I13" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="N13" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
       <x:c r="O13" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="P13" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="Q13" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
       <x:c r="R13" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="S13" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:19">
       <x:c r="A14" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B14" s="0" t="s">
+      <x:c r="H14" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G14" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H14" s="0" t="s">
-        <x:v>23</x:v>
+      <x:c r="J14" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="O14" s="0" t="s">
+        <x:v>67</x:v>
       </x:c>
       <x:c r="P14" s="0" t="s">
         <x:v>24</x:v>
+      </x:c>
+      <x:c r="R14" s="0" t="s">
+        <x:v>67</x:v>
       </x:c>
       <x:c r="S14" s="0" t="s">
         <x:v>24</x:v>
@@ -1328,19 +1331,40 @@
     </x:row>
     <x:row r="15" spans="1:19">
       <x:c r="A15" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="J15" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="E15" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H15" s="0" t="s">
-        <x:v>23</x:v>
+      <x:c r="O15" s="0" t="s">
+        <x:v>67</x:v>
       </x:c>
       <x:c r="P15" s="0" t="s">
         <x:v>24</x:v>
+      </x:c>
+      <x:c r="R15" s="0" t="s">
+        <x:v>67</x:v>
       </x:c>
       <x:c r="S15" s="0" t="s">
         <x:v>24</x:v>
@@ -1353,6 +1377,9 @@
       <x:c r="B16" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
+      <x:c r="G16" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
       <x:c r="H16" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -1370,23 +1397,17 @@
       <x:c r="B17" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
       <x:c r="H17" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="J17" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N17" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O17" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q17" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R17" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="P17" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S17" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:19">
@@ -1396,95 +1417,92 @@
       <x:c r="B18" s="0" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E18" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F18" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="G18" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="J18" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="L18" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="N18" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O18" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q18" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R18" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P18" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S18" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:19">
       <x:c r="A19" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="E19" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="F19" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H19" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="P19" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S19" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="J19" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="N19" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="O19" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="Q19" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="R19" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:19">
       <x:c r="A20" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F20" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H20" s="0" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="B20" s="0" t="s">
+      <x:c r="J20" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="L20" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="E20" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F20" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="H20" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P20" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S20" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="N20" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="O20" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="Q20" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="R20" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:19">
       <x:c r="A21" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
         <x:v>22</x:v>
@@ -1501,42 +1519,39 @@
     </x:row>
     <x:row r="22" spans="1:19">
       <x:c r="A22" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F22" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="F22" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="J22" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N22" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O22" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q22" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R22" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P22" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S22" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:19">
       <x:c r="A23" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E23" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="B23" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="G23" s="0" t="s">
-        <x:v>42</x:v>
+      <x:c r="F23" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
         <x:v>23</x:v>
@@ -1550,48 +1565,42 @@
     </x:row>
     <x:row r="24" spans="1:19">
       <x:c r="A24" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="F24" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="B24" s="0" t="s">
+      <x:c r="H24" s="0" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="E24" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F24" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H24" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
       <x:c r="J24" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="N24" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="O24" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="Q24" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="R24" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:19">
       <x:c r="A25" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="E25" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F25" s="0" t="s">
-        <x:v>22</x:v>
+      <x:c r="G25" s="0" t="s">
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
         <x:v>23</x:v>
@@ -1605,28 +1614,34 @@
     </x:row>
     <x:row r="26" spans="1:19">
       <x:c r="A26" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="B26" s="0" t="s">
+      <x:c r="E26" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H26" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="H26" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="J26" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="N26" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="O26" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="Q26" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="R26" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:19">
@@ -1637,31 +1652,16 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="J27" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="K27" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="N27" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="O27" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P27" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="R27" s="0" t="s">
-        <x:v>103</x:v>
       </x:c>
       <x:c r="S27" s="0" t="s">
         <x:v>24</x:v>
@@ -1669,66 +1669,66 @@
     </x:row>
     <x:row r="28" spans="1:19">
       <x:c r="A28" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="F28" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="J28" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="N28" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="O28" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="Q28" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="R28" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:19">
       <x:c r="A29" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F29" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="H29" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="J29" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="K29" s="0" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D29" s="0" t="s">
+      <x:c r="N29" s="0" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="G29" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H29" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="J29" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="L29" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="N29" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="O29" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q29" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="P29" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R29" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="S29" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:19">
@@ -1738,60 +1738,78 @@
       <x:c r="B30" s="0" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="E30" s="0" t="s">
-        <x:v>112</x:v>
-      </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="P30" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S30" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J30" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="N30" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="O30" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="Q30" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="R30" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:19">
       <x:c r="A31" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E31" s="0" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="F31" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
         <x:v>113</x:v>
       </x:c>
+      <x:c r="G31" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="I31" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J31" s="0" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="P31" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S31" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="L31" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="N31" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="O31" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="Q31" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="R31" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:19">
       <x:c r="A32" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E32" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="F32" s="0" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="B32" s="0" t="s">
+      <x:c r="H32" s="0" t="s">
         <x:v>118</x:v>
-      </x:c>
-      <x:c r="H32" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
       <x:c r="P32" s="0" t="s">
         <x:v>24</x:v>
@@ -1802,13 +1820,25 @@
     </x:row>
     <x:row r="33" spans="1:19">
       <x:c r="A33" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E33" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="F33" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="H33" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="I33" s="0" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="B33" s="0" t="s">
+      <x:c r="J33" s="0" t="s">
         <x:v>120</x:v>
-      </x:c>
-      <x:c r="H33" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
       <x:c r="P33" s="0" t="s">
         <x:v>24</x:v>
@@ -1824,9 +1854,6 @@
       <x:c r="B34" s="0" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="F34" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H34" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -1844,17 +1871,8 @@
       <x:c r="B35" s="0" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="E35" s="0" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="F35" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P35" s="0" t="s">
         <x:v>24</x:v>
@@ -1865,22 +1883,13 @@
     </x:row>
     <x:row r="36" spans="1:19">
       <x:c r="A36" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="D36" s="0" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="E36" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="G36" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H36" s="0" t="s">
         <x:v>23</x:v>
@@ -1894,34 +1903,28 @@
     </x:row>
     <x:row r="37" spans="1:19">
       <x:c r="A37" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H37" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I37" s="0" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="N37" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O37" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q37" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R37" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="P37" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S37" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:19">
@@ -1932,83 +1935,89 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="E38" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F38" s="0" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="F38" s="0" t="s">
-        <x:v>22</x:v>
+      <x:c r="G38" s="0" t="s">
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H38" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="I38" s="0" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="N38" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O38" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q38" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R38" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="P38" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S38" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:19">
       <x:c r="A39" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="B39" s="0" t="s">
+      <x:c r="D39" s="0" t="s">
         <x:v>138</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H39" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="I39" s="0" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="H39" s="0" t="s">
-        <x:v>140</x:v>
+      <x:c r="N39" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
       <x:c r="O39" s="0" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="P39" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="Q39" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
       <x:c r="R39" s="0" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="S39" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:19">
       <x:c r="A40" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="B40" s="0" t="s">
+      <x:c r="D40" s="0" t="s">
         <x:v>138</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H40" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="I40" s="0" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="J40" s="0" t="s">
-        <x:v>140</x:v>
+      <x:c r="N40" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
       <x:c r="O40" s="0" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="P40" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="Q40" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
       <x:c r="R40" s="0" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="S40" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:19">
@@ -2018,64 +2027,49 @@
       <x:c r="B41" s="0" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="E41" s="0" t="s">
+      <x:c r="F41" s="0" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="F41" s="0" t="s">
+      <x:c r="H41" s="0" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="H41" s="0" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="J41" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N41" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="O41" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q41" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="P41" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R41" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="S41" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:19">
       <x:c r="A42" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="D42" s="0" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="E42" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G42" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="H42" s="0" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="I42" s="0" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="N42" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="J42" s="0" t="s">
+        <x:v>144</x:v>
       </x:c>
       <x:c r="O42" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="P42" s="0" t="s">
         <x:v>24</x:v>
+      </x:c>
+      <x:c r="R42" s="0" t="s">
+        <x:v>144</x:v>
       </x:c>
       <x:c r="S42" s="0" t="s">
         <x:v>24</x:v>
@@ -2083,57 +2077,66 @@
     </x:row>
     <x:row r="43" spans="1:19">
       <x:c r="A43" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="B43" s="0" t="s">
+      <x:c r="E43" s="0" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="D43" s="0" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="E43" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G43" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="H43" s="0" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="I43" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="J43" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="N43" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="O43" s="0" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="P43" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S43" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="Q43" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="R43" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:19">
       <x:c r="A44" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="E44" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F44" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G44" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H44" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="I44" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="N44" s="0" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="B44" s="0" t="s">
+      <x:c r="O44" s="0" t="s">
         <x:v>154</x:v>
-      </x:c>
-      <x:c r="F44" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H44" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
       <x:c r="P44" s="0" t="s">
         <x:v>24</x:v>
@@ -2144,48 +2147,72 @@
     </x:row>
     <x:row r="45" spans="1:19">
       <x:c r="A45" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="E45" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F45" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G45" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H45" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="I45" s="0" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F45" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H45" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="J45" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="N45" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="O45" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q45" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R45" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="P45" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S45" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:19">
       <x:c r="A46" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F46" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H46" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="P46" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S46" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="J46" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="N46" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="O46" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="Q46" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="R46" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:19">
@@ -2195,9 +2222,6 @@
       <x:c r="B47" s="0" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="F47" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H47" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -2215,61 +2239,91 @@
       <x:c r="B48" s="0" t="s">
         <x:v>161</x:v>
       </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="E48" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
       <x:c r="F48" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H48" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="J48" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="K48" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L48" s="0" t="s">
+        <x:v>164</x:v>
       </x:c>
       <x:c r="N48" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="O48" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q48" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="P48" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R48" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="S48" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:19">
       <x:c r="A49" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="B49" s="0" t="s">
+      <x:c r="D49" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="E49" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F49" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H49" s="0" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="D49" s="0" t="s">
+      <x:c r="I49" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="J49" s="0" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="K49" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L49" s="0" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="E49" s="0" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="F49" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H49" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="J49" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="N49" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="O49" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q49" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="P49" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R49" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="S49" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:19">
@@ -2279,6 +2333,9 @@
       <x:c r="B50" s="0" t="s">
         <x:v>167</x:v>
       </x:c>
+      <x:c r="F50" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="H50" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -2286,6 +2343,87 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="S50" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:19">
+      <x:c r="A51" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="F51" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H51" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J51" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="N51" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="O51" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="Q51" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="R51" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:19">
+      <x:c r="A52" s="0" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D52" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="E52" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="F52" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H52" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J52" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="N52" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="O52" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="Q52" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="R52" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:19">
+      <x:c r="A53" s="0" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="H53" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P53" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S53" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -91,12 +91,6 @@
     <x:t xml:space="preserve">                                                                                                    </x:t>
   </x:si>
   <x:si>
-    <x:t>0A29-OCUQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>amjad ali</x:t>
-  </x:si>
-  <x:si>
     <x:t>331F-46PG</x:t>
   </x:si>
   <x:si>
@@ -151,183 +145,210 @@
     <x:t xml:space="preserve">tag 3 </x:t>
   </x:si>
   <x:si>
-    <x:t>4786-GNA5</x:t>
+    <x:t>2B13-9R2K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nbaaa Efgh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0300000000000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rana44@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11/07/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teacher</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E260-TX8K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>check now</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24D9-XVJK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tes test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03/29/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1414-W44K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3540479390287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3233232</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05/24/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05/25/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3323232323</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2AE0-BA0G</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test school</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AC22-Z9CM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test Streich</x:t>
+  </x:si>
+  <x:si>
+    <x:t>252F-ASJE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tett test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8BD9-RHPZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>finame shuja</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3535</x:t>
+  </x:si>
+  <x:si>
+    <x:t>211267313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12/25/2024 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test occupation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5435345</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4395-EYPH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arif lohar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D0C9-M0CQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>testm il</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70A6-XDYQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TETSTTTWT TT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>999999</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,add agent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10/05/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test sqaq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83B6-ED47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2289-PRD0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dilbar rukha</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member,Nabeel Ahmed,exteme team,Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D4C5-ZQQB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tets tet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0924-9S1L</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,arsalan team member</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/19/2001 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0F2D-MM6C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">testt </x:t>
+  </x:si>
+  <x:si>
+    <x:t>BE8D-A2NZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>reign test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09/19/1982 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8627-1VBD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rar test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FE65-MJIB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A962-ZCE3</x:t>
   </x:si>
   <x:si>
     <x:t>margalla hill</x:t>
   </x:si>
   <x:si>
-    <x:t>2B13-9R2K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nbaaa Efgh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0300000000000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rana44@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tag 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11/07/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Teacher</x:t>
-  </x:si>
-  <x:si>
-    <x:t>E260-TX8K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>check now</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24D9-XVJK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tes test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenz@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03/29/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1414-W44K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3540479390287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3233232</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05/24/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05/25/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3323232323</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2AE0-BA0G</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test school</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AC22-Z9CM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test Streich</x:t>
-  </x:si>
-  <x:si>
-    <x:t>252F-ASJE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tett test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D0C9-M0CQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>testm il</x:t>
-  </x:si>
-  <x:si>
-    <x:t>70A6-XDYQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TETSTTTWT TT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>999999</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,add agent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10/05/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test sqaq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83B6-ED47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2289-PRD0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dilbar rukha</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member,Nabeel Ahmed,exteme team,Owner nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D4C5-ZQQB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tets tet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0924-9S1L</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,arsalan team member</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/19/2001 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0F2D-MM6C</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">testt </x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE8D-A2NZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>reign test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09/19/1982 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8627-1VBD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rar test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FE65-MJIB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test nabeel</x:t>
-  </x:si>
-  <x:si>
     <x:t>7900-P6ME</x:t>
   </x:si>
   <x:si>
@@ -355,9 +376,6 @@
     <x:t>8540-Q7DB</x:t>
   </x:si>
   <x:si>
-    <x:t>211267313</x:t>
-  </x:si>
-  <x:si>
     <x:t>F4B8-KXPP</x:t>
   </x:si>
   <x:si>
@@ -494,24 +512,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">testhshhd...1 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>331E-Z1J3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>finame shuja</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3535</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12/25/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test occupation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5435345</x:t>
   </x:si>
   <x:si>
     <x:t>AFA9-V8G1</x:t>
@@ -1012,6 +1012,9 @@
       <x:c r="B3" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -1027,12 +1030,9 @@
     </x:row>
     <x:row r="4" spans="1:19">
       <x:c r="A4" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
@@ -1041,19 +1041,31 @@
       <x:c r="H4" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="P4" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S4" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="J4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R4" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:19">
       <x:c r="A5" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>22</x:v>
@@ -1061,37 +1073,31 @@
       <x:c r="H5" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="N5" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="O5" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="Q5" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="R5" s="0" t="s">
-        <x:v>32</x:v>
+      <x:c r="P5" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S5" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:19">
       <x:c r="A6" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="P6" s="0" t="s">
         <x:v>24</x:v>
@@ -1102,21 +1108,27 @@
     </x:row>
     <x:row r="7" spans="1:19">
       <x:c r="A7" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
+      <x:c r="E7" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="D7" s="0" t="s">
+      <x:c r="I7" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
+      <x:c r="J7" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="P7" s="0" t="s">
@@ -1128,28 +1140,19 @@
     </x:row>
     <x:row r="8" spans="1:19">
       <x:c r="A8" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P8" s="0" t="s">
         <x:v>24</x:v>
@@ -1160,36 +1163,51 @@
     </x:row>
     <x:row r="9" spans="1:19">
       <x:c r="A9" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P9" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S9" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="N9" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O9" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q9" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R9" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:19">
       <x:c r="A10" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>23</x:v>
@@ -1203,57 +1221,69 @@
     </x:row>
     <x:row r="11" spans="1:19">
       <x:c r="A11" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="L11" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="Q11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:19">
       <x:c r="A12" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="O12" s="0" t="s">
+        <x:v>63</x:v>
       </x:c>
       <x:c r="P12" s="0" t="s">
         <x:v>24</x:v>
+      </x:c>
+      <x:c r="R12" s="0" t="s">
+        <x:v>63</x:v>
       </x:c>
       <x:c r="S12" s="0" t="s">
         <x:v>24</x:v>
@@ -1266,64 +1296,55 @@
       <x:c r="B13" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="N13" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="O13" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="Q13" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="P13" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R13" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="S13" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:19">
       <x:c r="A14" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="E14" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F14" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="J14" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="O14" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P14" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="R14" s="0" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="S14" s="0" t="s">
         <x:v>24</x:v>
@@ -1331,40 +1352,19 @@
     </x:row>
     <x:row r="15" spans="1:19">
       <x:c r="A15" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F15" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="I15" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="J15" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="O15" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P15" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="R15" s="0" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="S15" s="0" t="s">
         <x:v>24</x:v>
@@ -1377,9 +1377,6 @@
       <x:c r="B16" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="G16" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="H16" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -1397,14 +1394,38 @@
       <x:c r="B17" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="K17" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="L17" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="N17" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="O17" s="0" t="s">
+        <x:v>75</x:v>
       </x:c>
       <x:c r="P17" s="0" t="s">
         <x:v>24</x:v>
+      </x:c>
+      <x:c r="R17" s="0" t="s">
+        <x:v>75</x:v>
       </x:c>
       <x:c r="S17" s="0" t="s">
         <x:v>24</x:v>
@@ -1412,16 +1433,49 @@
     </x:row>
     <x:row r="18" spans="1:19">
       <x:c r="A18" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="B18" s="0" t="s">
+      <x:c r="D18" s="0" t="s">
         <x:v>74</x:v>
       </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="I18" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="J18" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="K18" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="L18" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="N18" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="O18" s="0" t="s">
+        <x:v>75</x:v>
       </x:c>
       <x:c r="P18" s="0" t="s">
         <x:v>24</x:v>
+      </x:c>
+      <x:c r="R18" s="0" t="s">
+        <x:v>75</x:v>
       </x:c>
       <x:c r="S18" s="0" t="s">
         <x:v>24</x:v>
@@ -1429,106 +1483,103 @@
     </x:row>
     <x:row r="19" spans="1:19">
       <x:c r="A19" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="J19" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="N19" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="O19" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="Q19" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="R19" s="0" t="s">
-        <x:v>32</x:v>
+      <x:c r="P19" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S19" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:19">
       <x:c r="A20" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D20" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="E20" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="F20" s="0" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="G20" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="L20" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N20" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O20" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="Q20" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R20" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:19">
       <x:c r="A21" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="B21" s="0" t="s">
+      <x:c r="E21" s="0" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="E21" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G21" s="0" t="s">
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P21" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S21" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="J21" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L21" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="N21" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O21" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q21" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R21" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:19">
       <x:c r="A22" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
         <x:v>23</x:v>
@@ -1542,16 +1593,16 @@
     </x:row>
     <x:row r="23" spans="1:19">
       <x:c r="A23" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
         <x:v>23</x:v>
@@ -1565,297 +1616,294 @@
     </x:row>
     <x:row r="24" spans="1:19">
       <x:c r="A24" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="J24" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="N24" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="O24" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="Q24" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="R24" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P24" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S24" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:19">
       <x:c r="A25" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="G25" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P25" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S25" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="J25" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N25" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O25" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q25" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R25" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:19">
       <x:c r="A26" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="E26" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F26" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="G26" s="0" t="s">
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="J26" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="N26" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="O26" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="Q26" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="R26" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P26" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S26" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:19">
       <x:c r="A27" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P27" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S27" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="J27" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N27" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O27" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q27" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R27" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:19">
       <x:c r="A28" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F28" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="J28" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="N28" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="O28" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="Q28" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="R28" s="0" t="s">
-        <x:v>32</x:v>
+      <x:c r="P28" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S28" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:19">
       <x:c r="A29" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="E29" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F29" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="K29" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N29" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O29" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="P29" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q29" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R29" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="S29" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:19">
       <x:c r="A30" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
       <x:c r="F30" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="J30" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="N30" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="O30" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="Q30" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="R30" s="0" t="s">
-        <x:v>32</x:v>
+      <x:c r="P30" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S30" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:19">
       <x:c r="A31" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D31" s="0" t="s">
+      <x:c r="E31" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F31" s="0" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="G31" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="J31" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="L31" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="K31" s="0" t="s">
+        <x:v>115</x:v>
       </x:c>
       <x:c r="N31" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="O31" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="Q31" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="P31" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R31" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="S31" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:19">
       <x:c r="A32" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="E32" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="P32" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S32" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J32" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N32" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O32" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q32" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R32" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:19">
       <x:c r="A33" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="E33" s="0" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="F33" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G33" s="0" t="s">
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="I33" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J33" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="P33" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S33" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L33" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="N33" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O33" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q33" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R33" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:19">
       <x:c r="A34" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="B34" s="0" t="s">
+      <x:c r="E34" s="0" t="s">
         <x:v>122</x:v>
       </x:c>
+      <x:c r="F34" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="P34" s="0" t="s">
         <x:v>24</x:v>
@@ -1866,13 +1914,25 @@
     </x:row>
     <x:row r="35" spans="1:19">
       <x:c r="A35" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F35" s="0" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="B35" s="0" t="s">
+      <x:c r="H35" s="0" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="H35" s="0" t="s">
-        <x:v>23</x:v>
+      <x:c r="I35" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="J35" s="0" t="s">
+        <x:v>126</x:v>
       </x:c>
       <x:c r="P35" s="0" t="s">
         <x:v>24</x:v>
@@ -1883,13 +1943,10 @@
     </x:row>
     <x:row r="36" spans="1:19">
       <x:c r="A36" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="F36" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="H36" s="0" t="s">
         <x:v>23</x:v>
@@ -1903,22 +1960,13 @@
     </x:row>
     <x:row r="37" spans="1:19">
       <x:c r="A37" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D37" s="0" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="E37" s="0" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="F37" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H37" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P37" s="0" t="s">
         <x:v>24</x:v>
@@ -1929,22 +1977,13 @@
     </x:row>
     <x:row r="38" spans="1:19">
       <x:c r="A38" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="D38" s="0" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="E38" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="G38" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H38" s="0" t="s">
         <x:v>23</x:v>
@@ -1958,188 +1997,173 @@
     </x:row>
     <x:row r="39" spans="1:19">
       <x:c r="A39" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="E39" s="0" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="B39" s="0" t="s">
+      <x:c r="F39" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H39" s="0" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="F39" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H39" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I39" s="0" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="N39" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="O39" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="Q39" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="R39" s="0" t="s">
-        <x:v>32</x:v>
+      <x:c r="P39" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S39" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:19">
       <x:c r="A40" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="E40" s="0" t="s">
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="G40" s="0" t="s">
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H40" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="I40" s="0" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="N40" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="O40" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="Q40" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="R40" s="0" t="s">
-        <x:v>32</x:v>
+      <x:c r="P40" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S40" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:19">
       <x:c r="A41" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H41" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="I41" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="N41" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O41" s="0" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="P41" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q41" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R41" s="0" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="S41" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:19">
       <x:c r="A42" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H42" s="0" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="J42" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="I42" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="N42" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O42" s="0" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="P42" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q42" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R42" s="0" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="S42" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:19">
       <x:c r="A43" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="E43" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="H43" s="0" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="J43" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="N43" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="O43" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="Q43" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="P43" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R43" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="S43" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:19">
       <x:c r="A44" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="F44" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H44" s="0" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D44" s="0" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="E44" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F44" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G44" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H44" s="0" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="I44" s="0" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="N44" s="0" t="s">
-        <x:v>153</x:v>
+      <x:c r="J44" s="0" t="s">
+        <x:v>150</x:v>
       </x:c>
       <x:c r="O44" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="P44" s="0" t="s">
         <x:v>24</x:v>
+      </x:c>
+      <x:c r="R44" s="0" t="s">
+        <x:v>150</x:v>
       </x:c>
       <x:c r="S44" s="0" t="s">
         <x:v>24</x:v>
@@ -2147,83 +2171,107 @@
     </x:row>
     <x:row r="45" spans="1:19">
       <x:c r="A45" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D45" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G45" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="H45" s="0" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="I45" s="0" t="s">
         <x:v>155</x:v>
       </x:c>
       <x:c r="J45" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N45" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O45" s="0" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="P45" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S45" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q45" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R45" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:19">
       <x:c r="A46" s="0" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>31</x:v>
+      <x:c r="D46" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="E46" s="0" t="s">
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
+      <x:c r="G46" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
       <x:c r="H46" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="J46" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="I46" s="0" t="s">
+        <x:v>157</x:v>
       </x:c>
       <x:c r="N46" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="O46" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="Q46" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="R46" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="P46" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S46" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:19">
       <x:c r="A47" s="0" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="E47" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F47" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G47" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H47" s="0" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="B47" s="0" t="s">
+      <x:c r="I47" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="J47" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="N47" s="0" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="H47" s="0" t="s">
-        <x:v>23</x:v>
+      <x:c r="O47" s="0" t="s">
+        <x:v>160</x:v>
       </x:c>
       <x:c r="P47" s="0" t="s">
         <x:v>24</x:v>
@@ -2234,93 +2282,45 @@
     </x:row>
     <x:row r="48" spans="1:19">
       <x:c r="A48" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="C48" s="0" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="D48" s="0" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="E48" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H48" s="0" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="K48" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="L48" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J48" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N48" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O48" s="0" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="P48" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q48" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R48" s="0" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="S48" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:19">
       <x:c r="A49" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="C49" s="0" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="D49" s="0" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="E49" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F49" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="H49" s="0" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="I49" s="0" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="J49" s="0" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="K49" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="L49" s="0" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="N49" s="0" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="O49" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P49" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="R49" s="0" t="s">
-        <x:v>163</x:v>
       </x:c>
       <x:c r="S49" s="0" t="s">
         <x:v>24</x:v>
@@ -2357,22 +2357,22 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H51" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J51" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N51" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O51" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="Q51" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R51" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:19">
@@ -2392,22 +2392,22 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H52" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J52" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N52" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O52" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="Q52" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R52" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:19">

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="176">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="180">
   <x:si>
     <x:t>EZMId</x:t>
   </x:si>
@@ -118,6 +118,18 @@
     <x:t>nabeeloutsourcenz1@gmail.com</x:t>
   </x:si>
   <x:si>
+    <x:t>728E-OQ1W</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bingo jabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>balistan@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12/25/2024 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
     <x:t>D980-Q0AX</x:t>
   </x:si>
   <x:si>
@@ -229,7 +241,160 @@
     <x:t>tett test</x:t>
   </x:si>
   <x:si>
-    <x:t>8BD9-RHPZ</x:t>
+    <x:t>4395-EYPH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arif lohar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D0C9-M0CQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>testm il</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70A6-XDYQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TETSTTTWT TT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>999999</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,add agent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10/05/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test sqaq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83B6-ED47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2289-PRD0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dilbar rukha</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member,Nabeel Ahmed,exteme team,Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D4C5-ZQQB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tets tet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0924-9S1L</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,arsalan team member</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/19/2001 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DE35-5EBB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jan jj</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0F2D-MM6C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">testt </x:t>
+  </x:si>
+  <x:si>
+    <x:t>BE8D-A2NZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>reign test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09/19/1982 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8627-1VBD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rar test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FE65-MJIB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7900-P6ME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sufi cup</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/23/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/27/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/28/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5D0A-RMPK</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tst </x:t>
+  </x:si>
+  <x:si>
+    <x:t>8540-Q7DB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>211267313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F4B8-KXPP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nab ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rananabeelahmed772@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/03/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2323232332332</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/09/2023 06:52:56 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>95FF-JW04</x:t>
   </x:si>
   <x:si>
     <x:t>finame shuja</x:t>
@@ -238,163 +403,10 @@
     <x:t>3535</x:t>
   </x:si>
   <x:si>
-    <x:t>211267313</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12/25/2024 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
     <x:t>test occupation</x:t>
   </x:si>
   <x:si>
     <x:t>5435345</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4395-EYPH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arif lohar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D0C9-M0CQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>testm il</x:t>
-  </x:si>
-  <x:si>
-    <x:t>70A6-XDYQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TETSTTTWT TT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>999999</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,add agent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10/05/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test sqaq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83B6-ED47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2289-PRD0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dilbar rukha</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member,Nabeel Ahmed,exteme team,Owner nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D4C5-ZQQB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tets tet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0924-9S1L</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,arsalan team member</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/19/2001 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0F2D-MM6C</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">testt </x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE8D-A2NZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>reign test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09/19/1982 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8627-1VBD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rar test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FE65-MJIB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A962-ZCE3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>margalla hill</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7900-P6ME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sufi cup</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02/27/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02/28/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5D0A-RMPK</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tst </x:t>
-  </x:si>
-  <x:si>
-    <x:t>8540-Q7DB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F4B8-KXPP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nab ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rananabeelahmed772@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/03/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2323232332332</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/09/2023 06:52:56 +00:00</x:t>
   </x:si>
   <x:si>
     <x:t>9713-YA5L</x:t>
@@ -605,8 +617,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S53" totalsRowShown="0">
-  <x:autoFilter ref="A1:S53"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S54" totalsRowShown="0">
+  <x:autoFilter ref="A1:S54"/>
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="EZMId"/>
     <x:tableColumn id="2" name="Name"/>
@@ -920,7 +932,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:S53"/>
+  <x:dimension ref="A1:S54"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -1087,11 +1099,8 @@
       <x:c r="B6" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D6" s="0" t="s">
+      <x:c r="E6" s="0" t="s">
         <x:v>36</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>27</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>22</x:v>
@@ -1108,13 +1117,13 @@
     </x:row>
     <x:row r="7" spans="1:19">
       <x:c r="A7" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
         <x:v>27</x:v>
@@ -1123,13 +1132,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="P7" s="0" t="s">
         <x:v>24</x:v>
@@ -1140,19 +1143,28 @@
     </x:row>
     <x:row r="8" spans="1:19">
       <x:c r="A8" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
+      <x:c r="E8" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
+      <x:c r="I8" s="0" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>23</x:v>
+      <x:c r="J8" s="0" t="s">
+        <x:v>43</x:v>
       </x:c>
       <x:c r="P8" s="0" t="s">
         <x:v>24</x:v>
@@ -1163,92 +1175,83 @@
     </x:row>
     <x:row r="9" spans="1:19">
       <x:c r="A9" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="N9" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O9" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q9" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R9" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P9" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S9" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:19">
       <x:c r="A10" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B10" s="0" t="s">
+      <x:c r="F10" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P10" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S10" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N10" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O10" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q10" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R10" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:19">
       <x:c r="A11" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N11" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O11" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q11" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P11" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S11" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:19">
@@ -1258,73 +1261,64 @@
       <x:c r="B12" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="C12" s="0" t="s">
+      <x:c r="E12" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="D12" s="0" t="s">
+      <x:c r="F12" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O12" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="P12" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q12" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R12" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="S12" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:19">
       <x:c r="A13" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="I13" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="O13" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="P13" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="R13" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="S13" s="0" t="s">
         <x:v>24</x:v>
@@ -1332,19 +1326,40 @@
     </x:row>
     <x:row r="14" spans="1:19">
       <x:c r="A14" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B14" s="0" t="s">
+      <x:c r="H14" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G14" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H14" s="0" t="s">
-        <x:v>23</x:v>
+      <x:c r="I14" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="J14" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="O14" s="0" t="s">
+        <x:v>67</x:v>
       </x:c>
       <x:c r="P14" s="0" t="s">
         <x:v>24</x:v>
+      </x:c>
+      <x:c r="R14" s="0" t="s">
+        <x:v>67</x:v>
       </x:c>
       <x:c r="S14" s="0" t="s">
         <x:v>24</x:v>
@@ -1352,13 +1367,13 @@
     </x:row>
     <x:row r="15" spans="1:19">
       <x:c r="A15" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="E15" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
         <x:v>23</x:v>
@@ -1372,10 +1387,13 @@
     </x:row>
     <x:row r="16" spans="1:19">
       <x:c r="A16" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
         <x:v>23</x:v>
@@ -1389,43 +1407,16 @@
     </x:row>
     <x:row r="17" spans="1:19">
       <x:c r="A17" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C17" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D17" s="0" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F17" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="K17" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="L17" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="N17" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="O17" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P17" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="R17" s="0" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="S17" s="0" t="s">
         <x:v>24</x:v>
@@ -1433,49 +1424,19 @@
     </x:row>
     <x:row r="18" spans="1:19">
       <x:c r="A18" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C18" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="E18" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="I18" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="J18" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="K18" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="L18" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="N18" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="O18" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P18" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="R18" s="0" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="S18" s="0" t="s">
         <x:v>24</x:v>
@@ -1483,36 +1444,57 @@
     </x:row>
     <x:row r="19" spans="1:19">
       <x:c r="A19" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F19" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H19" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="P19" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S19" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="J19" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N19" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O19" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q19" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R19" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:19">
       <x:c r="A20" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B20" s="0" t="s">
+      <x:c r="D20" s="0" t="s">
         <x:v>81</x:v>
       </x:c>
+      <x:c r="E20" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F20" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
         <x:v>30</x:v>
+      </x:c>
+      <x:c r="L20" s="0" t="s">
+        <x:v>85</x:v>
       </x:c>
       <x:c r="N20" s="0" t="s">
         <x:v>30</x:v>
@@ -1529,57 +1511,39 @@
     </x:row>
     <x:row r="21" spans="1:19">
       <x:c r="A21" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D21" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="E21" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="G21" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="J21" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="L21" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="N21" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O21" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q21" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R21" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P21" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S21" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:19">
       <x:c r="A22" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="B22" s="0" t="s">
+      <x:c r="E22" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F22" s="0" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="E22" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="F22" s="0" t="s">
-        <x:v>22</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
         <x:v>23</x:v>
@@ -1599,10 +1563,10 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
         <x:v>23</x:v>
@@ -1619,22 +1583,28 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="F24" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="E24" s="0" t="s">
+      <x:c r="H24" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="F24" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H24" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P24" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S24" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="J24" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N24" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O24" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q24" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R24" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:19">
@@ -1642,39 +1612,33 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="J25" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N25" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O25" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q25" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R25" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P25" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S25" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:19">
       <x:c r="A26" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
         <x:v>23</x:v>
@@ -1688,10 +1652,10 @@
     </x:row>
     <x:row r="27" spans="1:19">
       <x:c r="A27" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>103</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
         <x:v>27</x:v>
@@ -1700,7 +1664,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
         <x:v>30</x:v>
@@ -1720,13 +1684,13 @@
     </x:row>
     <x:row r="28" spans="1:19">
       <x:c r="A28" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
         <x:v>22</x:v>
@@ -1743,10 +1707,10 @@
     </x:row>
     <x:row r="29" spans="1:19">
       <x:c r="A29" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
         <x:v>107</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>108</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
         <x:v>23</x:v>
@@ -1769,19 +1733,37 @@
     </x:row>
     <x:row r="30" spans="1:19">
       <x:c r="A30" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="B30" s="0" t="s">
+      <x:c r="E30" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F30" s="0" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="F30" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="J30" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="K30" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="N30" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="O30" s="0" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="P30" s="0" t="s">
         <x:v>24</x:v>
+      </x:c>
+      <x:c r="R30" s="0" t="s">
+        <x:v>112</x:v>
       </x:c>
       <x:c r="S30" s="0" t="s">
         <x:v>24</x:v>
@@ -1789,40 +1771,31 @@
     </x:row>
     <x:row r="31" spans="1:19">
       <x:c r="A31" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="E31" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J31" s="0" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="K31" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N31" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O31" s="0" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="P31" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q31" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R31" s="0" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="S31" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:19">
@@ -1830,16 +1803,22 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="F32" s="0" t="s">
-        <x:v>22</x:v>
+      <x:c r="G32" s="0" t="s">
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="J32" s="0" t="s">
         <x:v>30</x:v>
+      </x:c>
+      <x:c r="L32" s="0" t="s">
+        <x:v>42</x:v>
       </x:c>
       <x:c r="N32" s="0" t="s">
         <x:v>30</x:v>
@@ -1859,51 +1838,45 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D33" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="G33" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E33" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="F33" s="0" t="s">
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="J33" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="L33" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="N33" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O33" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q33" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R33" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="P33" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S33" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:19">
       <x:c r="A34" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="B34" s="0" t="s">
+      <x:c r="E34" s="0" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="E34" s="0" t="s">
+      <x:c r="F34" s="0" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="F34" s="0" t="s">
+      <x:c r="H34" s="0" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="H34" s="0" t="s">
+      <x:c r="I34" s="0" t="s">
         <x:v>124</x:v>
+      </x:c>
+      <x:c r="J34" s="0" t="s">
+        <x:v>125</x:v>
       </x:c>
       <x:c r="P34" s="0" t="s">
         <x:v>24</x:v>
@@ -1914,28 +1887,43 @@
     </x:row>
     <x:row r="35" spans="1:19">
       <x:c r="A35" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="I35" s="0" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="J35" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K35" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L35" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="N35" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="O35" s="0" t="s">
+        <x:v>37</x:v>
       </x:c>
       <x:c r="P35" s="0" t="s">
         <x:v>24</x:v>
+      </x:c>
+      <x:c r="R35" s="0" t="s">
+        <x:v>37</x:v>
       </x:c>
       <x:c r="S35" s="0" t="s">
         <x:v>24</x:v>
@@ -1943,16 +1931,49 @@
     </x:row>
     <x:row r="36" spans="1:19">
       <x:c r="A36" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="B36" s="0" t="s">
+      <x:c r="C36" s="0" t="s">
         <x:v>128</x:v>
       </x:c>
+      <x:c r="D36" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F36" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="H36" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I36" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="J36" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K36" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L36" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="N36" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="O36" s="0" t="s">
+        <x:v>37</x:v>
       </x:c>
       <x:c r="P36" s="0" t="s">
         <x:v>24</x:v>
+      </x:c>
+      <x:c r="R36" s="0" t="s">
+        <x:v>37</x:v>
       </x:c>
       <x:c r="S36" s="0" t="s">
         <x:v>24</x:v>
@@ -1960,10 +1981,10 @@
     </x:row>
     <x:row r="37" spans="1:19">
       <x:c r="A37" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="H37" s="0" t="s">
         <x:v>23</x:v>
@@ -1977,13 +1998,10 @@
     </x:row>
     <x:row r="38" spans="1:19">
       <x:c r="A38" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="F38" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="H38" s="0" t="s">
         <x:v>23</x:v>
@@ -1997,22 +2015,16 @@
     </x:row>
     <x:row r="39" spans="1:19">
       <x:c r="A39" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="E39" s="0" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P39" s="0" t="s">
         <x:v>24</x:v>
@@ -2023,25 +2035,22 @@
     </x:row>
     <x:row r="40" spans="1:19">
       <x:c r="A40" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="B40" s="0" t="s">
+      <x:c r="D40" s="0" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="D40" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="G40" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H40" s="0" t="s">
         <x:v>141</x:v>
-      </x:c>
-      <x:c r="H40" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
       <x:c r="P40" s="0" t="s">
         <x:v>24</x:v>
@@ -2058,39 +2067,36 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E41" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F41" s="0" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="F41" s="0" t="s">
-        <x:v>22</x:v>
+      <x:c r="G41" s="0" t="s">
+        <x:v>145</x:v>
       </x:c>
       <x:c r="H41" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="I41" s="0" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="N41" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O41" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q41" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R41" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="P41" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S41" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:19">
       <x:c r="A42" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
         <x:v>22</x:v>
@@ -2099,7 +2105,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="I42" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="N42" s="0" t="s">
         <x:v>30</x:v>
@@ -2116,54 +2122,57 @@
     </x:row>
     <x:row r="43" spans="1:19">
       <x:c r="A43" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="B43" s="0" t="s">
+      <x:c r="D43" s="0" t="s">
         <x:v>148</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H43" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="I43" s="0" t="s">
         <x:v>150</x:v>
       </x:c>
+      <x:c r="N43" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
       <x:c r="O43" s="0" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="P43" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q43" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R43" s="0" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="S43" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:19">
       <x:c r="A44" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="H44" s="0" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="J44" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="O44" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="P44" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="R44" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="S44" s="0" t="s">
         <x:v>24</x:v>
@@ -2176,78 +2185,69 @@
       <x:c r="B45" s="0" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="E45" s="0" t="s">
+      <x:c r="F45" s="0" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="F45" s="0" t="s">
+      <x:c r="H45" s="0" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="H45" s="0" t="s">
-        <x:v>155</x:v>
-      </x:c>
       <x:c r="J45" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N45" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="O45" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q45" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="P45" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="R45" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="S45" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:19">
       <x:c r="A46" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="B46" s="0" t="s">
+      <x:c r="E46" s="0" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="D46" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="E46" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="F46" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G46" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="H46" s="0" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="I46" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="J46" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N46" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O46" s="0" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="P46" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S46" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q46" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R46" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:19">
       <x:c r="A47" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
         <x:v>33</x:v>
@@ -2256,22 +2256,19 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="G47" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H47" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="I47" s="0" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="J47" s="0" t="s">
-        <x:v>162</x:v>
-      </x:c>
       <x:c r="N47" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="O47" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="P47" s="0" t="s">
         <x:v>24</x:v>
@@ -2282,59 +2279,80 @@
     </x:row>
     <x:row r="48" spans="1:19">
       <x:c r="A48" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E48" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F48" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G48" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H48" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="I48" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="J48" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="N48" s="0" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F48" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H48" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="J48" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N48" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="O48" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q48" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R48" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="P48" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S48" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:19">
       <x:c r="A49" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F49" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H49" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="P49" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S49" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="J49" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N49" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O49" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q49" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R49" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:19">
       <x:c r="A50" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="F50" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H50" s="0" t="s">
         <x:v>23</x:v>
@@ -2348,51 +2366,36 @@
     </x:row>
     <x:row r="51" spans="1:19">
       <x:c r="A51" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H51" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="J51" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N51" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O51" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q51" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R51" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P51" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S51" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:19">
       <x:c r="A52" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="D52" s="0" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="E52" s="0" t="s">
         <x:v>173</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H52" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J52" s="0" t="s">
         <x:v>30</x:v>
@@ -2417,13 +2420,48 @@
       <x:c r="B53" s="0" t="s">
         <x:v>175</x:v>
       </x:c>
+      <x:c r="D53" s="0" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="E53" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="F53" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="H53" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P53" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S53" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J53" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N53" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O53" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q53" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R53" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:19">
+      <x:c r="A54" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="H54" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P54" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S54" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="180">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="152">
   <x:si>
     <x:t>EZMId</x:t>
   </x:si>
@@ -85,12 +85,18 @@
     <x:t>Owner nabeel</x:t>
   </x:si>
   <x:si>
-    <x:t>01/01/1900 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">                                                                                                    </x:t>
   </x:si>
   <x:si>
+    <x:t>B1E1-CQMU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>expire thing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabel12@gmail.com</x:t>
+  </x:si>
+  <x:si>
     <x:t>331F-46PG</x:t>
   </x:si>
   <x:si>
@@ -106,9 +112,6 @@
     <x:t xml:space="preserve">test </x:t>
   </x:si>
   <x:si>
-    <x:t>01/01/0001 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
     <x:t>AE20-18YO</x:t>
   </x:si>
   <x:si>
@@ -118,7 +121,82 @@
     <x:t>nabeeloutsourcenz1@gmail.com</x:t>
   </x:si>
   <x:si>
-    <x:t>728E-OQ1W</x:t>
+    <x:t>D980-Q0AX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel secutriy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>434434434</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6F95-P7I6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TST again</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tag 3 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>2B13-9R2K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nbaaa Efgh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0300000000000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rana44@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teacher</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E260-TX8K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>check now</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24D9-XVJK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tes test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1414-W44K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3540479390287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3233232</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3323232323</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5621-A33G</x:t>
   </x:si>
   <x:si>
     <x:t>bingo jabeel</x:t>
@@ -127,102 +205,6 @@
     <x:t>balistan@gmail.com</x:t>
   </x:si>
   <x:si>
-    <x:t>12/25/2024 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D980-Q0AX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel secutriy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>434434434</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/03/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/01/2023 11:20:30 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6F95-P7I6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TST again</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tag 3 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>2B13-9R2K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nbaaa Efgh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0300000000000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rana44@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tag 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11/07/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Teacher</x:t>
-  </x:si>
-  <x:si>
-    <x:t>E260-TX8K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>check now</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24D9-XVJK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tes test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenz@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03/29/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1414-W44K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3540479390287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3233232</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05/24/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05/25/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3323232323</x:t>
-  </x:si>
-  <x:si>
     <x:t>2AE0-BA0G</x:t>
   </x:si>
   <x:si>
@@ -268,9 +250,6 @@
     <x:t>Owner nabeel,add agent</x:t>
   </x:si>
   <x:si>
-    <x:t>10/05/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
     <x:t>test sqaq</x:t>
   </x:si>
   <x:si>
@@ -304,15 +283,6 @@
     <x:t>Owner nabeel,arsalan team member</x:t>
   </x:si>
   <x:si>
-    <x:t>01/19/2001 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DE35-5EBB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>jan jj</x:t>
-  </x:si>
-  <x:si>
     <x:t>0F2D-MM6C</x:t>
   </x:si>
   <x:si>
@@ -325,9 +295,6 @@
     <x:t>reign test</x:t>
   </x:si>
   <x:si>
-    <x:t>09/19/1982 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
     <x:t>8627-1VBD</x:t>
   </x:si>
   <x:si>
@@ -349,18 +316,9 @@
     <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
   </x:si>
   <x:si>
-    <x:t>02/23/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02/27/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
     <x:t>mawaz</x:t>
   </x:si>
   <x:si>
-    <x:t>02/28/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
     <x:t>5D0A-RMPK</x:t>
   </x:si>
   <x:si>
@@ -385,30 +343,9 @@
     <x:t>Nabeel Ahmed</x:t>
   </x:si>
   <x:si>
-    <x:t>01/03/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
     <x:t>2323232332332</x:t>
   </x:si>
   <x:si>
-    <x:t>01/09/2023 06:52:56 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>95FF-JW04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>finame shuja</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3535</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test occupation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5435345</x:t>
-  </x:si>
-  <x:si>
     <x:t>9713-YA5L</x:t>
   </x:si>
   <x:si>
@@ -439,9 +376,6 @@
     <x:t>test3333@gmail.com</x:t>
   </x:si>
   <x:si>
-    <x:t>01/02/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
     <x:t>3A8B-SII4</x:t>
   </x:si>
   <x:si>
@@ -478,9 +412,6 @@
     <x:t>arsalan team member,Owner nabeel</x:t>
   </x:si>
   <x:si>
-    <x:t>02/15/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
     <x:t>D1DD-IRVU</x:t>
   </x:si>
   <x:si>
@@ -493,28 +424,13 @@
     <x:t>exteme team</x:t>
   </x:si>
   <x:si>
-    <x:t>08/11/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
     <x:t>4356-V95A</x:t>
   </x:si>
   <x:si>
     <x:t>main husband</x:t>
   </x:si>
   <x:si>
-    <x:t>08/10/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/02/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/17/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
     <x:t>msin husbanfd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/08/2023 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
     <x:t>043E-D109</x:t>
@@ -599,13 +515,20 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="1">
+  <x:cellStyleXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="1">
+  <x:cellXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -617,8 +540,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S54" totalsRowShown="0">
-  <x:autoFilter ref="A1:S54"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S52" totalsRowShown="0">
+  <x:autoFilter ref="A1:S52"/>
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="EZMId"/>
     <x:tableColumn id="2" name="Name"/>
@@ -932,7 +855,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:S54"/>
+  <x:dimension ref="A1:S52"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -1007,1462 +930,1044 @@
       <x:c r="F2" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="P2" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
       <x:c r="A3" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
+      <x:c r="E3" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="P3" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S3" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:19">
       <x:c r="A4" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
+      <x:c r="E4" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O4" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q4" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R4" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="P4" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S4" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:19">
       <x:c r="A5" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P5" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S5" s="0" t="s">
-        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:19">
       <x:c r="A6" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="P6" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S6" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:19">
       <x:c r="A7" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>41</x:v>
+      <x:c r="H7" s="1">
+        <x:v>45141</x:v>
       </x:c>
       <x:c r="P7" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S7" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:19">
       <x:c r="A8" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H8" s="1">
+        <x:v>45141</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>43</x:v>
+      <x:c r="J8" s="1">
+        <x:v>45139</x:v>
       </x:c>
       <x:c r="P8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:19">
       <x:c r="A9" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="P9" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S9" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:19">
       <x:c r="A10" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H10" s="1">
+        <x:v>45237</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="N10" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O10" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q10" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R10" s="0" t="s">
-        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:19">
       <x:c r="A11" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="P11" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S11" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:19">
       <x:c r="A12" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="J12" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N12" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O12" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q12" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R12" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="H12" s="1">
+        <x:v>45014</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:19">
       <x:c r="A13" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="H13" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="J13" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="O13" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H13" s="1">
+        <x:v>45070</x:v>
+      </x:c>
+      <x:c r="J13" s="1">
+        <x:v>45071</x:v>
+      </x:c>
+      <x:c r="O13" s="1">
+        <x:v>45071</x:v>
       </x:c>
       <x:c r="P13" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="R13" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R13" s="1">
+        <x:v>45071</x:v>
       </x:c>
       <x:c r="S13" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:19">
       <x:c r="A14" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="H14" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H14" s="1">
+        <x:v>45070</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="J14" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="O14" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J14" s="1">
+        <x:v>45071</x:v>
+      </x:c>
+      <x:c r="O14" s="1">
+        <x:v>45071</x:v>
       </x:c>
       <x:c r="P14" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="R14" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R14" s="1">
+        <x:v>45071</x:v>
       </x:c>
       <x:c r="S14" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:19">
       <x:c r="A15" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="G15" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H15" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H15" s="1">
+        <x:v>45651</x:v>
       </x:c>
       <x:c r="P15" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S15" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:19">
       <x:c r="A16" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="E16" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H16" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
+        <x:v>41</x:v>
       </x:c>
       <x:c r="P16" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S16" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:19">
       <x:c r="A17" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="H17" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>34</x:v>
       </x:c>
       <x:c r="P17" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S17" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:19">
       <x:c r="A18" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F18" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H18" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="P18" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S18" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:19">
       <x:c r="A19" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="H19" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="J19" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N19" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O19" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q19" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R19" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P19" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S19" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:19">
       <x:c r="A20" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D20" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="E20" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="F20" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="G20" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H20" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="J20" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="L20" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="N20" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O20" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q20" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R20" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:19">
       <x:c r="A21" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H21" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P21" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S21" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G21" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H21" s="1">
+        <x:v>45204</x:v>
+      </x:c>
+      <x:c r="L21" s="0" t="s">
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:19">
       <x:c r="A22" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H22" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P22" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S22" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:19">
       <x:c r="A23" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H23" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="P23" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S23" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:19">
       <x:c r="A24" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="H24" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="J24" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N24" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O24" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q24" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R24" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P24" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S24" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:19">
       <x:c r="A25" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="E25" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H25" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P25" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S25" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H25" s="1">
+        <x:v>36910</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:19">
       <x:c r="A26" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H26" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="P26" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S26" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:19">
       <x:c r="A27" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H27" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="J27" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N27" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O27" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q27" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R27" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="H27" s="1">
+        <x:v>30213</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:19">
       <x:c r="A28" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H28" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="P28" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S28" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:19">
       <x:c r="A29" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="H29" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="J29" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N29" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O29" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q29" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R29" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:19">
       <x:c r="A30" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="H30" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="J30" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="H30" s="1">
+        <x:v>44980</x:v>
+      </x:c>
+      <x:c r="J30" s="1">
+        <x:v>44984</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="N30" s="0" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="O30" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N30" s="1">
+        <x:v>44985</x:v>
+      </x:c>
+      <x:c r="O30" s="1">
+        <x:v>44984</x:v>
       </x:c>
       <x:c r="P30" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="R30" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R30" s="1">
+        <x:v>44984</x:v>
       </x:c>
       <x:c r="S30" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:19">
       <x:c r="A31" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="H31" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="J31" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N31" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O31" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q31" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R31" s="0" t="s">
-        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:19">
       <x:c r="A32" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H32" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="J32" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="L32" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="N32" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O32" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q32" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R32" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:19">
       <x:c r="A33" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="H33" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H33" s="1">
+        <x:v>44929</x:v>
       </x:c>
       <x:c r="P33" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S33" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:19">
       <x:c r="A34" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="H34" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H34" s="1">
+        <x:v>44929</x:v>
       </x:c>
       <x:c r="I34" s="0" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="J34" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="J34" s="1">
+        <x:v>44935</x:v>
       </x:c>
       <x:c r="P34" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S34" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:19">
       <x:c r="A35" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="C35" s="0" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="E35" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F35" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H35" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="K35" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="L35" s="0" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="N35" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="O35" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="P35" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="R35" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S35" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:19">
       <x:c r="A36" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="C36" s="0" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D36" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="E36" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F36" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H36" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I36" s="0" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="J36" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="K36" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="L36" s="0" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="N36" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="O36" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="P36" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="R36" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S36" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:19">
       <x:c r="A37" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="H37" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F37" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P37" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S37" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:19">
       <x:c r="A38" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="H38" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E38" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="F38" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H38" s="1">
+        <x:v>44928</x:v>
       </x:c>
       <x:c r="P38" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S38" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:19">
       <x:c r="A39" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="E39" s="0" t="s">
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H39" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G39" s="0" t="s">
+        <x:v>123</x:v>
       </x:c>
       <x:c r="P39" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S39" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:19">
       <x:c r="A40" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="E40" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H40" s="0" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="P40" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S40" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="I40" s="0" t="s">
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:19">
       <x:c r="A41" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="E41" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="G41" s="0" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="H41" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P41" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S41" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="I41" s="0" t="s">
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:19">
       <x:c r="A42" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="D42" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H42" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I42" s="0" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="N42" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O42" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q42" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R42" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="H42" s="1">
+        <x:v>44972</x:v>
+      </x:c>
+      <x:c r="O42" s="1">
+        <x:v>44972</x:v>
+      </x:c>
+      <x:c r="P42" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R42" s="1">
+        <x:v>44972</x:v>
+      </x:c>
+      <x:c r="S42" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:19">
       <x:c r="A43" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="D43" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H43" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I43" s="0" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="N43" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O43" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q43" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R43" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="H43" s="1">
+        <x:v>44972</x:v>
+      </x:c>
+      <x:c r="J43" s="1">
+        <x:v>44972</x:v>
+      </x:c>
+      <x:c r="O43" s="1">
+        <x:v>44972</x:v>
+      </x:c>
+      <x:c r="P43" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R43" s="1">
+        <x:v>44972</x:v>
+      </x:c>
+      <x:c r="S43" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:19">
       <x:c r="A44" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="E44" s="0" t="s">
+        <x:v>134</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="H44" s="0" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="O44" s="0" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="P44" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="R44" s="0" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="S44" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="H44" s="1">
+        <x:v>45149</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:19">
       <x:c r="A45" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="E45" s="0" t="s">
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="H45" s="0" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="J45" s="0" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="O45" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G45" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H45" s="1">
+        <x:v>45148</x:v>
+      </x:c>
+      <x:c r="I45" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="N45" s="1">
+        <x:v>45140</x:v>
+      </x:c>
+      <x:c r="O45" s="1">
+        <x:v>45155</x:v>
       </x:c>
       <x:c r="P45" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="R45" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S45" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:19">
       <x:c r="A46" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="H46" s="0" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="J46" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N46" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O46" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q46" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R46" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G46" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H46" s="1">
+        <x:v>45148</x:v>
+      </x:c>
+      <x:c r="I46" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="J46" s="1">
+        <x:v>45146</x:v>
+      </x:c>
+      <x:c r="N46" s="1">
+        <x:v>45140</x:v>
+      </x:c>
+      <x:c r="O46" s="1">
+        <x:v>45155</x:v>
+      </x:c>
+      <x:c r="P46" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S46" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:19">
       <x:c r="A47" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="D47" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="E47" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="G47" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H47" s="0" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="I47" s="0" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="N47" s="0" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="O47" s="0" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="P47" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S47" s="0" t="s">
-        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:19">
       <x:c r="A48" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="D48" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="E48" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F48" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G48" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H48" s="0" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="I48" s="0" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="J48" s="0" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="N48" s="0" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="O48" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="P48" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S48" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:19">
       <x:c r="A49" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H49" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="J49" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N49" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O49" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q49" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R49" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="P49" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S49" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:19">
       <x:c r="A50" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="H50" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P50" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S50" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="F50" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H50" s="1">
+        <x:v>45014</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:19">
       <x:c r="A51" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="E51" s="0" t="s">
+        <x:v>149</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H51" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P51" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S51" s="0" t="s">
-        <x:v>24</x:v>
+      <x:c r="H51" s="1">
+        <x:v>45014</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:19">
       <x:c r="A52" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="F52" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H52" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="J52" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N52" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O52" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q52" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R52" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:19">
-      <x:c r="A53" s="0" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="D53" s="0" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="E53" s="0" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="F53" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H53" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="J53" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="N53" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="O53" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q53" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R53" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:19">
-      <x:c r="A54" s="0" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="H54" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="P54" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="S54" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="P52" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S52" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="152">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
   <x:si>
     <x:t>EZMId</x:t>
   </x:si>
@@ -196,7 +196,7 @@
     <x:t>3323232323</x:t>
   </x:si>
   <x:si>
-    <x:t>5621-A33G</x:t>
+    <x:t>CA77-848B</x:t>
   </x:si>
   <x:si>
     <x:t>bingo jabeel</x:t>
@@ -436,10 +436,40 @@
     <x:t>043E-D109</x:t>
   </x:si>
   <x:si>
+    <x:t>C-7BEF-HGFR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>g masom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rananabeelahmed968@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>team member nabeel,Owner nabeel,Nabeel Ahmed,arsalan team member</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tet</x:t>
+  </x:si>
+  <x:si>
     <x:t>1D77-ED7L</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">testhshhd...1 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>4341-5MZR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>finame shuja</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3535</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test occupation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5435345</x:t>
   </x:si>
   <x:si>
     <x:t>AFA9-V8G1</x:t>
@@ -540,8 +570,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S52" totalsRowShown="0">
-  <x:autoFilter ref="A1:S52"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S55" totalsRowShown="0">
+  <x:autoFilter ref="A1:S55"/>
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="EZMId"/>
     <x:tableColumn id="2" name="Name"/>
@@ -855,7 +885,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:S52"/>
+  <x:dimension ref="A1:S55"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -950,6 +980,9 @@
       <x:c r="F3" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
+      <x:c r="H3" s="1">
+        <x:v>45413</x:v>
+      </x:c>
       <x:c r="P3" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -1898,22 +1931,22 @@
       <x:c r="B48" s="0" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="P48" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="S48" s="0" t="s">
-        <x:v>23</x:v>
+      <x:c r="E48" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="F48" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="K48" s="0" t="s">
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:19">
       <x:c r="A49" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="F49" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="P49" s="0" t="s">
         <x:v>23</x:v>
@@ -1924,49 +1957,160 @@
     </x:row>
     <x:row r="50" spans="1:19">
       <x:c r="A50" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="E50" s="0" t="s">
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H50" s="1">
-        <x:v>45014</x:v>
+        <x:v>45651</x:v>
+      </x:c>
+      <x:c r="K50" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="L50" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="N50" s="1">
+        <x:v>45651</x:v>
+      </x:c>
+      <x:c r="O50" s="1">
+        <x:v>45651</x:v>
+      </x:c>
+      <x:c r="P50" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R50" s="1">
+        <x:v>45651</x:v>
+      </x:c>
+      <x:c r="S50" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:19">
       <x:c r="A51" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H51" s="1">
-        <x:v>45014</x:v>
+        <x:v>45651</x:v>
+      </x:c>
+      <x:c r="I51" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="J51" s="1">
+        <x:v>45651</x:v>
+      </x:c>
+      <x:c r="K51" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="L51" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="N51" s="1">
+        <x:v>45651</x:v>
+      </x:c>
+      <x:c r="O51" s="1">
+        <x:v>45651</x:v>
+      </x:c>
+      <x:c r="P51" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R51" s="1">
+        <x:v>45651</x:v>
+      </x:c>
+      <x:c r="S51" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:19">
       <x:c r="A52" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F52" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P52" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="S52" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:19">
+      <x:c r="A53" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="F53" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H53" s="1">
+        <x:v>45014</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:19">
+      <x:c r="A54" s="0" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="E54" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="F54" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H54" s="1">
+        <x:v>45014</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:19">
+      <x:c r="A55" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="P55" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S55" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
   <x:si>
     <x:t>EZMId</x:t>
   </x:si>
@@ -94,7 +94,7 @@
     <x:t>expire thing</x:t>
   </x:si>
   <x:si>
-    <x:t>nabel12@gmail.com</x:t>
+    <x:t>nabel123@gmail.com</x:t>
   </x:si>
   <x:si>
     <x:t>331F-46PG</x:t>
@@ -121,6 +121,12 @@
     <x:t>nabeeloutsourcenz1@gmail.com</x:t>
   </x:si>
   <x:si>
+    <x:t>5D4D-B8T6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>margalla hill</x:t>
+  </x:si>
+  <x:si>
     <x:t>D980-Q0AX</x:t>
   </x:si>
   <x:si>
@@ -142,6 +148,9 @@
     <x:t xml:space="preserve">tag 3 </x:t>
   </x:si>
   <x:si>
+    <x:t>9801-L8WV</x:t>
+  </x:si>
+  <x:si>
     <x:t>2B13-9R2K</x:t>
   </x:si>
   <x:si>
@@ -196,7 +205,154 @@
     <x:t>3323232323</x:t>
   </x:si>
   <x:si>
-    <x:t>CA77-848B</x:t>
+    <x:t>2AE0-BA0G</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test school</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AC22-Z9CM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test Streich</x:t>
+  </x:si>
+  <x:si>
+    <x:t>252F-ASJE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tett test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4395-EYPH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arif lohar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D0C9-M0CQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>testm il</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BA4D-6452</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70A6-XDYQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TETSTTTWT TT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>999999</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,add agent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test sqaq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83B6-ED47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2289-PRD0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dilbar rukha</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member,Nabeel Ahmed,exteme team,Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D4C5-ZQQB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tets tet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0924-9S1L</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,arsalan team member</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0F2D-MM6C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">testt </x:t>
+  </x:si>
+  <x:si>
+    <x:t>BE8D-A2NZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>reign test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8627-1VBD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rar test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FE65-MJIB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>381C-XZEI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7900-P6ME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sufi cup</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5D0A-RMPK</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tst </x:t>
+  </x:si>
+  <x:si>
+    <x:t>8540-Q7DB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>211267313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F4B8-KXPP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nab ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rananabeelahmed772@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2323232332332</x:t>
+  </x:si>
+  <x:si>
+    <x:t>268D-H2DV</x:t>
   </x:si>
   <x:si>
     <x:t>bingo jabeel</x:t>
@@ -205,153 +361,15 @@
     <x:t>balistan@gmail.com</x:t>
   </x:si>
   <x:si>
-    <x:t>2AE0-BA0G</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test school</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AC22-Z9CM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test Streich</x:t>
-  </x:si>
-  <x:si>
-    <x:t>252F-ASJE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tett test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4395-EYPH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arif lohar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D0C9-M0CQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>testm il</x:t>
-  </x:si>
-  <x:si>
-    <x:t>70A6-XDYQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TETSTTTWT TT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>999999</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,add agent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test sqaq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83B6-ED47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2289-PRD0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dilbar rukha</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member,Nabeel Ahmed,exteme team,Owner nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D4C5-ZQQB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tets tet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0924-9S1L</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,arsalan team member</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0F2D-MM6C</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">testt </x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE8D-A2NZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>reign test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8627-1VBD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rar test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FE65-MJIB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7900-P6ME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sufi cup</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5D0A-RMPK</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tst </x:t>
-  </x:si>
-  <x:si>
-    <x:t>8540-Q7DB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>211267313</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F4B8-KXPP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nab ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rananabeelahmed772@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2323232332332</x:t>
-  </x:si>
-  <x:si>
     <x:t>9713-YA5L</x:t>
   </x:si>
   <x:si>
     <x:t>nimal test</x:t>
   </x:si>
   <x:si>
+    <x:t>D13A-G3UJ</x:t>
+  </x:si>
+  <x:si>
     <x:t>AA8F-FH1K</x:t>
   </x:si>
   <x:si>
@@ -364,18 +382,6 @@
     <x:t>first test</x:t>
   </x:si>
   <x:si>
-    <x:t>840E-CILQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel muhammad changes</x:t>
-  </x:si>
-  <x:si>
-    <x:t>33333333</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test3333@gmail.com</x:t>
-  </x:si>
-  <x:si>
     <x:t>3A8B-SII4</x:t>
   </x:si>
   <x:si>
@@ -388,6 +394,9 @@
     <x:t>tag 1</x:t>
   </x:si>
   <x:si>
+    <x:t>700C-RZYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>1AA1-TIH9</x:t>
   </x:si>
   <x:si>
@@ -436,40 +445,10 @@
     <x:t>043E-D109</x:t>
   </x:si>
   <x:si>
-    <x:t>C-7BEF-HGFR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>g masom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rananabeelahmed968@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>team member nabeel,Owner nabeel,Nabeel Ahmed,arsalan team member</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tet</x:t>
-  </x:si>
-  <x:si>
     <x:t>1D77-ED7L</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">testhshhd...1 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>4341-5MZR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>finame shuja</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3535</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test occupation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5435345</x:t>
   </x:si>
   <x:si>
     <x:t>AFA9-V8G1</x:t>
@@ -570,8 +549,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S55" totalsRowShown="0">
-  <x:autoFilter ref="A1:S55"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S57" totalsRowShown="0">
+  <x:autoFilter ref="A1:S57"/>
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="EZMId"/>
     <x:tableColumn id="2" name="Name"/>
@@ -885,7 +864,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:S55"/>
+  <x:dimension ref="A1:S57"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -981,7 +960,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H3" s="1">
-        <x:v>45413</x:v>
+        <x:v>45499</x:v>
       </x:c>
       <x:c r="P3" s="0" t="s">
         <x:v>23</x:v>
@@ -1048,17 +1027,8 @@
       <x:c r="B7" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="F7" s="0" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="H7" s="1">
-        <x:v>45141</x:v>
       </x:c>
       <x:c r="P7" s="0" t="s">
         <x:v>23</x:v>
@@ -1069,13 +1039,13 @@
     </x:row>
     <x:row r="8" spans="1:19">
       <x:c r="A8" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
         <x:v>29</x:v>
@@ -1086,12 +1056,6 @@
       <x:c r="H8" s="1">
         <x:v>45141</x:v>
       </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="J8" s="1">
-        <x:v>45139</x:v>
-      </x:c>
       <x:c r="P8" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -1101,16 +1065,28 @@
     </x:row>
     <x:row r="9" spans="1:19">
       <x:c r="A9" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B9" s="0" t="s">
+      <x:c r="E9" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H9" s="1">
+        <x:v>45141</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>41</x:v>
+      <x:c r="J9" s="1">
+        <x:v>45139</x:v>
       </x:c>
       <x:c r="P9" s="0" t="s">
         <x:v>23</x:v>
@@ -1121,36 +1097,33 @@
     </x:row>
     <x:row r="10" spans="1:19">
       <x:c r="A10" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="B10" s="0" t="s">
+      <x:c r="E10" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H10" s="1">
-        <x:v>45237</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>47</x:v>
+      <x:c r="P10" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S10" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:19">
       <x:c r="A11" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P11" s="0" t="s">
         <x:v>23</x:v>
@@ -1161,54 +1134,39 @@
     </x:row>
     <x:row r="12" spans="1:19">
       <x:c r="A12" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H12" s="1">
+        <x:v>45237</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H12" s="1">
-        <x:v>45014</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:19">
       <x:c r="A13" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F13" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H13" s="1">
-        <x:v>45070</x:v>
-      </x:c>
-      <x:c r="J13" s="1">
-        <x:v>45071</x:v>
-      </x:c>
-      <x:c r="O13" s="1">
-        <x:v>45071</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="P13" s="0" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="R13" s="1">
-        <x:v>45071</x:v>
       </x:c>
       <x:c r="S13" s="0" t="s">
         <x:v>23</x:v>
@@ -1221,58 +1179,49 @@
       <x:c r="B14" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="C14" s="0" t="s">
+      <x:c r="E14" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E14" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>45070</x:v>
-      </x:c>
-      <x:c r="I14" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="J14" s="1">
-        <x:v>45071</x:v>
-      </x:c>
-      <x:c r="O14" s="1">
-        <x:v>45071</x:v>
-      </x:c>
-      <x:c r="P14" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="R14" s="1">
-        <x:v>45071</x:v>
-      </x:c>
-      <x:c r="S14" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>45014</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:19">
       <x:c r="A15" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B15" s="0" t="s">
+      <x:c r="F15" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="E15" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F15" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H15" s="1">
-        <x:v>45651</x:v>
+        <x:v>45070</x:v>
+      </x:c>
+      <x:c r="J15" s="1">
+        <x:v>45071</x:v>
+      </x:c>
+      <x:c r="O15" s="1">
+        <x:v>45071</x:v>
       </x:c>
       <x:c r="P15" s="0" t="s">
         <x:v>23</x:v>
+      </x:c>
+      <x:c r="R15" s="1">
+        <x:v>45071</x:v>
       </x:c>
       <x:c r="S15" s="0" t="s">
         <x:v>23</x:v>
@@ -1280,16 +1229,40 @@
     </x:row>
     <x:row r="16" spans="1:19">
       <x:c r="A16" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="G16" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="H16" s="1">
+        <x:v>45070</x:v>
+      </x:c>
+      <x:c r="I16" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="J16" s="1">
+        <x:v>45071</x:v>
+      </x:c>
+      <x:c r="O16" s="1">
+        <x:v>45071</x:v>
       </x:c>
       <x:c r="P16" s="0" t="s">
         <x:v>23</x:v>
+      </x:c>
+      <x:c r="R16" s="1">
+        <x:v>45071</x:v>
       </x:c>
       <x:c r="S16" s="0" t="s">
         <x:v>23</x:v>
@@ -1297,13 +1270,16 @@
     </x:row>
     <x:row r="17" spans="1:19">
       <x:c r="A17" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
+        <x:v>43</x:v>
       </x:c>
       <x:c r="P17" s="0" t="s">
         <x:v>23</x:v>
@@ -1314,10 +1290,13 @@
     </x:row>
     <x:row r="18" spans="1:19">
       <x:c r="A18" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>34</x:v>
       </x:c>
       <x:c r="P18" s="0" t="s">
         <x:v>23</x:v>
@@ -1328,13 +1307,10 @@
     </x:row>
     <x:row r="19" spans="1:19">
       <x:c r="A19" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F19" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="P19" s="0" t="s">
         <x:v>23</x:v>
@@ -1345,47 +1321,35 @@
     </x:row>
     <x:row r="20" spans="1:19">
       <x:c r="A20" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F20" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P20" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S20" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:19">
       <x:c r="A21" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D21" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E21" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F21" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="G21" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="H21" s="1">
-        <x:v>45204</x:v>
-      </x:c>
-      <x:c r="L21" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:19">
       <x:c r="A22" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="E22" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
         <x:v>22</x:v>
@@ -1399,33 +1363,39 @@
     </x:row>
     <x:row r="23" spans="1:19">
       <x:c r="A23" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="P23" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="S23" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G23" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H23" s="1">
+        <x:v>45204</x:v>
+      </x:c>
+      <x:c r="L23" s="0" t="s">
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:19">
       <x:c r="A24" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
         <x:v>22</x:v>
@@ -1439,27 +1409,36 @@
     </x:row>
     <x:row r="25" spans="1:19">
       <x:c r="A25" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="H25" s="1">
-        <x:v>36910</x:v>
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="P25" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S25" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:19">
       <x:c r="A26" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="G26" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P26" s="0" t="s">
         <x:v>23</x:v>
@@ -1470,33 +1449,27 @@
     </x:row>
     <x:row r="27" spans="1:19">
       <x:c r="A27" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="E27" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>30213</x:v>
+        <x:v>36910</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:19">
       <x:c r="A28" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="E28" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="F28" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G28" s="0" t="s">
+        <x:v>43</x:v>
       </x:c>
       <x:c r="P28" s="0" t="s">
         <x:v>23</x:v>
@@ -1507,45 +1480,36 @@
     </x:row>
     <x:row r="29" spans="1:19">
       <x:c r="A29" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F29" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H29" s="1">
+        <x:v>30213</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:19">
       <x:c r="A30" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="H30" s="1">
-        <x:v>44980</x:v>
-      </x:c>
-      <x:c r="J30" s="1">
-        <x:v>44984</x:v>
-      </x:c>
-      <x:c r="K30" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="N30" s="1">
-        <x:v>44985</x:v>
-      </x:c>
-      <x:c r="O30" s="1">
-        <x:v>44984</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P30" s="0" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="R30" s="1">
-        <x:v>44984</x:v>
       </x:c>
       <x:c r="S30" s="0" t="s">
         <x:v>23</x:v>
@@ -1553,50 +1517,62 @@
     </x:row>
     <x:row r="31" spans="1:19">
       <x:c r="A31" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="F31" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:19">
       <x:c r="A32" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D32" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="G32" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="L32" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F32" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P32" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S32" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:19">
       <x:c r="A33" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>44929</x:v>
+        <x:v>44980</x:v>
+      </x:c>
+      <x:c r="J33" s="1">
+        <x:v>44984</x:v>
+      </x:c>
+      <x:c r="K33" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="N33" s="1">
+        <x:v>44985</x:v>
+      </x:c>
+      <x:c r="O33" s="1">
+        <x:v>44984</x:v>
       </x:c>
       <x:c r="P33" s="0" t="s">
         <x:v>23</x:v>
+      </x:c>
+      <x:c r="R33" s="1">
+        <x:v>44984</x:v>
       </x:c>
       <x:c r="S33" s="0" t="s">
         <x:v>23</x:v>
@@ -1604,53 +1580,47 @@
     </x:row>
     <x:row r="34" spans="1:19">
       <x:c r="A34" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="E34" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="H34" s="1">
-        <x:v>44929</x:v>
-      </x:c>
-      <x:c r="I34" s="0" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="J34" s="1">
-        <x:v>44935</x:v>
-      </x:c>
-      <x:c r="P34" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="S34" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:19">
       <x:c r="A35" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="P35" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="S35" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G35" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="L35" s="0" t="s">
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:19">
       <x:c r="A36" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F36" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H36" s="1">
+        <x:v>44929</x:v>
       </x:c>
       <x:c r="P36" s="0" t="s">
         <x:v>23</x:v>
@@ -1661,13 +1631,25 @@
     </x:row>
     <x:row r="37" spans="1:19">
       <x:c r="A37" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H37" s="1">
+        <x:v>44929</x:v>
+      </x:c>
+      <x:c r="I37" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="J37" s="1">
+        <x:v>44935</x:v>
       </x:c>
       <x:c r="P37" s="0" t="s">
         <x:v>23</x:v>
@@ -1678,22 +1660,19 @@
     </x:row>
     <x:row r="38" spans="1:19">
       <x:c r="A38" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="D38" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>44928</x:v>
+        <x:v>45651</x:v>
       </x:c>
       <x:c r="P38" s="0" t="s">
         <x:v>23</x:v>
@@ -1704,22 +1683,10 @@
     </x:row>
     <x:row r="39" spans="1:19">
       <x:c r="A39" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="E39" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="F39" s="0" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G39" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="P39" s="0" t="s">
         <x:v>23</x:v>
@@ -1730,59 +1697,47 @@
     </x:row>
     <x:row r="40" spans="1:19">
       <x:c r="A40" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="D40" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="I40" s="0" t="s">
-        <x:v>127</x:v>
+      <x:c r="P40" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S40" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:19">
       <x:c r="A41" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="D41" s="0" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="F41" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="I41" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="P41" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S41" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:19">
       <x:c r="A42" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="H42" s="1">
-        <x:v>44972</x:v>
-      </x:c>
-      <x:c r="O42" s="1">
-        <x:v>44972</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P42" s="0" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="R42" s="1">
-        <x:v>44972</x:v>
       </x:c>
       <x:c r="S42" s="0" t="s">
         <x:v>23</x:v>
@@ -1790,28 +1745,25 @@
     </x:row>
     <x:row r="43" spans="1:19">
       <x:c r="A43" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="E43" s="0" t="s">
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="H43" s="1">
-        <x:v>44972</x:v>
-      </x:c>
-      <x:c r="J43" s="1">
-        <x:v>44972</x:v>
-      </x:c>
-      <x:c r="O43" s="1">
-        <x:v>44972</x:v>
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="G43" s="0" t="s">
+        <x:v>125</x:v>
       </x:c>
       <x:c r="P43" s="0" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="R43" s="1">
-        <x:v>44972</x:v>
       </x:c>
       <x:c r="S43" s="0" t="s">
         <x:v>23</x:v>
@@ -1819,154 +1771,136 @@
     </x:row>
     <x:row r="44" spans="1:19">
       <x:c r="A44" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="E44" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="H44" s="1">
-        <x:v>45149</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P44" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S44" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:19">
       <x:c r="A45" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="E45" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G45" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="H45" s="1">
-        <x:v>45148</x:v>
-      </x:c>
       <x:c r="I45" s="0" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="N45" s="1">
-        <x:v>45140</x:v>
-      </x:c>
-      <x:c r="O45" s="1">
-        <x:v>45155</x:v>
-      </x:c>
-      <x:c r="P45" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="S45" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:19">
       <x:c r="A46" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="E46" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G46" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="H46" s="1">
-        <x:v>45148</x:v>
-      </x:c>
       <x:c r="I46" s="0" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="J46" s="1">
-        <x:v>45146</x:v>
-      </x:c>
-      <x:c r="N46" s="1">
-        <x:v>45140</x:v>
-      </x:c>
-      <x:c r="O46" s="1">
-        <x:v>45155</x:v>
-      </x:c>
-      <x:c r="P46" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="S46" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:19">
       <x:c r="A47" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="H47" s="1">
+        <x:v>44972</x:v>
+      </x:c>
+      <x:c r="O47" s="1">
+        <x:v>44972</x:v>
+      </x:c>
+      <x:c r="P47" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R47" s="1">
+        <x:v>44972</x:v>
+      </x:c>
+      <x:c r="S47" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:19">
       <x:c r="A48" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="E48" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="K48" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="H48" s="1">
+        <x:v>44972</x:v>
+      </x:c>
+      <x:c r="J48" s="1">
+        <x:v>44972</x:v>
+      </x:c>
+      <x:c r="O48" s="1">
+        <x:v>44972</x:v>
+      </x:c>
+      <x:c r="P48" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="R48" s="1">
+        <x:v>44972</x:v>
+      </x:c>
+      <x:c r="S48" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:19">
       <x:c r="A49" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="P49" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="S49" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="E49" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="F49" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H49" s="1">
+        <x:v>45149</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:19">
       <x:c r="A50" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="C50" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
         <x:v>34</x:v>
@@ -1974,26 +1908,23 @@
       <x:c r="F50" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
+      <x:c r="G50" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
       <x:c r="H50" s="1">
-        <x:v>45651</x:v>
-      </x:c>
-      <x:c r="K50" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="L50" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>45148</x:v>
+      </x:c>
+      <x:c r="I50" s="0" t="s">
+        <x:v>140</x:v>
       </x:c>
       <x:c r="N50" s="1">
-        <x:v>45651</x:v>
+        <x:v>45140</x:v>
       </x:c>
       <x:c r="O50" s="1">
-        <x:v>45651</x:v>
+        <x:v>45155</x:v>
       </x:c>
       <x:c r="P50" s="0" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="R50" s="1">
-        <x:v>45651</x:v>
       </x:c>
       <x:c r="S50" s="0" t="s">
         <x:v>23</x:v>
@@ -2001,16 +1932,13 @@
     </x:row>
     <x:row r="51" spans="1:19">
       <x:c r="A51" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="C51" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
         <x:v>34</x:v>
@@ -2018,32 +1946,26 @@
       <x:c r="F51" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
+      <x:c r="G51" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
       <x:c r="H51" s="1">
-        <x:v>45651</x:v>
+        <x:v>45148</x:v>
       </x:c>
       <x:c r="I51" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="J51" s="1">
-        <x:v>45651</x:v>
-      </x:c>
-      <x:c r="K51" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="L51" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>45146</x:v>
       </x:c>
       <x:c r="N51" s="1">
-        <x:v>45651</x:v>
+        <x:v>45140</x:v>
       </x:c>
       <x:c r="O51" s="1">
-        <x:v>45651</x:v>
+        <x:v>45155</x:v>
       </x:c>
       <x:c r="P51" s="0" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="R51" s="1">
-        <x:v>45651</x:v>
       </x:c>
       <x:c r="S51" s="0" t="s">
         <x:v>23</x:v>
@@ -2051,66 +1973,91 @@
     </x:row>
     <x:row r="52" spans="1:19">
       <x:c r="A52" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="P52" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="S52" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:19">
       <x:c r="A53" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="F53" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H53" s="1">
-        <x:v>45014</x:v>
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="P53" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S53" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:19">
       <x:c r="A54" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="D54" s="0" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="E54" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H54" s="1">
-        <x:v>45014</x:v>
+      <x:c r="P54" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S54" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:19">
       <x:c r="A55" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="P55" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="S55" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="F55" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H55" s="1">
+        <x:v>45014</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:19">
+      <x:c r="A56" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D56" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="E56" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="F56" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H56" s="1">
+        <x:v>45014</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:19">
+      <x:c r="A57" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="P57" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S57" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
   <x:si>
     <x:t>EZMId</x:t>
   </x:si>
@@ -73,37 +73,55 @@
     <x:t>X-ray Grading</x:t>
   </x:si>
   <x:si>
+    <x:t>601F-EQSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test gamux</x:t>
+  </x:si>
+  <x:si>
+    <x:t>a@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1558-41KA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>passport num</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B1E1-CQMU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>expire thing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabel123@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>331F-46PG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>st test</x:t>
+  </x:si>
+  <x:si>
     <x:t>BC27-YS4F</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">test </x:t>
   </x:si>
   <x:si>
-    <x:t>Owner nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1558-41KA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>passport num</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>601F-EQSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test gamux</x:t>
-  </x:si>
-  <x:si>
-    <x:t>a@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>331F-46PG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>st test</x:t>
+    <x:t>AE20-18YO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tst client log</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz1@gmail.com</x:t>
   </x:si>
   <x:si>
     <x:t>D980-Q0AX</x:t>
@@ -115,33 +133,21 @@
     <x:t>434434434</x:t>
   </x:si>
   <x:si>
+    <x:t>1D77-ED7L</x:t>
+  </x:si>
+  <x:si>
+    <x:t>retret retret</x:t>
+  </x:si>
+  <x:si>
     <x:t>6F95-P7I6</x:t>
   </x:si>
   <x:si>
     <x:t>TST again</x:t>
   </x:si>
   <x:si>
-    <x:t>nabeeloutsourcenz1@gmail.com</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">tag 3 </x:t>
   </x:si>
   <x:si>
-    <x:t>B1E1-CQMU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>expire thing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabel123@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AE20-18YO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tst client log</x:t>
-  </x:si>
-  <x:si>
     <x:t>2B13-9R2K</x:t>
   </x:si>
   <x:si>
@@ -157,54 +163,96 @@
     <x:t>Teacher</x:t>
   </x:si>
   <x:si>
+    <x:t>A5C1-YB22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>basic wfe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member,Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>relative test</x:t>
+  </x:si>
+  <x:si>
     <x:t>E260-TX8K</x:t>
   </x:si>
   <x:si>
     <x:t>check now</x:t>
   </x:si>
   <x:si>
+    <x:t>24D9-XVJK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tes test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1414-W44K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3540479390287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3233232</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7900-P6ME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sufi cup wife</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3A8B-SII4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>new child</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,team member nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag 3 ,tag 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ayesh ahmed</x:t>
+  </x:si>
+  <x:si>
     <x:t>2AE0-BA0G</x:t>
   </x:si>
   <x:si>
     <x:t>test school</x:t>
   </x:si>
   <x:si>
-    <x:t>1D77-ED7L</x:t>
-  </x:si>
-  <x:si>
-    <x:t>retret retret</x:t>
-  </x:si>
-  <x:si>
     <x:t>AC22-Z9CM</x:t>
   </x:si>
   <x:si>
     <x:t>test Streich</x:t>
   </x:si>
   <x:si>
-    <x:t>24D9-XVJK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tes test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenz@gmail.com</x:t>
-  </x:si>
-  <x:si>
     <x:t>252F-ASJE</x:t>
   </x:si>
   <x:si>
     <x:t>tett test</x:t>
   </x:si>
   <x:si>
-    <x:t>A5C1-YB22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>basic wfe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member,Owner nabeel</x:t>
-  </x:si>
-  <x:si>
     <x:t>2289-PRD0</x:t>
   </x:si>
   <x:si>
@@ -214,40 +262,94 @@
     <x:t>arsalan team member,Nabeel Ahmed,exteme team,Owner nabeel</x:t>
   </x:si>
   <x:si>
-    <x:t>7900-P6ME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sufi cup wife</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
+    <x:t>4395-EYPH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arif lohar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D0C9-M0CQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>testm il</x:t>
+  </x:si>
+  <x:si>
+    <x:t>shcool relation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>relation@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70A6-XDYQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TETSTTTWT TT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>999999</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,add agent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test sqaq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>510D-BPGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bingo jabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>balistan@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83B6-ED47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F4B8-KXPP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nab ahmed wife</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dilbar rukha</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D4C5-ZQQB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tets tet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tet tt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>kiran nao</x:t>
   </x:si>
   <x:si>
     <x:t>0924-9S1L</x:t>
   </x:si>
   <x:si>
-    <x:t>test test</x:t>
-  </x:si>
-  <x:si>
     <x:t>Owner nabeel,arsalan team member</x:t>
   </x:si>
   <x:si>
-    <x:t>relative test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4395-EYPH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arif lohar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F4D2-F48I</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bingo jabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>balistan@gmail.com</x:t>
+    <x:t>test tesssss</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0F2D-MM6C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">testt </x:t>
   </x:si>
   <x:si>
     <x:t>BE8D-A2NZ</x:t>
@@ -256,43 +358,52 @@
     <x:t>reign test</x:t>
   </x:si>
   <x:si>
-    <x:t>1414-W44K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3540479390287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3233232</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member</x:t>
-  </x:si>
-  <x:si>
-    <x:t>70A6-XDYQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TETSTTTWT TT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>999999</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,add agent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test sqaq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ayesh ahmed</x:t>
+    <x:t>8627-1VBD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rar test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FE65-MJIB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4356-V95A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>new partner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sufi cup</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz</x:t>
+  </x:si>
+  <x:si>
+    <x:t>school child</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5D0A-RMPK</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tst </x:t>
+  </x:si>
+  <x:si>
+    <x:t>8540-Q7DB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>211267313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nab ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rananabeelahmed772@gmail.com</x:t>
   </x:si>
   <x:si>
     <x:t>9713-YA5L</x:t>
@@ -301,133 +412,88 @@
     <x:t>nimal test</x:t>
   </x:si>
   <x:si>
-    <x:t>3A8B-SII4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>new child</x:t>
-  </x:si>
-  <x:si>
-    <x:t>211267313</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,team member nabeel</x:t>
+    <x:t>AA8F-FH1K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>lets see</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2E65-SXT6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>first test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>840E-CILQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel muhammad changes</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33333333</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test3333@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>new last</x:t>
   </x:si>
   <x:si>
     <x:t>tag 1</x:t>
   </x:si>
   <x:si>
-    <x:t>F4B8-KXPP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nab ahmed wife</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>shcool relation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>new last</x:t>
-  </x:si>
-  <x:si>
-    <x:t>E115-XQP6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>margalla hill</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FE65-MJIB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83B6-ED47</x:t>
+    <x:t>1AA1-TIH9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>carmi gandazia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3232323</x:t>
   </x:si>
   <x:si>
     <x:t>nab ahmed child</x:t>
   </x:si>
   <x:si>
-    <x:t>D0C9-M0CQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>testm il</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4356-V95A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>new partner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>school child</x:t>
+    <x:t>TRST TEST</x:t>
   </x:si>
   <x:si>
     <x:t>basic web</x:t>
   </x:si>
   <x:si>
-    <x:t>dilbar rukha</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sufi cup</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5D0A-RMPK</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tst </x:t>
+    <x:t>D1DD-IRVU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>khush hona1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>khush1@gmail.con</x:t>
+  </x:si>
+  <x:si>
+    <x:t>exteme team</x:t>
+  </x:si>
+  <x:si>
+    <x:t>main husband</x:t>
   </x:si>
   <x:si>
     <x:t>another relative</x:t>
   </x:si>
   <x:si>
-    <x:t>D4C5-ZQQB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tets tet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nab ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rananabeelahmed772@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8540-Q7DB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test</x:t>
-  </x:si>
-  <x:si>
     <x:t>043E-D109</x:t>
   </x:si>
   <x:si>
-    <x:t>tet tt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2E65-SXT6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>first test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D1DD-IRVU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>khush hona1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>khush1@gmail.con</x:t>
-  </x:si>
-  <x:si>
-    <x:t>exteme team</x:t>
+    <x:t xml:space="preserve">testhshhd...1 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFA9-V8G1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test missinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBB9-PGI5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>trd test</x:t>
   </x:si>
   <x:si>
     <x:t>F12A-92SY</x:t>
@@ -442,76 +508,16 @@
     <x:t>nabeeloutsourcenz2@gmail.com</x:t>
   </x:si>
   <x:si>
-    <x:t>test tesssss</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRST TEST</x:t>
-  </x:si>
-  <x:si>
-    <x:t>main husband</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBB9-PGI5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>trd test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0F2D-MM6C</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">testt </x:t>
-  </x:si>
-  <x:si>
     <x:t>2B7C-80QZ</x:t>
   </x:si>
   <x:si>
     <x:t>client nme</x:t>
   </x:si>
   <x:si>
-    <x:t>AFA9-V8G1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test missinh</x:t>
-  </x:si>
-  <x:si>
     <x:t>tst r</x:t>
   </x:si>
   <x:si>
-    <x:t>8627-1VBD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rar test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>840E-CILQ</x:t>
-  </x:si>
-  <x:si>
     <x:t>ayesha nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AA8F-FH1K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>lets see</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel muhammad changes</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test3333@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1AA1-TIH9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>carmi gandazia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3232323</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">testhshhd...1 </x:t>
   </x:si>
 </x:sst>
 </file>
@@ -966,70 +972,67 @@
       <x:c r="B2" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
       <x:c r="A3" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:19">
       <x:c r="A4" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H4" s="1">
+        <x:v>45519</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:19">
       <x:c r="A5" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:19">
       <x:c r="A6" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="H6" s="1">
-        <x:v>45141</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:19">
@@ -1042,69 +1045,72 @@
       <x:c r="E7" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>36</x:v>
+      <x:c r="F7" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:19">
       <x:c r="A8" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
+      <x:c r="D8" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>45519</x:v>
+        <x:v>45141</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:19">
       <x:c r="A9" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:19">
       <x:c r="A10" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="B10" s="0" t="s">
+      <x:c r="E10" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
         <x:v>43</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="H10" s="1">
-        <x:v>45237</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:19">
       <x:c r="A11" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B11" s="0" t="s">
+      <x:c r="H11" s="1">
+        <x:v>45237</x:v>
+      </x:c>
+      <x:c r="L11" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
     </x:row>
@@ -1116,18 +1122,21 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:19">
       <x:c r="A13" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>52</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H13" s="1">
+        <x:v>45476</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:19">
@@ -1137,9 +1146,6 @@
       <x:c r="B14" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E14" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
     </x:row>
     <x:row r="15" spans="1:19">
       <x:c r="A15" s="0" t="s">
@@ -1152,7 +1158,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H15" s="1">
         <x:v>45014</x:v>
@@ -1165,440 +1171,434 @@
       <x:c r="B16" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H16" s="1">
+        <x:v>45070</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" spans="1:19">
       <x:c r="A17" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H17" s="1">
+        <x:v>45505</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:19">
       <x:c r="A18" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:19">
       <x:c r="A19" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E19" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H19" s="1">
-        <x:v>45505</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:19">
       <x:c r="A20" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="H20" s="1">
-        <x:v>36910</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:19">
       <x:c r="A21" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="F21" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G21" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="H21" s="1">
-        <x:v>45476</x:v>
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:19">
       <x:c r="A22" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F22" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:19">
       <x:c r="A23" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="E23" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="H23" s="1">
-        <x:v>45651</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:19">
       <x:c r="A24" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="E24" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="H24" s="1">
-        <x:v>30213</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:19">
       <x:c r="A25" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D25" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E25" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F25" s="0" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="H25" s="1">
-        <x:v>45070</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:19">
       <x:c r="A26" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="B26" s="0" t="s">
+      <x:c r="E26" s="0" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="D26" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="E26" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="G26" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>45204</x:v>
-      </x:c>
-      <x:c r="L26" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>26021</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:19">
       <x:c r="A27" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F27" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="D27" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F27" s="0" t="s">
-        <x:v>21</x:v>
+      <x:c r="G27" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H27" s="1">
+        <x:v>45204</x:v>
+      </x:c>
+      <x:c r="L27" s="0" t="s">
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:19">
       <x:c r="A28" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F28" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H28" s="1">
+        <x:v>45651</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:19">
       <x:c r="A29" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D29" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="G29" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:19">
       <x:c r="A30" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F30" s="0" t="s">
         <x:v>101</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="F30" s="0" t="s">
-        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:19">
       <x:c r="A31" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="E31" s="0" t="s">
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G31" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:19">
       <x:c r="A32" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="D32" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="G32" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:19">
       <x:c r="A33" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H33" s="1">
+        <x:v>44175</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:19">
       <x:c r="A34" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="E34" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F34" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H34" s="1">
+        <x:v>26022</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:19">
       <x:c r="A35" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="E35" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H35" s="1">
+        <x:v>36910</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:19">
       <x:c r="A36" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H36" s="1">
+        <x:v>26021</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:19">
       <x:c r="A37" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G37" s="0" t="s">
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:19">
       <x:c r="A38" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="D38" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="E38" s="0" t="s">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G38" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H38" s="1">
+        <x:v>30213</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:19">
       <x:c r="A39" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E39" s="0" t="s">
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G39" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:19">
       <x:c r="A40" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="F40" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="H40" s="1">
-        <x:v>44972</x:v>
-      </x:c>
     </x:row>
     <x:row r="41" spans="1:19">
       <x:c r="A41" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="E41" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:19">
       <x:c r="A42" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E42" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="F42" s="0" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="E42" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="F42" s="0" t="s">
-        <x:v>68</x:v>
       </x:c>
       <x:c r="H42" s="1">
         <x:v>44980</x:v>
       </x:c>
       <x:c r="K42" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:19">
       <x:c r="A43" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>122</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:19">
       <x:c r="A44" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G44" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:19">
       <x:c r="A45" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="E45" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="F45" s="0" t="s">
-        <x:v>21</x:v>
+      <x:c r="D45" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="G45" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="L45" s="0" t="s">
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:19">
       <x:c r="A46" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="E46" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="F46" s="0" t="s">
         <x:v>101</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="E46" s="0" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="F46" s="0" t="s">
-        <x:v>103</x:v>
       </x:c>
       <x:c r="H46" s="1">
         <x:v>44929</x:v>
@@ -1606,276 +1606,264 @@
     </x:row>
     <x:row r="47" spans="1:19">
       <x:c r="A47" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D47" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="G47" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="L47" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:19">
       <x:c r="A48" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F48" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:19">
       <x:c r="A49" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G49" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="H49" s="1">
-        <x:v>44175</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:19">
       <x:c r="A50" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="F50" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="E50" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="H50" s="1">
+        <x:v>44928</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:19">
       <x:c r="A51" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="H51" s="1">
-        <x:v>45149</x:v>
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G51" s="0" t="s">
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:19">
       <x:c r="A52" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="E52" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="H52" s="1">
-        <x:v>45014</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:19">
       <x:c r="A53" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G53" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:19">
       <x:c r="A54" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="G54" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:19">
       <x:c r="A55" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="D55" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="E55" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G55" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H55" s="1">
-        <x:v>45148</x:v>
+        <x:v>44972</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:19">
       <x:c r="A56" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="E56" s="0" t="s">
+        <x:v>150</x:v>
       </x:c>
       <x:c r="F56" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H56" s="1">
-        <x:v>45014</x:v>
+        <x:v>45149</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:19">
       <x:c r="A57" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D57" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="E57" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F57" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G57" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H57" s="1">
+        <x:v>45148</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:19">
       <x:c r="A58" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F58" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:19">
       <x:c r="A59" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F59" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:19">
       <x:c r="A60" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="D60" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="F60" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="H60" s="1">
-        <x:v>45047</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:19">
       <x:c r="A61" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="E61" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="F61" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:19">
       <x:c r="A62" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="E62" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="F62" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H62" s="1">
-        <x:v>45169</x:v>
+        <x:v>45014</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:19">
       <x:c r="A63" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="D63" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="E63" s="0" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F63" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H63" s="1">
+        <x:v>45014</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:19">
       <x:c r="A64" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="E64" s="0" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="H64" s="1">
-        <x:v>44928</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:19">
       <x:c r="A65" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="D65" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H65" s="1">
+        <x:v>45047</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:19">
       <x:c r="A66" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E66" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H66" s="1">
+        <x:v>45169</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="184">
   <x:si>
     <x:t>EZMId</x:t>
   </x:si>
@@ -73,6 +73,15 @@
     <x:t>X-ray Grading</x:t>
   </x:si>
   <x:si>
+    <x:t>574C-4I7Q</x:t>
+  </x:si>
+  <x:si>
+    <x:t>margalla hill</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel</x:t>
+  </x:si>
+  <x:si>
     <x:t>601F-EQSK</x:t>
   </x:si>
   <x:si>
@@ -82,7 +91,31 @@
     <x:t>a@gmail.com</x:t>
   </x:si>
   <x:si>
-    <x:t>Owner nabeel</x:t>
+    <x:t>F4B8-KXPP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nab ahmed wife</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7CAB-QBI3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>wife GvX4T</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3540404040</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>occupation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>80A6-5VCD</x:t>
   </x:si>
   <x:si>
     <x:t>1558-41KA</x:t>
@@ -91,7 +124,31 @@
     <x:t>passport num</x:t>
   </x:si>
   <x:si>
-    <x:t>test@gmail.com</x:t>
+    <x:t>2289-PRD0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dilbar rukha</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz1@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member,Nabeel Ahmed,exteme team,Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7900-P6ME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>wif cup wife</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>331F-46PG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>st test</x:t>
   </x:si>
   <x:si>
     <x:t>B1E1-CQMU</x:t>
@@ -103,10 +160,10 @@
     <x:t>nabel123@gmail.com</x:t>
   </x:si>
   <x:si>
-    <x:t>331F-46PG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>st test</x:t>
+    <x:t>4356-V95A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>new partner</x:t>
   </x:si>
   <x:si>
     <x:t>BC27-YS4F</x:t>
@@ -115,22 +172,97 @@
     <x:t xml:space="preserve">test </x:t>
   </x:si>
   <x:si>
+    <x:t>D980-Q0AX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel secutriy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>434434434</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2B13-9R2K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nbaaa Efgh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rana44@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teacher</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nab ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rananabeelahmed772@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2AE0-BA0G</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test school</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tag 3 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>relative test</x:t>
+  </x:si>
+  <x:si>
     <x:t>AE20-18YO</x:t>
   </x:si>
   <x:si>
     <x:t>tst client log</x:t>
   </x:si>
   <x:si>
-    <x:t>nabeeloutsourcenz1@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D980-Q0AX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel secutriy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>434434434</x:t>
+    <x:t>0F7C-7GGW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nw profile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6F95-P7I6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TST again</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24D9-XVJK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tes test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E260-TX8K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>check now</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFA9-V8G1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test missinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>shcool relation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>relation@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D0C9-M0CQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>testm il</x:t>
   </x:si>
   <x:si>
     <x:t>1D77-ED7L</x:t>
@@ -139,28 +271,91 @@
     <x:t>retret retret</x:t>
   </x:si>
   <x:si>
-    <x:t>6F95-P7I6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TST again</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tag 3 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>2B13-9R2K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nbaaa Efgh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rana44@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tag 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Teacher</x:t>
+    <x:t>EBB9-PGI5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>trd test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8A4F-QGQD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D4C5-ZQQB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tets tet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ayesh ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>840E-CILQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ayesha nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83B6-ED47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>kiran nao</x:t>
+  </x:si>
+  <x:si>
+    <x:t>66B5-QH28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bingo jabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>balistan@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test tesssss</x:t>
+  </x:si>
+  <x:si>
+    <x:t>170B-XD4G</x:t>
+  </x:si>
+  <x:si>
+    <x:t>finame shuja</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3535</x:t>
+  </x:si>
+  <x:si>
+    <x:t>211267313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test occupation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>252F-ASJE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tett test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8540-Q7DB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tet tt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AA8F-FH1K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>lets see</x:t>
   </x:si>
   <x:si>
     <x:t>A5C1-YB22</x:t>
@@ -172,22 +367,43 @@
     <x:t>arsalan team member,Owner nabeel</x:t>
   </x:si>
   <x:si>
-    <x:t>relative test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>E260-TX8K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>check now</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24D9-XVJK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tes test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenz@gmail.com</x:t>
+    <x:t>D1DD-IRVU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>khush hona1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>khush1@gmail.con</x:t>
+  </x:si>
+  <x:si>
+    <x:t>exteme team</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70A6-XDYQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TETSTTTWT TT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>999999</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,add agent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test sqaq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>main husband</x:t>
+  </x:si>
+  <x:si>
+    <x:t>school child</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0F2D-MM6C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">testt </x:t>
   </x:si>
   <x:si>
     <x:t>1414-W44K</x:t>
@@ -208,13 +424,19 @@
     <x:t>arsalan team member</x:t>
   </x:si>
   <x:si>
-    <x:t>7900-P6ME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sufi cup wife</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
+    <x:t>BE8D-A2NZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>reign test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>child hAnUT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FE65-MJIB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test nabeel</x:t>
   </x:si>
   <x:si>
     <x:t>3A8B-SII4</x:t>
@@ -223,22 +445,25 @@
     <x:t>new child</x:t>
   </x:si>
   <x:si>
-    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
-  </x:si>
-  <x:si>
     <x:t>Owner nabeel,team member nabeel</x:t>
   </x:si>
   <x:si>
     <x:t>tag 3 ,tag 1</x:t>
   </x:si>
   <x:si>
-    <x:t>ayesh ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2AE0-BA0G</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test school</x:t>
+    <x:t>5D0A-RMPK</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tst </x:t>
+  </x:si>
+  <x:si>
+    <x:t>basic web</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sufi cup</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz</x:t>
   </x:si>
   <x:si>
     <x:t>AC22-Z9CM</x:t>
@@ -247,19 +472,37 @@
     <x:t>test Streich</x:t>
   </x:si>
   <x:si>
-    <x:t>252F-ASJE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tett test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2289-PRD0</x:t>
+    <x:t>1AA1-TIH9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>carmi gandazia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3232323</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F12A-92SY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>first name last name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5657</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz2@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2E65-SXT6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>first test</x:t>
   </x:si>
   <x:si>
     <x:t>rukha begum</x:t>
   </x:si>
   <x:si>
-    <x:t>arsalan team member,Nabeel Ahmed,exteme team,Owner nabeel</x:t>
+    <x:t>nab ahmed child</x:t>
   </x:si>
   <x:si>
     <x:t>4395-EYPH</x:t>
@@ -268,73 +511,10 @@
     <x:t>arif lohar</x:t>
   </x:si>
   <x:si>
-    <x:t>D0C9-M0CQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>testm il</x:t>
-  </x:si>
-  <x:si>
-    <x:t>shcool relation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>relation@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>70A6-XDYQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TETSTTTWT TT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>999999</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,add agent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test sqaq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>510D-BPGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bingo jabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>balistan@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83B6-ED47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F4B8-KXPP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nab ahmed wife</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dilbar rukha</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D4C5-ZQQB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tets tet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tet tt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>kiran nao</x:t>
+    <x:t>new last</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag 1</x:t>
   </x:si>
   <x:si>
     <x:t>0924-9S1L</x:t>
@@ -343,19 +523,7 @@
     <x:t>Owner nabeel,arsalan team member</x:t>
   </x:si>
   <x:si>
-    <x:t>test tesssss</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0F2D-MM6C</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">testt </x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE8D-A2NZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>reign test</x:t>
+    <x:t>another relative</x:t>
   </x:si>
   <x:si>
     <x:t>8627-1VBD</x:t>
@@ -364,46 +532,7 @@
     <x:t>rar test</x:t>
   </x:si>
   <x:si>
-    <x:t>FE65-MJIB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4356-V95A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>new partner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sufi cup</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz</x:t>
-  </x:si>
-  <x:si>
-    <x:t>school child</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5D0A-RMPK</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tst </x:t>
-  </x:si>
-  <x:si>
-    <x:t>8540-Q7DB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>211267313</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nab ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rananabeelahmed772@gmail.com</x:t>
+    <x:t>TRST TEST</x:t>
   </x:si>
   <x:si>
     <x:t>9713-YA5L</x:t>
@@ -412,19 +541,7 @@
     <x:t>nimal test</x:t>
   </x:si>
   <x:si>
-    <x:t>AA8F-FH1K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>lets see</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2E65-SXT6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>first test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>840E-CILQ</x:t>
+    <x:t>E99C-5INR</x:t>
   </x:si>
   <x:si>
     <x:t>nabeel muhammad changes</x:t>
@@ -436,78 +553,12 @@
     <x:t>test3333@gmail.com</x:t>
   </x:si>
   <x:si>
-    <x:t>new last</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tag 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1AA1-TIH9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>carmi gandazia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3232323</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nab ahmed child</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRST TEST</x:t>
-  </x:si>
-  <x:si>
-    <x:t>basic web</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D1DD-IRVU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>khush hona1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>khush1@gmail.con</x:t>
-  </x:si>
-  <x:si>
-    <x:t>exteme team</x:t>
-  </x:si>
-  <x:si>
-    <x:t>main husband</x:t>
-  </x:si>
-  <x:si>
-    <x:t>another relative</x:t>
-  </x:si>
-  <x:si>
     <x:t>043E-D109</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">testhshhd...1 </x:t>
   </x:si>
   <x:si>
-    <x:t>AFA9-V8G1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test missinh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBB9-PGI5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>trd test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F12A-92SY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>first name last name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5657</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenz2@gmail.com</x:t>
-  </x:si>
-  <x:si>
     <x:t>2B7C-80QZ</x:t>
   </x:si>
   <x:si>
@@ -515,9 +566,6 @@
   </x:si>
   <x:si>
     <x:t>tst r</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ayesha nabeel</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -588,8 +636,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S66" totalsRowShown="0">
-  <x:autoFilter ref="A1:S66"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S75" totalsRowShown="0">
+  <x:autoFilter ref="A1:S75"/>
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="EZMId"/>
     <x:tableColumn id="2" name="Name"/>
@@ -903,7 +951,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:S66"/>
+  <x:dimension ref="A1:S75"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -972,81 +1020,75 @@
       <x:c r="B2" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
       <x:c r="A3" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
+      <x:c r="E3" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:19">
       <x:c r="A4" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
+      <x:c r="F4" s="0" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H4" s="1">
-        <x:v>45519</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:19">
       <x:c r="A5" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
+      <x:c r="C5" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:19">
       <x:c r="A6" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:19">
       <x:c r="A7" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:19">
@@ -1056,95 +1098,101 @@
       <x:c r="B8" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="D8" s="0" t="s">
+      <x:c r="E8" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H8" s="1">
-        <x:v>45141</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:19">
       <x:c r="A9" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H9" s="1">
+        <x:v>45505</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:19">
       <x:c r="A10" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:19">
       <x:c r="A11" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>45237</x:v>
-      </x:c>
-      <x:c r="L11" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45519</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:19">
       <x:c r="A12" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:19">
       <x:c r="A13" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H13" s="1">
-        <x:v>45476</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:19">
       <x:c r="A14" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B14" s="0" t="s">
+      <x:c r="D14" s="0" t="s">
         <x:v>54</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H14" s="1">
+        <x:v>45141</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:19">
@@ -1158,282 +1206,258 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>45014</x:v>
+        <x:v>45237</x:v>
+      </x:c>
+      <x:c r="L15" s="0" t="s">
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:19">
       <x:c r="A16" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C16" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D16" s="0" t="s">
+      <x:c r="E16" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="E16" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>45070</x:v>
+        <x:v>44929</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:19">
       <x:c r="A17" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="B17" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F17" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H17" s="1">
-        <x:v>45505</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:19">
       <x:c r="A18" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="E18" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="G18" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H18" s="1">
+        <x:v>45476</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:19">
       <x:c r="A19" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:19">
       <x:c r="A20" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G20" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:19">
       <x:c r="A21" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G21" s="0" t="s">
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:19">
       <x:c r="A22" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F22" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H22" s="1">
+        <x:v>45014</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:19">
       <x:c r="A23" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="F23" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:19">
       <x:c r="A24" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:19">
       <x:c r="A25" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H25" s="1">
+        <x:v>26021</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:19">
       <x:c r="A26" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="E26" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F26" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H26" s="1">
-        <x:v>26021</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:19">
       <x:c r="A27" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D27" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E27" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F27" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="G27" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H27" s="1">
-        <x:v>45204</x:v>
-      </x:c>
-      <x:c r="L27" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:19">
       <x:c r="A28" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="E28" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>45651</x:v>
+        <x:v>45014</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:19">
       <x:c r="A29" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="E29" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:19">
       <x:c r="A30" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:19">
       <x:c r="A31" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="E31" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:19">
       <x:c r="A32" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="F32" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H32" s="1">
+        <x:v>45169</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:19">
       <x:c r="A33" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E33" s="0" t="s">
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H33" s="1">
-        <x:v>44175</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:19">
       <x:c r="A34" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F34" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H34" s="1">
         <x:v>26022</x:v>
@@ -1441,27 +1465,30 @@
     </x:row>
     <x:row r="35" spans="1:19">
       <x:c r="A35" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>36910</x:v>
+        <x:v>45651</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:19">
       <x:c r="A36" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H36" s="1">
         <x:v>26021</x:v>
@@ -1469,166 +1496,208 @@
     </x:row>
     <x:row r="37" spans="1:19">
       <x:c r="A37" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="G37" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F37" s="0" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:19">
       <x:c r="A38" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H38" s="1">
-        <x:v>30213</x:v>
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K38" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="L38" s="0" t="s">
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:19">
       <x:c r="A39" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="E39" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F39" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:19">
       <x:c r="A40" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="G40" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="L40" s="0" t="s">
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:19">
       <x:c r="A41" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H41" s="1">
+        <x:v>44175</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:19">
       <x:c r="A42" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="E42" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="F42" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H42" s="1">
-        <x:v>44980</x:v>
-      </x:c>
-      <x:c r="K42" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:19">
       <x:c r="A43" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:19">
       <x:c r="A44" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E44" s="0" t="s">
+        <x:v>119</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H44" s="1">
+        <x:v>45149</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:19">
       <x:c r="A45" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="E45" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F45" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="G45" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H45" s="1">
+        <x:v>45204</x:v>
+      </x:c>
+      <x:c r="L45" s="0" t="s">
         <x:v>125</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D45" s="0" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="G45" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="L45" s="0" t="s">
-        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:19">
       <x:c r="A46" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G46" s="0" t="s">
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H46" s="1">
-        <x:v>44929</x:v>
+        <x:v>45148</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:19">
       <x:c r="A47" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="F47" s="0" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:19">
       <x:c r="A48" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="G48" s="0" t="s">
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:19">
       <x:c r="A49" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="E49" s="0" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="B49" s="0" t="s">
+      <x:c r="F49" s="0" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="F49" s="0" t="s">
-        <x:v>22</x:v>
+      <x:c r="H49" s="1">
+        <x:v>45070</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:19">
@@ -1638,78 +1707,81 @@
       <x:c r="B50" s="0" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="D50" s="0" t="s">
-        <x:v>138</x:v>
-      </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F50" s="0" t="s">
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H50" s="1">
-        <x:v>44928</x:v>
+        <x:v>30213</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:19">
       <x:c r="A51" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="D51" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="G51" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="L51" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:19">
       <x:c r="A52" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="D52" s="0" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="F52" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:19">
       <x:c r="A53" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="E53" s="0" t="s">
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="G53" s="0" t="s">
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:19">
       <x:c r="A54" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
         <x:v>146</x:v>
       </x:c>
+      <x:c r="F54" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
     </x:row>
     <x:row r="55" spans="1:19">
       <x:c r="A55" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
         <x:v>147</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H55" s="1">
         <x:v>44972</x:v>
@@ -1717,153 +1789,255 @@
     </x:row>
     <x:row r="56" spans="1:19">
       <x:c r="A56" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="B56" s="0" t="s">
+      <x:c r="E56" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F56" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H56" s="1">
+        <x:v>44980</x:v>
+      </x:c>
+      <x:c r="K56" s="0" t="s">
         <x:v>149</x:v>
-      </x:c>
-      <x:c r="E56" s="0" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="F56" s="0" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="H56" s="1">
-        <x:v>45149</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:19">
       <x:c r="A57" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="D57" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F57" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G57" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H57" s="1">
-        <x:v>45148</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:19">
       <x:c r="A58" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
         <x:v>153</x:v>
       </x:c>
+      <x:c r="D58" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
       <x:c r="F58" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:19">
       <x:c r="A59" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="D59" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="E59" s="0" t="s">
+        <x:v>158</x:v>
       </x:c>
       <x:c r="F59" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H59" s="1">
+        <x:v>45014</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:19">
       <x:c r="A60" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F60" s="0" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:19">
       <x:c r="A61" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="F61" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:19">
       <x:c r="A62" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="F62" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H62" s="1">
-        <x:v>45014</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:19">
       <x:c r="A63" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="D63" s="0" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="E63" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="F63" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H63" s="1">
-        <x:v>45014</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:19">
       <x:c r="A64" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
         <x:v>165</x:v>
       </x:c>
+      <x:c r="D64" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="E64" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F64" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="G64" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
     </x:row>
     <x:row r="65" spans="1:19">
       <x:c r="A65" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H65" s="1">
-        <x:v>45047</x:v>
+        <x:v>36910</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:19">
       <x:c r="A66" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="E66" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H66" s="1">
-        <x:v>45169</x:v>
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="F66" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:19">
+      <x:c r="A67" s="0" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="E67" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F67" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:19">
+      <x:c r="A68" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:19">
+      <x:c r="A69" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>174</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:19">
+      <x:c r="A70" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F70" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:19">
+      <x:c r="A71" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="D71" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="E71" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="H71" s="1">
+        <x:v>44928</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:19">
+      <x:c r="A72" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F72" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:19">
+      <x:c r="A73" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:19">
+      <x:c r="A74" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:19">
+      <x:c r="A75" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="F75" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="H75" s="1">
+        <x:v>45047</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/ClientsList.xlsx
+++ b/cypress/downloads/ClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="184">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="172">
   <x:si>
     <x:t>EZMId</x:t>
   </x:si>
@@ -73,151 +73,397 @@
     <x:t>X-ray Grading</x:t>
   </x:si>
   <x:si>
-    <x:t>574C-4I7Q</x:t>
+    <x:t>601F-EQSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test gamux</x:t>
+  </x:si>
+  <x:si>
+    <x:t>a@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1D77-ED7L</x:t>
+  </x:si>
+  <x:si>
+    <x:t>retret retret</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24D9-XVJK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tes test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B1E1-CQMU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>expire thing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabel123@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0419-D00O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rananabeelahmed968@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel@outsourcenz.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2B13-9R2K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nbaaa Efgh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rana44@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teacher</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7900-P6ME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>wif cup wife</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz1@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D980-Q0AX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel secutriy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>434434434</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6F95-P7I6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TST again</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tag 3 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>1414-W44K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3540479390287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3233232</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member</x:t>
+  </x:si>
+  <x:si>
+    <x:t>331F-46PG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>st test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E260-TX8K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>check now</x:t>
+  </x:si>
+  <x:si>
+    <x:t>252F-ASJE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tett test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2AE0-BA0G</x:t>
+  </x:si>
+  <x:si>
+    <x:t>shcool relation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>relation@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test school</x:t>
+  </x:si>
+  <x:si>
+    <x:t>relative test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A5C1-YB22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>basic wfe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member,Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D0C9-M0CQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>testm il</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BC27-YS4F</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">test </x:t>
+  </x:si>
+  <x:si>
+    <x:t>ayesh ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>school child</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83B6-ED47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2289-PRD0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dilbar rukha</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member,Nabeel Ahmed,exteme team,Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rukha begum</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3A8B-SII4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>new child</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,team member nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag 3 ,tag 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BE8D-A2NZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>reign test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AE20-18YO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tst client log</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F4B8-KXPP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nab ahmed wife</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBB9-PGI5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>trd test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tet tt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0F2D-MM6C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">testt </x:t>
+  </x:si>
+  <x:si>
+    <x:t>70A6-XDYQ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TETSTTTWT TT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>999999</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,add agent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test sqaq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test tesssss</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5D0A-RMPK</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tst </x:t>
+  </x:si>
+  <x:si>
+    <x:t>155A-XX5F</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bingo jabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>balistan@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4356-V95A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>new partner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8627-1VBD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rar test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nab ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rananabeelahmed772@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FE65-MJIB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AA8F-FH1K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>lets see</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8540-Q7DB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>211267313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9713-YA5L</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nimal test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AC22-Z9CM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test Streich</x:t>
+  </x:si>
+  <x:si>
+    <x:t>new last</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B18D-C0NX</x:t>
   </x:si>
   <x:si>
     <x:t>margalla hill</x:t>
   </x:si>
   <x:si>
-    <x:t>Owner nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>601F-EQSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test gamux</x:t>
-  </x:si>
-  <x:si>
-    <x:t>a@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F4B8-KXPP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nab ahmed wife</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7CAB-QBI3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>wife GvX4T</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3540404040</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>occupation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>80A6-5VCD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1558-41KA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>passport num</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2289-PRD0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dilbar rukha</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenz1@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member,Nabeel Ahmed,exteme team,Owner nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7900-P6ME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>wif cup wife</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>331F-46PG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>st test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B1E1-CQMU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>expire thing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabel123@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4356-V95A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>new partner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BC27-YS4F</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">test </x:t>
-  </x:si>
-  <x:si>
-    <x:t>D980-Q0AX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel secutriy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>434434434</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2B13-9R2K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nbaaa Efgh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rana44@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tag 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Teacher</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nab ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rananabeelahmed772@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2AE0-BA0G</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test school</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tag 3 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>relative test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AE20-18YO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tst client log</x:t>
+    <x:t>basic web</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sufi cup</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1AA1-TIH9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>carmi gandazia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3232323</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4395-EYPH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arif lohar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nab ahmed child</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2E65-SXT6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>first test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRST TEST</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D4C5-ZQQB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tets tet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F12A-92SY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>first name last name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5657</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz2@gmail.com</x:t>
   </x:si>
   <x:si>
     <x:t>0F7C-7GGW</x:t>
@@ -226,25 +472,25 @@
     <x:t>nw profile</x:t>
   </x:si>
   <x:si>
-    <x:t>6F95-P7I6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TST again</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24D9-XVJK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tes test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenz@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>E260-TX8K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>check now</x:t>
+    <x:t>tst r</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0924-9S1L</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,arsalan team member</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D1DD-IRVU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>khush hona1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>khush1@gmail.con</x:t>
+  </x:si>
+  <x:si>
+    <x:t>exteme team</x:t>
   </x:si>
   <x:si>
     <x:t>AFA9-V8G1</x:t>
@@ -253,309 +499,30 @@
     <x:t>test missinh</x:t>
   </x:si>
   <x:si>
-    <x:t>shcool relation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>relation@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D0C9-M0CQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>testm il</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1D77-ED7L</x:t>
-  </x:si>
-  <x:si>
-    <x:t>retret retret</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBB9-PGI5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>trd test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8A4F-QGQD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D4C5-ZQQB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tets tet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ayesh ahmed</x:t>
+    <x:t>043E-D109</x:t>
   </x:si>
   <x:si>
     <x:t>840E-CILQ</x:t>
   </x:si>
   <x:si>
+    <x:t>nabeel muhammad changes</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33333333</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test3333@gmail.com</x:t>
+  </x:si>
+  <x:si>
     <x:t>ayesha nabeel</x:t>
   </x:si>
   <x:si>
-    <x:t>83B6-ED47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>kiran nao</x:t>
-  </x:si>
-  <x:si>
-    <x:t>66B5-QH28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bingo jabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>balistan@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test tesssss</x:t>
-  </x:si>
-  <x:si>
-    <x:t>170B-XD4G</x:t>
-  </x:si>
-  <x:si>
-    <x:t>finame shuja</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3535</x:t>
-  </x:si>
-  <x:si>
-    <x:t>211267313</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test occupation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>252F-ASJE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tett test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8540-Q7DB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tet tt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AA8F-FH1K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>lets see</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A5C1-YB22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>basic wfe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member,Owner nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D1DD-IRVU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>khush hona1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>khush1@gmail.con</x:t>
-  </x:si>
-  <x:si>
-    <x:t>exteme team</x:t>
-  </x:si>
-  <x:si>
-    <x:t>70A6-XDYQ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TETSTTTWT TT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>999999</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,add agent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test sqaq</x:t>
+    <x:t>another relative</x:t>
   </x:si>
   <x:si>
     <x:t>main husband</x:t>
   </x:si>
   <x:si>
-    <x:t>school child</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0F2D-MM6C</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">testt </x:t>
-  </x:si>
-  <x:si>
-    <x:t>1414-W44K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3540479390287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3233232</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE8D-A2NZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>reign test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>child hAnUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FE65-MJIB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3A8B-SII4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>new child</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,team member nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tag 3 ,tag 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5D0A-RMPK</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tst </x:t>
-  </x:si>
-  <x:si>
-    <x:t>basic web</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sufi cup</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AC22-Z9CM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test Streich</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1AA1-TIH9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>carmi gandazia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3232323</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F12A-92SY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>first name last name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5657</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenz2@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2E65-SXT6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>first test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rukha begum</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nab ahmed child</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4395-EYPH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arif lohar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>new last</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tag 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0924-9S1L</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,arsalan team member</x:t>
-  </x:si>
-  <x:si>
-    <x:t>another relative</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8627-1VBD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rar test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRST TEST</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9713-YA5L</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nimal test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>E99C-5INR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel muhammad changes</x:t>
-  </x:si>
-  <x:si>
-    <x:t>33333333</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test3333@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>043E-D109</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">testhshhd...1 </x:t>
   </x:si>
   <x:si>
@@ -563,9 +530,6 @@
   </x:si>
   <x:si>
     <x:t>client nme</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tst r</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -636,8 +600,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S75" totalsRowShown="0">
-  <x:autoFilter ref="A1:S75"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:S68" totalsRowShown="0">
+  <x:autoFilter ref="A1:S68"/>
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="EZMId"/>
     <x:tableColumn id="2" name="Name"/>
@@ -951,7 +915,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:S75"/>
+  <x:dimension ref="A1:S68"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -1020,22 +984,19 @@
       <x:c r="B2" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
       <x:c r="A3" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:19">
@@ -1045,8 +1006,14 @@
       <x:c r="B4" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H4" s="1">
+        <x:v>45014</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:19">
@@ -1056,52 +1023,64 @@
       <x:c r="B5" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="s">
+      <x:c r="E5" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H5" s="1">
+        <x:v>45519</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:19">
       <x:c r="A6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:19">
       <x:c r="A7" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>31</x:v>
+      <x:c r="F7" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:19">
       <x:c r="A8" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
+      <x:c r="E8" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="E8" s="0" t="s">
+      <x:c r="F8" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F8" s="0" t="s">
+      <x:c r="H8" s="1">
+        <x:v>45237</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
@@ -1113,10 +1092,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H9" s="1">
         <x:v>45505</x:v>
@@ -1124,140 +1103,131 @@
     </x:row>
     <x:row r="10" spans="1:19">
       <x:c r="A10" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H10" s="1">
+        <x:v>45141</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:19">
       <x:c r="A11" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="H11" s="1">
-        <x:v>45519</x:v>
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:19">
       <x:c r="A12" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H12" s="1">
+        <x:v>45070</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:19">
       <x:c r="A13" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:19">
       <x:c r="A14" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E14" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F14" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="H14" s="1">
-        <x:v>45141</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:19">
       <x:c r="A15" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E15" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F15" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G15" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H15" s="1">
-        <x:v>45237</x:v>
-      </x:c>
-      <x:c r="L15" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:19">
       <x:c r="A16" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>44929</x:v>
+        <x:v>26021</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:19">
       <x:c r="A17" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:19">
       <x:c r="A18" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H18" s="1">
         <x:v>45476</x:v>
@@ -1265,66 +1235,54 @@
     </x:row>
     <x:row r="19" spans="1:19">
       <x:c r="A19" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E19" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:19">
       <x:c r="A20" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="F20" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:19">
       <x:c r="A21" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="E21" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G21" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F21" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:19">
       <x:c r="A22" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="E22" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="H22" s="1">
-        <x:v>45014</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:19">
       <x:c r="A23" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>76</x:v>
+      </x:c>
+      <x:c r="F23" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:19">
@@ -1332,35 +1290,38 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:19">
       <x:c r="A25" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="H25" s="1">
-        <x:v>26021</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:19">
       <x:c r="A26" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>82</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:19">
@@ -1370,379 +1331,358 @@
       <x:c r="B27" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
+      <x:c r="E27" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="F27" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G27" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" spans="1:19">
       <x:c r="A28" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>45014</x:v>
+        <x:v>30213</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:19">
       <x:c r="A29" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:19">
       <x:c r="A30" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="E30" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:19">
       <x:c r="A31" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H31" s="1">
+        <x:v>45014</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:19">
       <x:c r="A32" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="E32" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F32" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>45169</x:v>
+        <x:v>44175</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:19">
       <x:c r="A33" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="E33" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="F33" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G33" s="0" t="s">
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:19">
       <x:c r="A34" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F34" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="G34" s="0" t="s">
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>26022</x:v>
+        <x:v>45204</x:v>
+      </x:c>
+      <x:c r="L34" s="0" t="s">
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:19">
       <x:c r="A35" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="E35" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>45651</x:v>
+        <x:v>26021</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:19">
       <x:c r="A36" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="H36" s="1">
-        <x:v>26021</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:19">
       <x:c r="A37" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
+        <x:v>110</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H37" s="1">
+        <x:v>45651</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:19">
       <x:c r="A38" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="C38" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="D38" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="E38" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="K38" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="L38" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:19">
       <x:c r="A39" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="E39" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F39" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:19">
       <x:c r="A40" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D40" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="G40" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="L40" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E40" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="F40" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="H40" s="1">
+        <x:v>44929</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:19">
       <x:c r="A41" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="F41" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="H41" s="1">
-        <x:v>44175</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:19">
       <x:c r="A42" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:19">
       <x:c r="A43" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="F43" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G43" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L43" s="0" t="s">
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:19">
       <x:c r="A44" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="E44" s="0" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="F44" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="H44" s="1">
-        <x:v>45149</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:19">
       <x:c r="A45" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="D45" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="F45" s="0" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="G45" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H45" s="1">
-        <x:v>45204</x:v>
-      </x:c>
-      <x:c r="L45" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:19">
       <x:c r="A46" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G46" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H46" s="1">
-        <x:v>45148</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:19">
       <x:c r="A47" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:19">
       <x:c r="A48" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="G48" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="F48" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H48" s="1">
+        <x:v>44972</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:19">
       <x:c r="A49" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="C49" s="0" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="D49" s="0" t="s">
         <x:v>133</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="F49" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H49" s="1">
+        <x:v>44980</x:v>
+      </x:c>
+      <x:c r="K49" s="0" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="F49" s="0" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="H49" s="1">
-        <x:v>45070</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:19">
       <x:c r="A50" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="B50" s="0" t="s">
+      <x:c r="D50" s="0" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="E50" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="F50" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="H50" s="1">
-        <x:v>30213</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:19">
       <x:c r="A51" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="C51" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E51" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="L51" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:19">
       <x:c r="A52" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
         <x:v>140</x:v>
+      </x:c>
+      <x:c r="F52" s="0" t="s">
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:19">
@@ -1752,59 +1692,50 @@
       <x:c r="B53" s="0" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="E53" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="G53" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:19">
       <x:c r="A54" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="F54" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:19">
       <x:c r="A55" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E55" s="0" t="s">
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="H55" s="1">
-        <x:v>44972</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:19">
       <x:c r="A56" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D56" s="0" t="s">
         <x:v>148</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="F56" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H56" s="1">
-        <x:v>44980</x:v>
-      </x:c>
-      <x:c r="K56" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>45014</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:19">
@@ -1814,230 +1745,156 @@
       <x:c r="B57" s="0" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="E57" s="0" t="s">
-        <x:v>38</x:v>
+      <x:c r="F57" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:19">
       <x:c r="A58" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="B58" s="0" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="D58" s="0" t="s">
-        <x:v>154</x:v>
-      </x:c>
       <x:c r="F58" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H58" s="1">
+        <x:v>45047</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:19">
       <x:c r="A59" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="D59" s="0" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="E59" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F59" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="H59" s="1">
-        <x:v>45014</x:v>
+        <x:v>36910</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:19">
       <x:c r="A60" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="E60" s="0" t="s">
+        <x:v>157</x:v>
       </x:c>
       <x:c r="F60" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="H60" s="1">
+        <x:v>45149</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:19">
       <x:c r="A61" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="F61" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:19">
       <x:c r="A62" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F62" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:19">
       <x:c r="A63" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="B63" s="0" t="s">
+      <x:c r="D63" s="0" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="F63" s="0" t="s">
-        <x:v>21</x:v>
+      <x:c r="E63" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="H63" s="1">
+        <x:v>44928</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:19">
       <x:c r="A64" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="D64" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="F64" s="0" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="G64" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H64" s="1">
+        <x:v>45169</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:19">
       <x:c r="A65" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="B65" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="H65" s="1">
-        <x:v>36910</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:19">
       <x:c r="A66" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D66" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="E66" s="0" t="s">
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G66" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H66" s="1">
+        <x:v>45148</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:19">
       <x:c r="A67" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="E67" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F67" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:19">
       <x:c r="A68" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" spans="1:19">
-      <x:c r="A69" s="0" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="B69" s="0" t="s">
-        <x:v>174</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" spans="1:19">
-      <x:c r="A70" s="0" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="B70" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F70" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" spans="1:19">
-      <x:c r="A71" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="D71" s="0" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="E71" s="0" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="H71" s="1">
-        <x:v>44928</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72" spans="1:19">
-      <x:c r="A72" s="0" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="B72" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F72" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" spans="1:19">
-      <x:c r="A73" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="B73" s="0" t="s">
-        <x:v>180</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" spans="1:19">
-      <x:c r="A74" s="0" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="B74" s="0" t="s">
-        <x:v>182</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" spans="1:19">
-      <x:c r="A75" s="0" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="B75" s="0" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="F75" s="0" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="H75" s="1">
-        <x:v>45047</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
